--- a/nuevas_plazas.xlsx
+++ b/nuevas_plazas.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K7"/>
+  <dimension ref="A1:K8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,11 +491,7 @@
           <t>Docente de aula</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
           <t>Úmbita</t>
@@ -506,10 +502,8 @@
           <t>28/03/2026 a las 08:01</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
+      <c r="E2" t="n">
+        <v>63</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -548,11 +542,7 @@
           <t>Docente de aula</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr">
         <is>
           <t>Otanche</t>
@@ -563,10 +553,8 @@
           <t>28/03/2026 a las 08:01</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
+      <c r="E3" t="n">
+        <v>15</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -605,11 +593,7 @@
           <t>Docente de aula</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr">
         <is>
           <t>Ciénega</t>
@@ -620,10 +604,8 @@
           <t>28/03/2026 a las 08:01</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
+      <c r="E4" t="n">
+        <v>19</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -662,11 +644,7 @@
           <t>Docente de aula</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
           <t>Villa De Leyva</t>
@@ -677,10 +655,8 @@
           <t>28/03/2026 a las 08:01</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
+      <c r="E5" t="n">
+        <v>28</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -719,11 +695,7 @@
           <t>Docente tutor (Planta Temporal PTA)</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
           <t>Támara</t>
@@ -734,10 +706,8 @@
           <t>28/03/2026 a las 08:02</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
+      <c r="E6" t="n">
+        <v>39</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -776,52 +746,103 @@
           <t>Docente de aula</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Girardot</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>28/03/2026 a las 08:03</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>19</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Girardot</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Cundinamarca</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>ía de Educación: Girardot</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>I.E. SIMON BOLIVAR</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>I.E. SIMON BOLIVAR SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>ón: CL 65 46 A 95</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Girardot</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>28/03/2026 a las 08:03</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Girardot</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Cundinamarca</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>ía de Educación: Girardot</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Itaguí</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>28/03/2026 a las 08:05</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Itaguí</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>ía de Educación: Itaguí</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
         <is>
           <t>I.E. SIMON BOLIVAR</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t>I.E. SIMON BOLIVAR SEDE PRINCIPAL</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>ón: CL 65 46 A 95</t>
         </is>

--- a/nuevas_plazas.xlsx
+++ b/nuevas_plazas.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K8"/>
+  <dimension ref="A1:O11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -484,6 +484,26 @@
           <t>Direccion</t>
         </is>
       </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Tipo Priorización</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Zona Detalle</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Barrio</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Calendario Educativo</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -535,6 +555,10 @@
           <t>ón: CL 65 46 A 95</t>
         </is>
       </c>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -586,6 +610,10 @@
           <t>ón: CL 65 46 A 95</t>
         </is>
       </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -637,6 +665,10 @@
           <t>ón: CL 65 46 A 95</t>
         </is>
       </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -688,6 +720,10 @@
           <t>ón: CL 65 46 A 95</t>
         </is>
       </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -739,6 +775,10 @@
           <t>ón: CL 65 46 A 95</t>
         </is>
       </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -790,6 +830,10 @@
           <t>ón: CL 65 46 A 95</t>
         </is>
       </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -797,11 +841,7 @@
           <t>Docente de aula</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
           <t>Itaguí</t>
@@ -812,10 +852,8 @@
           <t>28/03/2026 a las 08:05</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
+      <c r="E8" t="n">
+        <v>60</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -845,6 +883,241 @@
       <c r="K8" t="inlineStr">
         <is>
           <t>ón: CL 65 46 A 95</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Matemáticas</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Itaguí</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>28/03/2026 a las 08:05</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Itaguí</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>ía de Educación: Itaguí</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>I.E. SIMON BOLIVAR</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>I.E. SIMON BOLIVAR SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>ón: CL 65 46 A 95</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>Itaguí</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Dirección: CL 65 46 A 95</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Humanidades y lengua castellana</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Itaguí</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>28/03/2026 a las 08:05</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Itaguí</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>ía de Educación: Itaguí</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>I.E. SIMON BOLIVAR</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>I.E. SIMON BOLIVAR SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>ón: CL 65 46 A 95</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>Itaguí</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Dirección: CL 65 46 A 95</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Itaguí</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>28/03/2026 a las 08:05</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Itaguí</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>ía de Educación: Itaguí</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>I.E. SIMON BOLIVAR</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>I.E. SIMON BOLIVAR SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>ón: CL 65 46 A 95</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Itaguí</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Dirección: CL 65 46 A 95</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
     </row>

--- a/nuevas_plazas.xlsx
+++ b/nuevas_plazas.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O11"/>
+  <dimension ref="A1:O17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -911,10 +911,8 @@
           <t>28/03/2026 a las 08:05</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
+      <c r="E9" t="n">
+        <v>62</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -988,10 +986,8 @@
           <t>28/03/2026 a las 08:05</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
+      <c r="E10" t="n">
+        <v>82</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1065,10 +1061,8 @@
           <t>28/03/2026 a las 08:05</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>113</t>
-        </is>
+      <c r="E11" t="n">
+        <v>113</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1120,6 +1114,420 @@
           <t>A</t>
         </is>
       </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Ciencias sociales</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Úmbita</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>28/03/2026 a las 08:01</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Marquez</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Boyacá</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>ía de Educación: Boyacá</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>I.E. SIMON BOLIVAR</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>I.E. SIMON BOLIVAR SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>ón: CL 65 46 A 95</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>Itaguí</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>Dirección: CL 65 46 A 95</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Idioma extranjero inglés</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Otanche</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>28/03/2026 a las 08:01</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Occidente</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Boyacá</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>ía de Educación: Boyacá</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>I.E. CARLOS ENRIQUE CORTES</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>I.E. CARLOS E. CORTES SEDE PRINCI</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>ón: CL 63 54 B 41</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>Itaguí</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>LA ALDEA</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Idioma extranjero inglés</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ciénega</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>28/03/2026 a las 08:01</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Marquez</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Boyacá</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>ía de Educación: Boyacá</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>I.E. LOS GOMEZ</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>I.E. LOS GOMEZ SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>ón: VDA. LOS GÓMEZ</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>Itaguí</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>Dirección: VDA. LOS GÓMEZ</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Idioma extranjero inglés</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Villa De Leyva</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>28/03/2026 a las 08:01</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Ricaurte</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Boyacá</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>ía de Educación: Boyacá</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>I.E. JUAN NEPOMUCENO CADAVID</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>I.E. JUAN NEPOMUCENO CADAVID SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>ón: KR 48 48 48</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>Itaguí</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>Dirección: KR 48 48 48</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Cargo Docente tutor (Planta Temporal PTA)</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Ciencias sociales</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Támara</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>28/03/2026 a las 08:02</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Casanare</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Casanare</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>ía de Educación: Casanare</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Educación artística - artes plásticas</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Girardot</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>28/03/2026 a las 08:03</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Girardot</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Cundinamarca</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>ía de Educación: Girardot</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/nuevas_plazas.xlsx
+++ b/nuevas_plazas.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O17"/>
+  <dimension ref="A1:O20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1136,10 +1136,8 @@
           <t>28/03/2026 a las 08:01</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
+      <c r="E12" t="n">
+        <v>69</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1213,10 +1211,8 @@
           <t>28/03/2026 a las 08:01</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
+      <c r="E13" t="n">
+        <v>16</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1290,10 +1286,8 @@
           <t>28/03/2026 a las 08:01</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
+      <c r="E14" t="n">
+        <v>21</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1367,10 +1361,8 @@
           <t>28/03/2026 a las 08:01</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
+      <c r="E15" t="n">
+        <v>29</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1444,10 +1436,8 @@
           <t>28/03/2026 a las 08:02</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
+      <c r="E16" t="n">
+        <v>43</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1497,10 +1487,8 @@
           <t>28/03/2026 a las 08:03</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
+      <c r="E17" t="n">
+        <v>19</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1529,6 +1517,237 @@
       <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr"/>
     </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Humanidades y lengua castellana</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Itaguí</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>28/03/2026 a las 08:05</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Itaguí</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>ía de Educación: Itaguí</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>I.E. CARLOS ENRIQUE CORTES</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>I.E. CARLOS E. CORTES SEDE PRINCI</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>ón: CL 63 54 B 41</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>Itaguí</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>LA ALDEA</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Itaguí</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>28/03/2026 a las 08:05</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Itaguí</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>ía de Educación: Itaguí</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>I.E. LOS GOMEZ</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>I.E. LOS GOMEZ SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>ón: VDA. LOS GÓMEZ</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>Itaguí</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>Dirección: VDA. LOS GÓMEZ</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Itaguí</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>28/03/2026 a las 08:05</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Itaguí</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>ía de Educación: Itaguí</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>I.E. JUAN NEPOMUCENO CADAVID</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>I.E. JUAN NEPOMUCENO CADAVID SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>ón: KR 48 48 48</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>Itaguí</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>Dirección: KR 48 48 48</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/nuevas_plazas.xlsx
+++ b/nuevas_plazas.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O5"/>
+  <dimension ref="A1:O8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,10 +531,8 @@
           <t>28/03/2026 a las 08:05</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
+      <c r="F2" t="n">
+        <v>67</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -608,10 +606,8 @@
           <t>28/03/2026 a las 08:05</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
+      <c r="F3" t="n">
+        <v>84</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -685,10 +681,8 @@
           <t>28/03/2026 a las 08:05</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
+      <c r="F4" t="n">
+        <v>116</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -762,10 +756,8 @@
           <t>28/03/2026 a las 08:05</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>117</t>
-        </is>
+      <c r="F5" t="n">
+        <v>117</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -808,6 +800,237 @@
         </is>
       </c>
       <c r="O5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Matemáticas</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Itaguí</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>07/04/2026 a las 16:05</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Itaguí</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>ía de Educación: Itaguí</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>I.E. LOS GOMEZ</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>I.E. LOS GOMEZ SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>Dirección: VDA. LOS GÓMEZ</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>ón: VDA. LOS GÓMEZ</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ciencias naturales y educación ambiental</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Rionegro</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>07/04/2026 a las 16:24</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Rionegro</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>ía de Educación: Rionegro</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>I.E QUEBRADA ARRIBA BALDOMERO SANIN CANO</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>I.E QUEBRADA ARRIBA BALDOMERO SANIN CANO-SEDE PPAL</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>QUEBRADA ARRIBA</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>ón: KR 57 D 52 14</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Preescolar</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Rionegro</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>07/04/2026 a las 16:27</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Rionegro</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>ía de Educación: Rionegro</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>I.E QUEBRADA ARRIBA BALDOMERO SANIN CANO</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>I.E QUEBRADA ARRIBA BALDOMERO SANIN CANO-SEDE PPAL</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>QUEBRADA ARRIBA</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>ón: KR 57 D 52 14</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
         <is>
           <t>A</t>
         </is>

--- a/nuevas_plazas.xlsx
+++ b/nuevas_plazas.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O8"/>
+  <dimension ref="A1:O9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -831,10 +831,8 @@
           <t>07/04/2026 a las 16:05</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
+      <c r="F6" t="n">
+        <v>11</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -908,10 +906,8 @@
           <t>07/04/2026 a las 16:24</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="F7" t="n">
+        <v>6</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -985,10 +981,8 @@
           <t>07/04/2026 a las 16:27</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="F8" t="n">
+        <v>4</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -1031,6 +1025,83 @@
         </is>
       </c>
       <c r="O8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ciencias naturales y educación ambiental</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Rionegro</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>11/04/2026 a las 15:50</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Rionegro</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>ía de Educación: Rionegro</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>I.E QUEBRADA ARRIBA BALDOMERO SANIN CANO</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>I.E QUEBRADA ARRIBA BALDOMERO SANIN CANO-SEDE PPAL</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>QUEBRADA ARRIBA</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>ón: KR 57 D 52 14</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
         <is>
           <t>A</t>
         </is>

--- a/nuevas_plazas.xlsx
+++ b/nuevas_plazas.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O9"/>
+  <dimension ref="A1:O16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1056,10 +1056,8 @@
           <t>11/04/2026 a las 15:50</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
+      <c r="F9" t="n">
+        <v>16</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -1102,6 +1100,545 @@
         </is>
       </c>
       <c r="O9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ciencias naturales química</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>16/04/2026 a las 10:52</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>ía de Educación: Medellín</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>I.E. JUAN MARIA CESPEDES</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>I.E. JUAN MARIA CESPEDES - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>Dirección: CLL 32B NO 76A-48</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>ón: CLL 32B NO 76A-48</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Priorizadas para jóvenes entre 18 y 28 años</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Matemáticas</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>16/04/2026 a las 10:52</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>ía de Educación: Medellín</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>I.E. JUAN MARIA CESPEDES</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>I.E. JUAN MARIA CESPEDES - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Dirección: CLL 32B NO 76A-48</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>ón: CLL 32B NO 76A-48</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ciencias naturales física</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>16/04/2026 a las 10:52</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>ía de Educación: Medellín</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>I.E. JUAN MARIA CESPEDES</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>I.E. JUAN MARIA CESPEDES - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>Dirección: CLL 32B NO 76A-48</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>ón: CLL 32B NO 76A-48</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Humanidades y lengua castellana</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>16/04/2026 a las 10:52</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>ía de Educación: Medellín</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>I.E. JUAN MARIA CESPEDES</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>I.E. JUAN MARIA CESPEDES - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>Dirección: CLL 32B NO 76A-48</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>ón: CLL 32B NO 76A-48</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Filosofía</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>16/04/2026 a las 10:52</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>ía de Educación: Medellín</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>I.E. JUAN MARIA CESPEDES</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>I.E. JUAN MARIA CESPEDES - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>Dirección: CLL 32B NO 76A-48</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>ón: CLL 32B NO 76A-48</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Matemáticas</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>16/04/2026 a las 10:52</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>ía de Educación: Medellín</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>I.E. SAN ROBERTO BELARMINO</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>I.E. SAN ROBERTO BELARMINO - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>LAS MERCEDES</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>ón: CL 32 B 83 39</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Educación ética y en valores</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>16/04/2026 a las 10:52</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>ía de Educación: Medellín</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>I.E. SAN ROBERTO BELARMINO</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>I.E. SAN ROBERTO BELARMINO - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>LAS MERCEDES</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>ón: CL 32 B 83 39</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
         <is>
           <t>A</t>
         </is>

--- a/nuevas_plazas.xlsx
+++ b/nuevas_plazas.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O16"/>
+  <dimension ref="A1:O34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1131,10 +1131,8 @@
           <t>16/04/2026 a las 10:52</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F10" t="n">
+        <v>0</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -1208,10 +1206,8 @@
           <t>16/04/2026 a las 10:52</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="F11" t="n">
+        <v>1</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -1285,10 +1281,8 @@
           <t>16/04/2026 a las 10:52</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F12" t="n">
+        <v>0</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -1362,10 +1356,8 @@
           <t>16/04/2026 a las 10:52</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="F13" t="n">
+        <v>4</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -1439,10 +1431,8 @@
           <t>16/04/2026 a las 10:52</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="F14" t="n">
+        <v>2</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -1516,10 +1506,8 @@
           <t>16/04/2026 a las 10:52</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="F15" t="n">
+        <v>1</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -1593,10 +1581,8 @@
           <t>16/04/2026 a las 10:52</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="F16" t="n">
+        <v>3</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1639,6 +1625,1392 @@
         </is>
       </c>
       <c r="O16" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Priorizadas para jóvenes entre 18 y 28 años</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ciencias naturales y educación ambiental</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>San Pedro De Urabá</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>16/04/2026 a las 15:11</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>San Pedro de Urabá</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>I. E. R. SANTA CATALINA</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>COLEGIO SANTA CATALINA - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>CORREG. SANTA CATALINA</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>ón: CORREG. SANTA CATALINA.</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Humanidades y lengua castellana</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Segovia</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>16/04/2026 a las 15:11</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Segovia</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>I. E. SANTO DOMINGO SAVIO</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>SANTA LAURA</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>Dirección: VDA SANTA LAURA</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>ón: VDA SANTA LAURA</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Humanidades y lengua castellana</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Sonsón</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>16/04/2026 a las 15:11</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Sonsón</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>I. E. TECNICO AGROPECUARIO Y EN SALUD DE SONSÂ¿N</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>C. E. R. ARENILLAL</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>VDA. ARENILLAL</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>ón: VDA ARENILLAL</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Preescolar</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Tarazá</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>16/04/2026 a las 15:11</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Tarazá</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>I. E. RAFAEL NUNEZ</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>E U ANGEL AMABLE ARROYAVE</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>Dirección: KR 31 30 46</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>ón: KR 31 30 46</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Idioma extranjero inglés</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Tarazá</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>16/04/2026 a las 15:11</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Tarazá</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>I. E. ANTONIO ROLDAN BETANCUR</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>COLEGIO ANTONIO ROLDAN BETANCUR - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>BARRIO. GARZON</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>ón: KR 36 32 114</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Ciencias sociales</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Tarso</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>16/04/2026 a las 15:12</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Suroeste</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>I. E. JOSE PRIETO ARANGO</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>LICEO JOSE PRIETO ARANGO - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>LA CANCHA</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>ón: CL 18 27 77</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Ciencias naturales y educación ambiental</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Toledo</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>16/04/2026 a las 15:12</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Toledo</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>C. E. R. LA LINDA</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>C. E. R. LA LINDA - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>VDA. LA LINDA</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>ón: VDA. LA LINDA</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Urrao</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>16/04/2026 a las 15:12</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Urrao</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>I. E. R. JAIPERA</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>I. E. R. JAIPERA - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>VDA. JAIPERA</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>ón: CALLE 39 25-14</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Humanidades y lengua castellana</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Valdivia</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>16/04/2026 a las 15:12</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Valdivia</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>C. E. R. LA PAULINA</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>C. E. R. LOS NUTABES</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>VDA. EL QUINCE</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>ón: VDA. EL QUINCE</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Educación artística – música</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Vegachí</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>16/04/2026 a las 15:12</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Vegachí</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>I. E. EFE GOMEZ</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>LICEO EFE GOMEZ - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>CABECEERA MPAL</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>ón: KR 47 50 40</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Educación física, recreación y deporte</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Yalí</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>16/04/2026 a las 15:12</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Yalí</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>I. E. LORENZO YALI</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>C. E. R. CASAMORA</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>VDA CASAMORA</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>ón: VDA CASAMORA</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Yolombó</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>16/04/2026 a las 15:12</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Yolombó</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>I. E. R. LA FLORESTA</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>COLEGIO LA FLORESTA - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>CORREG. LA FLORESTA</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>ón: CORREG. LA FLORESTA</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Yondó</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>16/04/2026 a las 15:12</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Yondó</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>I. E. LUIS EDUARDO DIAZ</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>LA PATRIA</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>Dirección: KR 49 47 31 &lt;EOF&gt;</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>ón: KR 49 47 31 &lt;EOF&gt;</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Humanidades y lengua castellana</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Yondó</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>16/04/2026 a las 15:12</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Yondó</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>C. E. R. LA PRIMAVERA</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>C. E. R. EL BAGRE</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>VDA. EL BAGRE</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>ón: VDA EL BAGRE</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Yondó</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>16/04/2026 a las 15:12</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Yondó</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>C. E. R. CAÂ¿O BLANCO</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>C. E. R. LA UNION</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>VDA. LA UNIÓN</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>ón: VDA LA UNIÓN</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Yondó</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>16/04/2026 a las 15:12</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Yondó</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>C. E. R. LA PRIMAVERA</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>C. E. R. ONCE DE NOVIEMBRE</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>VDA. X-10</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>ón: VDA X-10</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Idioma extranjero inglés</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Yondó</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>16/04/2026 a las 15:12</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Yondó</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>C. E. R. CAÂ¿O BLANCO</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>C. E. R. EL REMOLINO</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>VDA. PEÑAS BLANCAS</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>ón: VDA PEÑAS BLANCAS</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Educación ética y en valores</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Zaragoza</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>16/04/2026 a las 15:12</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Zaragoza</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>I. E. LUIS FERNANDO RESTREPO RESTREPO</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>I. E. LUIS FERNANDO RESTREPO RESTREPO - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>BR. LAS BRISAS</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>ón: IND BR. LAS BRISAS</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
         <is>
           <t>A</t>
         </is>

--- a/nuevas_plazas.xlsx
+++ b/nuevas_plazas.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O34"/>
+  <dimension ref="A1:O41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1656,10 +1656,8 @@
           <t>16/04/2026 a las 15:11</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F17" t="n">
+        <v>0</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1733,10 +1731,8 @@
           <t>16/04/2026 a las 15:11</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F18" t="n">
+        <v>0</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1810,10 +1806,8 @@
           <t>16/04/2026 a las 15:11</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F19" t="n">
+        <v>0</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1887,10 +1881,8 @@
           <t>16/04/2026 a las 15:11</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F20" t="n">
+        <v>0</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1964,10 +1956,8 @@
           <t>16/04/2026 a las 15:11</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F21" t="n">
+        <v>0</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -2041,10 +2031,8 @@
           <t>16/04/2026 a las 15:12</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F22" t="n">
+        <v>0</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -2118,10 +2106,8 @@
           <t>16/04/2026 a las 15:12</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F23" t="n">
+        <v>0</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -2195,10 +2181,8 @@
           <t>16/04/2026 a las 15:12</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="F24" t="n">
+        <v>1</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -2272,10 +2256,8 @@
           <t>16/04/2026 a las 15:12</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F25" t="n">
+        <v>0</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -2349,10 +2331,8 @@
           <t>16/04/2026 a las 15:12</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F26" t="n">
+        <v>0</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -2426,10 +2406,8 @@
           <t>16/04/2026 a las 15:12</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F27" t="n">
+        <v>0</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -2503,10 +2481,8 @@
           <t>16/04/2026 a las 15:12</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F28" t="n">
+        <v>0</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -2580,10 +2556,8 @@
           <t>16/04/2026 a las 15:12</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F29" t="n">
+        <v>0</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -2657,10 +2631,8 @@
           <t>16/04/2026 a las 15:12</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F30" t="n">
+        <v>0</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -2734,10 +2706,8 @@
           <t>16/04/2026 a las 15:12</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F31" t="n">
+        <v>0</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -2811,10 +2781,8 @@
           <t>16/04/2026 a las 15:12</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F32" t="n">
+        <v>0</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -2888,10 +2856,8 @@
           <t>16/04/2026 a las 15:12</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F33" t="n">
+        <v>0</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -2965,10 +2931,8 @@
           <t>16/04/2026 a las 15:12</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F34" t="n">
+        <v>0</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -3011,6 +2975,545 @@
         </is>
       </c>
       <c r="O34" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Ciencias sociales</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Sopetrán</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>16/04/2026 a las 15:11</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Occidente</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>I. E. JOSE MARIA VILLA</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>COLEGIO JOSE MARIA VILLA - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>AREA URBANA</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>ón: CL 9 10 52</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Ciencias naturales y educación ambiental</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Yondó</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>16/04/2026 a las 15:12</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Yondó</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>I. E. LUIS EDUARDO DIAZ</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>I. E. LUIS EDUARDO DIAZ - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>BARRIO. EL PROGRESO</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>ón: KR 45 50 52</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Priorizadas para jóvenes entre 18 y 28 años</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Idioma extranjero inglés</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Zaragoza</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>16/04/2026 a las 15:12</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Zaragoza</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>I. E. SANTO CRISTO DE ZARAGOZA</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>LICEO SANTO CRISTO DE ZARAGOZA - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>SANTA ELENA</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>ón: CLL 39B 37 10</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Priorizadas para jóvenes entre 18 y 28 años</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Preescolar</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Remedios</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>16/04/2026 a las 15:12</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Remedios</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>I.E. IGNACIO YEPES YEPES</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>E U REMEDIOS</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>ALTO DE LAS TAPIAS</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>ón: CQ 8 15 149</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Cargo Docente Orientador</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Sin asignación directa</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Cáceres</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>16/04/2026 a las 15:12</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Cáceres</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>I. E. R. EL TIGRE</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>I. E. R. EL TIGRE - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>VDA. EL TIGRE</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>ón: VDA. EL TIGRE KM 26</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Cargo Docente Orientador</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Sin asignación directa</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Nechí</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>16/04/2026 a las 15:12</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Nechí</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>I. E. JORGE ELIECER GAITAN</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>COLEGIO JORGE ELIECER GAITAN - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>CORREG. CARGUEROS</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>ón: CORREG. CARGUEROS</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Matemáticas</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Dabeiba</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>16/04/2026 a las 15:12</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Dabeiba</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>I. E. R. URAMA</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>C. E. R. LA BALSITA</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>VDA. LA BALSITA</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>ón: VDA LA BALSITA</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
         <is>
           <t>A</t>
         </is>

--- a/nuevas_plazas.xlsx
+++ b/nuevas_plazas.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O41"/>
+  <dimension ref="A1:O43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3006,10 +3006,8 @@
           <t>16/04/2026 a las 15:11</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
+      <c r="F35" t="n">
+        <v>14</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -3083,10 +3081,8 @@
           <t>16/04/2026 a las 15:12</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
+      <c r="F36" t="n">
+        <v>7</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -3160,10 +3156,8 @@
           <t>16/04/2026 a las 15:12</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="F37" t="n">
+        <v>1</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -3237,10 +3231,8 @@
           <t>16/04/2026 a las 15:12</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
+      <c r="F38" t="n">
+        <v>11</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -3314,10 +3306,8 @@
           <t>16/04/2026 a las 15:12</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
+      <c r="F39" t="n">
+        <v>10</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -3391,10 +3381,8 @@
           <t>16/04/2026 a las 15:12</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
+      <c r="F40" t="n">
+        <v>9</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -3468,10 +3456,8 @@
           <t>16/04/2026 a las 15:12</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
+      <c r="F41" t="n">
+        <v>7</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -3514,6 +3500,160 @@
         </is>
       </c>
       <c r="O41" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Tecnología e informática</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Itaguí</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>16/04/2026 a las 16:39</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Itaguí</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>ía de Educación: Itaguí</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>INSTITUCION EDUCATIVA SIMON BOLIVAR</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>INSTITUCION EDUCATIVA SIMON BOLIVAR SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>Dirección: CL 65 46 A 95</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>ón: CL 65 46 A 95</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Preescolar</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Itaguí</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>16/04/2026 a las 16:39</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Itaguí</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>ía de Educación: Itaguí</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>I.E. CIUDAD ITAGUI</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>I.E. CIUDAD ITAGUI SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>Dirección: KR 55 A 61 21</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>ón: KR 55 A 61 21</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
         <is>
           <t>A</t>
         </is>

--- a/nuevas_plazas.xlsx
+++ b/nuevas_plazas.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O43"/>
+  <dimension ref="A1:O45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3531,10 +3531,8 @@
           <t>16/04/2026 a las 16:39</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
+      <c r="F42" t="n">
+        <v>13</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -3608,10 +3606,8 @@
           <t>16/04/2026 a las 16:39</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
+      <c r="F43" t="n">
+        <v>19</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -3654,6 +3650,160 @@
         </is>
       </c>
       <c r="O43" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Ciencias naturales y educación ambiental</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Itaguí</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>17/04/2026 a las 13:11</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Itaguí</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>ía de Educación: Itaguí</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>I.E. ENRIQUE VELEZ ESCOBAR</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>I.E. ENRIQUE VELEZ SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>Dirección: CRA 52 C #72-69</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>ón: CRA 52 C #72-69</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Educación ética y en valores</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Itaguí</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>17/04/2026 a las 13:11</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Itaguí</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>ía de Educación: Itaguí</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>I.E. ENRIQUE VELEZ ESCOBAR</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>I.E. ENRIQUE VELEZ SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>Dirección: CRA 52 C #72-69</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>ón: CRA 52 C #72-69</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
         <is>
           <t>A</t>
         </is>

--- a/nuevas_plazas.xlsx
+++ b/nuevas_plazas.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O45"/>
+  <dimension ref="A1:O46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3681,10 +3681,8 @@
           <t>17/04/2026 a las 13:11</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
+      <c r="F44" t="n">
+        <v>18</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -3758,10 +3756,8 @@
           <t>17/04/2026 a las 13:11</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
+      <c r="F45" t="n">
+        <v>11</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -3804,6 +3800,83 @@
         </is>
       </c>
       <c r="O45" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Educación física, recreación y deporte</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Rionegro</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>18/04/2026 a las 08:27</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Rionegro</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>ía de Educación: Rionegro</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>I.E QUEBRADA ARRIBA BALDOMERO SANIN CANO</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>I.E QUEBRADA ARRIBA BALDOMERO SANIN CANO-SEDE PPAL</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>QUEBRADA ARRIBA</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>ón: KR 57 D 52 14</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
         <is>
           <t>A</t>
         </is>

--- a/nuevas_plazas.xlsx
+++ b/nuevas_plazas.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O46"/>
+  <dimension ref="A1:O47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3831,10 +3831,8 @@
           <t>18/04/2026 a las 08:27</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
+      <c r="F46" t="n">
+        <v>28</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -3877,6 +3875,83 @@
         </is>
       </c>
       <c r="O46" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Educación física, recreación y deporte</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Rionegro</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>22/04/2026 a las 08:18</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Rionegro</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>ía de Educación: Rionegro</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>I.E QUEBRADA ARRIBA BALDOMERO SANIN CANO</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>I.E QUEBRADA ARRIBA BALDOMERO SANIN CANO-SEDE PPAL</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>QUEBRADA ARRIBA</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>ón: KR 57 D 52 14</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
         <is>
           <t>A</t>
         </is>

--- a/nuevas_plazas.xlsx
+++ b/nuevas_plazas.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O47"/>
+  <dimension ref="A1:O49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3906,10 +3906,8 @@
           <t>22/04/2026 a las 08:18</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
+      <c r="F47" t="n">
+        <v>36</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -3952,6 +3950,160 @@
         </is>
       </c>
       <c r="O47" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Humanidades y lengua castellana</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Valdivia</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>23/04/2026 a las 10:42</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Valdivia</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>C. E. R. LA PAULINA</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>C. E. R. LOS NUTABES</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>VDA. EL QUINCE</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>ón: VDA. EL QUINCE</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Educación física, recreación y deporte</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Yalí</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>23/04/2026 a las 10:44</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Yalí</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>I. E. LORENZO YALI</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>C. E. R. CASAMORA</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>VDA CASAMORA</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>ón: VDA CASAMORA</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
         <is>
           <t>A</t>
         </is>

--- a/nuevas_plazas.xlsx
+++ b/nuevas_plazas.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O49"/>
+  <dimension ref="A1:O51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3981,10 +3981,8 @@
           <t>23/04/2026 a las 10:42</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
+      <c r="F48" t="n">
+        <v>15</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -4058,10 +4056,8 @@
           <t>23/04/2026 a las 10:44</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
+      <c r="F49" t="n">
+        <v>41</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -4104,6 +4100,160 @@
         </is>
       </c>
       <c r="O49" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Matemáticas</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Cocorná</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>23/04/2026 a las 14:55</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Cocorná</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>I. E. COCORNA</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>LICEO COCORNA - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>B. COCORNÁ</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>ón: CL 23 23 27</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Tecnología e informática</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Cocorná</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>23/04/2026 a las 14:55</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Cocorná</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>I. E. EVA TULIA QUINTERO DE TORO</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>I. E. EVA TULIA QUINTERO DE TORO - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>VDA. LA PIÑUELA</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>ón: VDA. LA PIÑUELA</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
         <is>
           <t>A</t>
         </is>

--- a/nuevas_plazas.xlsx
+++ b/nuevas_plazas.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O51"/>
+  <dimension ref="A1:O79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4131,10 +4131,8 @@
           <t>23/04/2026 a las 14:55</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="F50" t="n">
+        <v>1</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -4208,10 +4206,8 @@
           <t>23/04/2026 a las 14:55</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="F51" t="n">
+        <v>1</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -4254,6 +4250,2162 @@
         </is>
       </c>
       <c r="O51" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Tecnología e informática</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Concordia</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>23/04/2026 a las 14:55</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Suroeste</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>I. E. DE JESUS</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>I. E. DE JESUS - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>KR 22 19 65</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>ón: KR 22 19 65</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Matemáticas</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Dabeiba</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>23/04/2026 a las 14:55</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Dabeiba</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>I. E. R. URAMA</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>C. E. R. MONTEBELLO</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>VDA. MONTEBELLO</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>ón: VDA MONTEBELLO</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Educación física, recreación y deporte</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>El Bagre</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>23/04/2026 a las 14:55</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>El Bagre</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>I. E. R. PUERTO CLAVER</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>LICEO PUERTO CLAVER - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>B. SAN CARLOS</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>ón: CORREG.PUERTO CLAVER</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Educación física, recreación y deporte</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>El Bagre</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>23/04/2026 a las 14:55</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>El Bagre</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>I. E. R. PUERTO LOPEZ</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>COLEGIO PUERTO LOPEZ - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>CORREGIMIENTO PUERTO LOPEZ</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>ón: CORREG. PUERTO LOPEZ</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>El Bagre</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>23/04/2026 a las 14:55</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>El Bagre</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>I. E. R. PUERTO CLAVER</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>E U PUERTO CLAVER</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>B. PLAN BONITO 1</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>ón: IND CORREG.PUERTO CLAVER</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>El Bagre</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>23/04/2026 a las 14:55</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>El Bagre</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>I. E. LAS DELICIAS</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>COLEGIO LAS DELICIAS - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>BARRIO LAS DELICIAS</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>ón: CL 66 47 101</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>El Carmen De Viboral</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>23/04/2026 a las 14:55</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Oriente</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>I. E. CAMPESTRE NUEVO HORIZONTE</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>CENTRO EDUCATIVO RURAL EL BRASIL</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>Dirección: VDA EL BRASIL</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>ón: VDA EL BRASIL</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Educación física, recreación y deporte</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Girardotá</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>23/04/2026 a las 14:55</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Valle del Aburrá</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>I. E. COLOMBIA</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>I. E. COLOMBIA - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>CL 5 A 14 A 62</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>ón: CL 5 A 14 A 62</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Preescolar</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Heliconia</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>23/04/2026 a las 14:55</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Occidente</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>I. E. SAN RAFAEL</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>E U CRISTO REY</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>Dirección: KR 19 21 114</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>ón: KR 19 21 114</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Preescolar</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Ituango</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>23/04/2026 a las 14:55</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Ituango</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>I. E. PEDRO NEL OSPINA</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>E U ANTONIO J ARAQUE</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>CENTRO</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>ón: IND KL MADRID # 19</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Humanidades y lengua castellana</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Ituango</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>23/04/2026 a las 14:55</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Ituango</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>I. E. R. LA PEREZ</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>I. E. R. EL CEDRAL</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>VDA. EL CEDRAL</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>ón: VDA. EL CEDRAL</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Ituango</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>23/04/2026 a las 14:55</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Ituango</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>I. E. LUIS MARIA PRECIADO ECHAVARRIA</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>I. E. LUIS MARIA PRECIADO ECHAVARRIA - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>Dirección: CORREG. SANTA RITA</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>ón: CORREG. SANTA RITA</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Ciencias naturales química</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Maceo</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>23/04/2026 a las 14:55</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Maceo</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>I. E. R. LA FLORESTA</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>I. E. R. LA FLORESTA - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>CORREG.LA FLORESTA</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>ón: CORREG.LA FLORESTA</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Idioma extranjero inglés</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Maceo</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>23/04/2026 a las 14:56</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Maceo</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>I. E. FILIBERTO RESTREPO SIERRA</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>LICEO MANUELA BELTRAN - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>CABECERA MPAL.</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>ón: CL. 30 25-35</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Nariño</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>23/04/2026 a las 14:56</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Nariño</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>I. E. PUERTO VENUS</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>C. E. R. EL ZAFIRO</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>VDA EL ZAFIRO</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>ón: VDA. EL ZAFIRO</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Priorizadas para jóvenes entre 18 y 28 años</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Matemáticas</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Nariño</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>23/04/2026 a las 14:56</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Nariño</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>C. E. R. EL CARMELO</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>C. E. R. DAMAS</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>VDA. DAMAS</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>ón: VDA. DAMAS</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Matemáticas</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Nechí</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>23/04/2026 a las 14:56</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Nechí</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>I.E.R TRINIDAD ARRIBA</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>C. E. R. TRINIDAD ABAJO</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>Dirección: VDA TRINIDAD ABAJO</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>ón: VDA TRINIDAD ABAJO</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Priorizadas para jóvenes entre 18 y 28 años</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Nechí</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>23/04/2026 a las 14:56</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Nechí</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>I. E. NECHI</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>E U NECHI</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>CL. LA MISERICORDIA</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>ón: CL. LA MISERICORDIA</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Ciencias sociales</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Necoclí</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>23/04/2026 a las 14:56</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Necoclí</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>I. E. R. TULAPITA</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>I. E. R. TULAPITA - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>VDA. TULAPITA</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>ón: VDA. TULAPITA</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Educación física, recreación y deporte</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Necoclí</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>23/04/2026 a las 14:56</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Necoclí</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>I. E. R. PUEBLO NUEVO</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>COLEGIO PUEBLO NUEVO - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>CORREG.PUEBLO NUEVO</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>ón: CORREG. PUEBLO NUEVO</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Necoclí</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>23/04/2026 a las 14:56</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Necoclí</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>I. E. R. TULAPITA</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>E R I LA CENIZOSA</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>VDA. LA CENIZOSA</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>ón: VDA. LA CENIZOSA</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Priorizadas para jóvenes entre 18 y 28 años</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Puerto Triunfo</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>23/04/2026 a las 14:56</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Puerto Triunfo</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>I. E. R. HERMANO DANIEL</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>I. E. R. HERMANO DANIEL - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>CORREG.LAS MERCEDES</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>ón: CORREG.LAS MERCEDES</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Puerto Triunfo</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>23/04/2026 a las 14:56</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Puerto Triunfo</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>I. E. PABLO VI</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>I. E. PABLO VI - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>AV. LA ESTACIÓN</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>ón: CL 14 12 58 &lt;EOF&gt;</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Ciencias sociales</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>San Jerónimo</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>23/04/2026 a las 14:56</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Occidente</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>I. E. ESCUELA NORMAL SUPERIOR GENOVEVA DIAZ</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>I. E. ESCUELA NORMAL SUPERIOR GENOVEVA DIAZ - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>Dirección: KR 11 20 15</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>ón: KR 11 20 15</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Educación artística – música</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>San Juan De Urabá</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>23/04/2026 a las 14:56</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>San Juan de Urabá</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>I. E. R. EL FILO DE DAMAQUIEL</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>I. E. R. EL FILO DE DAMAQUIEL - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>VDA FILO DAMAQUIEL</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>ón: VDA FILO DAMAQUIEL</t>
+        </is>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Matemáticas</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>San Juan De Urabá</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>23/04/2026 a las 14:56</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>San Juan de Urabá</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>C. E. R. SAN JUAN ORIENTAL</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>C. E. R. SAN JUAN ORIENTAL - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>VDA. SAN JUAN ORIENTAL</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>ón: VDA. SAN JUAN ORIENTAL</t>
+        </is>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Matemáticas</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>San Luis</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>23/04/2026 a las 14:56</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>San Luis</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>I. E. SAN LUIS</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>E U MADRE LAURA</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>ZONA URBANA</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>ón: KR 22 21 56</t>
+        </is>
+      </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>San Luis</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>23/04/2026 a las 14:56</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>San Luis</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>I. E. R. LA JOSEFINA</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>C.E.R SAN PABLO</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>Dirección: VDA. SAN PABLO</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>ón: VDA. SAN PABLO</t>
+        </is>
+      </c>
+      <c r="O79" t="inlineStr">
         <is>
           <t>A</t>
         </is>

--- a/nuevas_plazas.xlsx
+++ b/nuevas_plazas.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O79"/>
+  <dimension ref="A1:O80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4281,10 +4281,8 @@
           <t>23/04/2026 a las 14:55</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="F52" t="n">
+        <v>5</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -4358,10 +4356,8 @@
           <t>23/04/2026 a las 14:55</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="F53" t="n">
+        <v>5</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -4435,10 +4431,8 @@
           <t>23/04/2026 a las 14:55</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="F54" t="n">
+        <v>4</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -4512,10 +4506,8 @@
           <t>23/04/2026 a las 14:55</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="F55" t="n">
+        <v>3</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -4589,10 +4581,8 @@
           <t>23/04/2026 a las 14:55</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="F56" t="n">
+        <v>8</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
@@ -4666,10 +4656,8 @@
           <t>23/04/2026 a las 14:55</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
+      <c r="F57" t="n">
+        <v>7</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -4743,10 +4731,8 @@
           <t>23/04/2026 a las 14:55</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
+      <c r="F58" t="n">
+        <v>13</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -4820,10 +4806,8 @@
           <t>23/04/2026 a las 14:55</t>
         </is>
       </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="F59" t="n">
+        <v>6</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -4897,10 +4881,8 @@
           <t>23/04/2026 a las 14:55</t>
         </is>
       </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
+      <c r="F60" t="n">
+        <v>11</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
@@ -4974,10 +4956,8 @@
           <t>23/04/2026 a las 14:55</t>
         </is>
       </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
+      <c r="F61" t="n">
+        <v>9</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
@@ -5051,10 +5031,8 @@
           <t>23/04/2026 a las 14:55</t>
         </is>
       </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
+      <c r="F62" t="n">
+        <v>13</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
@@ -5128,10 +5106,8 @@
           <t>23/04/2026 a las 14:55</t>
         </is>
       </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
+      <c r="F63" t="n">
+        <v>9</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
@@ -5205,10 +5181,8 @@
           <t>23/04/2026 a las 14:55</t>
         </is>
       </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="F64" t="n">
+        <v>5</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
@@ -5282,10 +5256,8 @@
           <t>23/04/2026 a las 14:56</t>
         </is>
       </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="F65" t="n">
+        <v>6</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
@@ -5359,10 +5331,8 @@
           <t>23/04/2026 a las 14:56</t>
         </is>
       </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="F66" t="n">
+        <v>8</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
@@ -5436,10 +5406,8 @@
           <t>23/04/2026 a las 14:56</t>
         </is>
       </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="F67" t="n">
+        <v>6</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
@@ -5513,10 +5481,8 @@
           <t>23/04/2026 a las 14:56</t>
         </is>
       </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="F68" t="n">
+        <v>5</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
@@ -5590,10 +5556,8 @@
           <t>23/04/2026 a las 14:56</t>
         </is>
       </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
+      <c r="F69" t="n">
+        <v>9</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
@@ -5667,10 +5631,8 @@
           <t>23/04/2026 a las 14:56</t>
         </is>
       </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
+      <c r="F70" t="n">
+        <v>15</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
@@ -5744,10 +5706,8 @@
           <t>23/04/2026 a las 14:56</t>
         </is>
       </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="F71" t="n">
+        <v>6</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
@@ -5821,10 +5781,8 @@
           <t>23/04/2026 a las 14:56</t>
         </is>
       </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
+      <c r="F72" t="n">
+        <v>13</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
@@ -5898,10 +5856,8 @@
           <t>23/04/2026 a las 14:56</t>
         </is>
       </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
+      <c r="F73" t="n">
+        <v>11</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
@@ -5975,10 +5931,8 @@
           <t>23/04/2026 a las 14:56</t>
         </is>
       </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
+      <c r="F74" t="n">
+        <v>10</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
@@ -6052,10 +6006,8 @@
           <t>23/04/2026 a las 14:56</t>
         </is>
       </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
+      <c r="F75" t="n">
+        <v>14</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
@@ -6129,10 +6081,8 @@
           <t>23/04/2026 a las 14:56</t>
         </is>
       </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="F76" t="n">
+        <v>3</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
@@ -6206,10 +6156,8 @@
           <t>23/04/2026 a las 14:56</t>
         </is>
       </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="F77" t="n">
+        <v>4</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
@@ -6283,10 +6231,8 @@
           <t>23/04/2026 a las 14:56</t>
         </is>
       </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="F78" t="n">
+        <v>4</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
@@ -6360,10 +6306,8 @@
           <t>23/04/2026 a las 14:56</t>
         </is>
       </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
+      <c r="F79" t="n">
+        <v>13</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
@@ -6406,6 +6350,83 @@
         </is>
       </c>
       <c r="O79" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Educación física, recreación y deporte</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Rionegro</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>24/04/2026 a las 07:36</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>139</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Rionegro</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>ía de Educación: Rionegro</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>I.E QUEBRADA ARRIBA BALDOMERO SANIN CANO</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>I.E QUEBRADA ARRIBA BALDOMERO SANIN CANO-SEDE PPAL</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>QUEBRADA ARRIBA</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>ón: KR 57 D 52 14</t>
+        </is>
+      </c>
+      <c r="O80" t="inlineStr">
         <is>
           <t>A</t>
         </is>

--- a/nuevas_plazas.xlsx
+++ b/nuevas_plazas.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O80"/>
+  <dimension ref="A1:O81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6381,10 +6381,8 @@
           <t>24/04/2026 a las 07:36</t>
         </is>
       </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>139</t>
-        </is>
+      <c r="F80" t="n">
+        <v>139</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
@@ -6427,6 +6425,83 @@
         </is>
       </c>
       <c r="O80" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Idioma extranjero inglés</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Rionegro</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>25/04/2026 a las 14:26</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Rionegro</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>ía de Educación: Rionegro</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>I. E. JOSE MARIA CORDOBA</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>I. E. LICEO JOSE MARIA CORDOBA - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>ALTOS DE LA PEREIRA</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>ón: CR 52 40-86</t>
+        </is>
+      </c>
+      <c r="O81" t="inlineStr">
         <is>
           <t>A</t>
         </is>

--- a/nuevas_plazas.xlsx
+++ b/nuevas_plazas.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O81"/>
+  <dimension ref="A1:O85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6456,10 +6456,8 @@
           <t>25/04/2026 a las 14:26</t>
         </is>
       </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F81" t="n">
+        <v>0</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
@@ -6502,6 +6500,314 @@
         </is>
       </c>
       <c r="O81" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Itaguí</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>25/04/2026 a las 14:29</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Itaguí</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>ía de Educación: Itaguí</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>I.E. AVELINO SALDARRIAGA</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>I.E. AVELINO SALDARRIAGA SEDE PRI</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>LA INDEPENDENCIA</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>ón: CL 39 49 77</t>
+        </is>
+      </c>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Ciencias sociales</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Itaguí</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>25/04/2026 a las 14:29</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Itaguí</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>ía de Educación: Itaguí</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>I.E. AVELINO SALDARRIAGA</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>I.E. AVELINO SALDARRIAGA SEDE PRI</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>LA INDEPENDENCIA</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>ón: CL 39 49 77</t>
+        </is>
+      </c>
+      <c r="O83" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Educación física, recreación y deporte</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Itaguí</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>25/04/2026 a las 14:29</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Itaguí</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>ía de Educación: Itaguí</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>I.E. AVELINO SALDARRIAGA</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>I.E. AVELINO SALDARRIAGA SEDE PRI</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>LA INDEPENDENCIA</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>ón: CL 39 49 77</t>
+        </is>
+      </c>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Educación artística – danzas</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Itaguí</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>25/04/2026 a las 14:29</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Itaguí</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>ía de Educación: Itaguí</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>I.E. AVELINO SALDARRIAGA</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>I.E. AVELINO SALDARRIAGA SEDE PRI</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>LA INDEPENDENCIA</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>ón: CL 39 49 77</t>
+        </is>
+      </c>
+      <c r="O85" t="inlineStr">
         <is>
           <t>A</t>
         </is>

--- a/nuevas_plazas.xlsx
+++ b/nuevas_plazas.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O85"/>
+  <dimension ref="A1:O97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6531,10 +6531,8 @@
           <t>25/04/2026 a las 14:29</t>
         </is>
       </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
+      <c r="F82" t="n">
+        <v>21</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
@@ -6608,10 +6606,8 @@
           <t>25/04/2026 a las 14:29</t>
         </is>
       </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
+      <c r="F83" t="n">
+        <v>23</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
@@ -6685,10 +6681,8 @@
           <t>25/04/2026 a las 14:29</t>
         </is>
       </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
+      <c r="F84" t="n">
+        <v>13</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
@@ -6762,52 +6756,974 @@
           <t>25/04/2026 a las 14:29</t>
         </is>
       </c>
-      <c r="F85" t="inlineStr">
+      <c r="F85" t="n">
+        <v>1</v>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Itaguí</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>ía de Educación: Itaguí</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>I.E. AVELINO SALDARRIAGA</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>I.E. AVELINO SALDARRIAGA SEDE PRI</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>LA INDEPENDENCIA</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>ón: CL 39 49 77</t>
+        </is>
+      </c>
+      <c r="O85" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Matemáticas</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Bello</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>25/04/2026 a las 15:41</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Bello</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>ía de Educación: Bello</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>I.E. Jorge Eliecer Gaitan</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>Liceo Nocturno Jorge Eliecer Gaitan Ayala - Sede P</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>Dirección: CRA 50 NO 53-04</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>ón: CRA 50 NO 53-04</t>
+        </is>
+      </c>
+      <c r="O86" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Matemáticas</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Bello</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>25/04/2026 a las 15:41</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Bello</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>ía de Educación: Bello</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>I.E. Tomas Cadavid Restrepo</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>Colegio Tomas Cadavid - Sede Principal</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>Dirección: CRA 55 N0 38-170</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>ón: CRA 55 N0 38-170</t>
+        </is>
+      </c>
+      <c r="O87" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Matemáticas</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Bello</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>25/04/2026 a las 15:41</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Bello</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>ía de Educación: Bello</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>I.E. Betsabe Espinal</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>Betsabe Espinal - Sede Principal</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>Dirección: AV 33 59 53</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>ón: AV 33 59 53</t>
+        </is>
+      </c>
+      <c r="O88" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Ciencias sociales</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Bello</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>25/04/2026 a las 15:41</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Bello</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>ía de Educación: Bello</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>I.E. La Primavera</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>I.E. La Primavera - Sede Principa</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>Dirección: KR 68 C 59 A 35</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>ón: KR 68 C 59 A 35</t>
+        </is>
+      </c>
+      <c r="O89" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Ciencias sociales</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Bello</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>25/04/2026 a las 15:41</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Bello</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>ía de Educación: Bello</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>I.E. Fernando Velez</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>I.E. Fernando Velez - Sede Princi</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>Dirección: KR 58 A 52 C 135</t>
+        </is>
+      </c>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>ón: KR 58 A 52 C 135</t>
+        </is>
+      </c>
+      <c r="O90" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Idioma extranjero inglés</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Bello</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>25/04/2026 a las 15:41</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>Itaguí</t>
-        </is>
-      </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>Antioquia</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>ía de Educación: Itaguí</t>
-        </is>
-      </c>
-      <c r="J85" t="inlineStr">
-        <is>
-          <t>I.E. AVELINO SALDARRIAGA</t>
-        </is>
-      </c>
-      <c r="K85" t="inlineStr">
-        <is>
-          <t>I.E. AVELINO SALDARRIAGA SEDE PRI</t>
-        </is>
-      </c>
-      <c r="L85" t="inlineStr">
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Bello</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>ía de Educación: Bello</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>I.E. Antonio Maria Bedoya</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>Escuela Rural Antonio Maria Bedoya - Sede Principa</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>TIERRADENTRO</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t>ón: CARRERA 69 77 220</t>
+        </is>
+      </c>
+      <c r="O91" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Tecnología e informática</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Bello</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>25/04/2026 a las 15:41</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Bello</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>ía de Educación: Bello</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>I.E. Gilberto Echeverri Mejia</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>Gilberto Echeverri Mejia - Sede Principal</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr">
         <is>
           <t>URBANA</t>
         </is>
       </c>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>LA INDEPENDENCIA</t>
-        </is>
-      </c>
-      <c r="N85" t="inlineStr">
-        <is>
-          <t>ón: CL 39 49 77</t>
-        </is>
-      </c>
-      <c r="O85" t="inlineStr">
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>Dirección: CLL 68 NO 49A-41</t>
+        </is>
+      </c>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t>ón: CLL 68 NO 49A-41</t>
+        </is>
+      </c>
+      <c r="O92" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Bello</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>25/04/2026 a las 15:41</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Bello</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>ía de Educación: Bello</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>I.E. Comercial Antonio Roldan Bet</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>Liceo De Bello - Sede Principal</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>Dirección: DG 65 NO 45BB-215</t>
+        </is>
+      </c>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>ón: DG 65 NO 45BB-215</t>
+        </is>
+      </c>
+      <c r="O93" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Bello</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>25/04/2026 a las 15:41</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Bello</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>ía de Educación: Bello</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>I.E. Cincuentenario de Fabricato</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>Colegio Cincuentenario De Fabricato - Sede Princip</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>Dirección: KR 56 A 60 61</t>
+        </is>
+      </c>
+      <c r="N94" t="inlineStr">
+        <is>
+          <t>ón: KR 56 A 60 61</t>
+        </is>
+      </c>
+      <c r="O94" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Bello</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>25/04/2026 a las 15:41</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Bello</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>ía de Educación: Bello</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>I.E. Raquel Jaramillo</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>Escuela Nicolas Sierra Sierra</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>.</t>
+        </is>
+      </c>
+      <c r="N95" t="inlineStr">
+        <is>
+          <t>ón: KR 73 25 B 19</t>
+        </is>
+      </c>
+      <c r="O95" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Preescolar</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Bello</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>25/04/2026 a las 15:41</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Bello</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>ía de Educación: Bello</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>I.E. Josefa Campos</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>Colegio Fe Y Alegria Josefa Campos - Sede Princip</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>Dirección: DG 65 NO 45BB-137</t>
+        </is>
+      </c>
+      <c r="N96" t="inlineStr">
+        <is>
+          <t>ón: DG 65 NO 45BB-137</t>
+        </is>
+      </c>
+      <c r="O96" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Preescolar</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Bello</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>25/04/2026 a las 15:41</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Bello</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>ía de Educación: Bello</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>I.E. Centenario de Bello</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>I.E. Centenario de Bello - Sede P</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>Dirección: CR 41F NO 20CC-50</t>
+        </is>
+      </c>
+      <c r="N97" t="inlineStr">
+        <is>
+          <t>ón: CR 41F NO 20CC-50</t>
+        </is>
+      </c>
+      <c r="O97" t="inlineStr">
         <is>
           <t>A</t>
         </is>

--- a/nuevas_plazas.xlsx
+++ b/nuevas_plazas.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O97"/>
+  <dimension ref="A1:O99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6831,10 +6831,8 @@
           <t>25/04/2026 a las 15:41</t>
         </is>
       </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="F86" t="n">
+        <v>2</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
@@ -6908,10 +6906,8 @@
           <t>25/04/2026 a las 15:41</t>
         </is>
       </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="F87" t="n">
+        <v>2</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
@@ -6985,10 +6981,8 @@
           <t>25/04/2026 a las 15:41</t>
         </is>
       </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="F88" t="n">
+        <v>3</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
@@ -7062,10 +7056,8 @@
           <t>25/04/2026 a las 15:41</t>
         </is>
       </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="F89" t="n">
+        <v>3</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
@@ -7139,10 +7131,8 @@
           <t>25/04/2026 a las 15:41</t>
         </is>
       </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="F90" t="n">
+        <v>4</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
@@ -7216,10 +7206,8 @@
           <t>25/04/2026 a las 15:41</t>
         </is>
       </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="F91" t="n">
+        <v>1</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
@@ -7293,10 +7281,8 @@
           <t>25/04/2026 a las 15:41</t>
         </is>
       </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="F92" t="n">
+        <v>8</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
@@ -7370,10 +7356,8 @@
           <t>25/04/2026 a las 15:41</t>
         </is>
       </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="F93" t="n">
+        <v>5</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
@@ -7447,10 +7431,8 @@
           <t>25/04/2026 a las 15:41</t>
         </is>
       </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="F94" t="n">
+        <v>3</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
@@ -7524,10 +7506,8 @@
           <t>25/04/2026 a las 15:41</t>
         </is>
       </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="F95" t="n">
+        <v>4</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
@@ -7601,10 +7581,8 @@
           <t>25/04/2026 a las 15:41</t>
         </is>
       </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="F96" t="n">
+        <v>3</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
@@ -7678,52 +7656,204 @@
           <t>25/04/2026 a las 15:41</t>
         </is>
       </c>
-      <c r="F97" t="inlineStr">
+      <c r="F97" t="n">
+        <v>4</v>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Bello</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>ía de Educación: Bello</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>I.E. Centenario de Bello</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>I.E. Centenario de Bello - Sede P</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>Dirección: CR 41F NO 20CC-50</t>
+        </is>
+      </c>
+      <c r="N97" t="inlineStr">
+        <is>
+          <t>ón: CR 41F NO 20CC-50</t>
+        </is>
+      </c>
+      <c r="O97" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Ciencias sociales</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Envigado</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>28/04/2026 a las 12:03</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Envigado</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>ía de Educación: Envigado</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>I. E. NORMAL SUPERIOR DE ENVIGADO</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>SEDE NORMAL SUPERIOR DE ENVIGADO</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>Dirección: CL 37 S 33 14</t>
+        </is>
+      </c>
+      <c r="N98" t="inlineStr">
+        <is>
+          <t>ón: CL 37 S 33 14</t>
+        </is>
+      </c>
+      <c r="O98" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Educación ética y en valores</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Rionegro</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>28/04/2026 a las 12:04</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>Bello</t>
-        </is>
-      </c>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t>Antioquia</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr">
-        <is>
-          <t>ía de Educación: Bello</t>
-        </is>
-      </c>
-      <c r="J97" t="inlineStr">
-        <is>
-          <t>I.E. Centenario de Bello</t>
-        </is>
-      </c>
-      <c r="K97" t="inlineStr">
-        <is>
-          <t>I.E. Centenario de Bello - Sede P</t>
-        </is>
-      </c>
-      <c r="L97" t="inlineStr">
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Rionegro</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>ía de Educación: Rionegro</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>I.E QUEBRADA ARRIBA BALDOMERO SANIN CANO</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>I.E QUEBRADA ARRIBA BALDOMERO SANIN CANO-SEDE PPAL</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr">
         <is>
           <t>URBANA</t>
         </is>
       </c>
-      <c r="M97" t="inlineStr">
-        <is>
-          <t>Dirección: CR 41F NO 20CC-50</t>
-        </is>
-      </c>
-      <c r="N97" t="inlineStr">
-        <is>
-          <t>ón: CR 41F NO 20CC-50</t>
-        </is>
-      </c>
-      <c r="O97" t="inlineStr">
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>QUEBRADA ARRIBA</t>
+        </is>
+      </c>
+      <c r="N99" t="inlineStr">
+        <is>
+          <t>ón: KR 57 D 52 14</t>
+        </is>
+      </c>
+      <c r="O99" t="inlineStr">
         <is>
           <t>A</t>
         </is>

--- a/nuevas_plazas.xlsx
+++ b/nuevas_plazas.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O99"/>
+  <dimension ref="A1:O100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7731,10 +7731,8 @@
           <t>28/04/2026 a las 12:03</t>
         </is>
       </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
+      <c r="F98" t="n">
+        <v>7</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
@@ -7808,10 +7806,8 @@
           <t>28/04/2026 a las 12:04</t>
         </is>
       </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="F99" t="n">
+        <v>4</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
@@ -7854,6 +7850,83 @@
         </is>
       </c>
       <c r="O99" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Humanidades y lengua castellana</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Ituango</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>30/04/2026 a las 10:25</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Ituango</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>I. E. R. LA PEREZ</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>I. E. R. EL CEDRAL</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>VDA. EL CEDRAL</t>
+        </is>
+      </c>
+      <c r="N100" t="inlineStr">
+        <is>
+          <t>ón: VDA. EL CEDRAL</t>
+        </is>
+      </c>
+      <c r="O100" t="inlineStr">
         <is>
           <t>A</t>
         </is>

--- a/nuevas_plazas.xlsx
+++ b/nuevas_plazas.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O100"/>
+  <dimension ref="A1:O101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7881,10 +7881,8 @@
           <t>30/04/2026 a las 10:25</t>
         </is>
       </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
+      <c r="F100" t="n">
+        <v>13</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
@@ -7927,6 +7925,83 @@
         </is>
       </c>
       <c r="O100" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Educación ética y en valores</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Rionegro</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>01/05/2026 a las 07:27</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Rionegro</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>ía de Educación: Rionegro</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>I.E QUEBRADA ARRIBA BALDOMERO SANIN CANO</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>I.E QUEBRADA ARRIBA BALDOMERO SANIN CANO-SEDE PPAL</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>QUEBRADA ARRIBA</t>
+        </is>
+      </c>
+      <c r="N101" t="inlineStr">
+        <is>
+          <t>ón: KR 57 D 52 14</t>
+        </is>
+      </c>
+      <c r="O101" t="inlineStr">
         <is>
           <t>A</t>
         </is>

--- a/nuevas_plazas.xlsx
+++ b/nuevas_plazas.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O101"/>
+  <dimension ref="A1:O120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7956,10 +7956,8 @@
           <t>01/05/2026 a las 07:27</t>
         </is>
       </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
+      <c r="F101" t="n">
+        <v>26</v>
       </c>
       <c r="G101" t="inlineStr">
         <is>
@@ -8002,6 +8000,1469 @@
         </is>
       </c>
       <c r="O101" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Caucasia</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>01/05/2026 a las 12:37</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Caucasia</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>I.E.R. LAS MALVINAS</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>I.E.R LAS MALVINAS - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>VDA. LAS MALVINAS</t>
+        </is>
+      </c>
+      <c r="N102" t="inlineStr">
+        <is>
+          <t>ón: VDA. LAS MALVINAS</t>
+        </is>
+      </c>
+      <c r="O102" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Matemáticas</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Abejorral</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>01/05/2026 a las 12:37</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Oriente</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>I. E. FUNDACION CELIA DUQUE DE DUQUE</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>CENTRO EDUCATIVO RURAL EL GUADUAL</t>
+        </is>
+      </c>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>VEREDA EL GUADUAL</t>
+        </is>
+      </c>
+      <c r="N103" t="inlineStr">
+        <is>
+          <t>ón: VEREDA EL GUADUAL</t>
+        </is>
+      </c>
+      <c r="O103" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Humanidades y lengua castellana</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Abejorral</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>01/05/2026 a las 12:37</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>Oriente</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>I. E. FUNDACION CELIA DUQUE DE DUQUE</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>I. E. FUNDACION CELIA DUQUE DE DUQUE - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>BARRIO OBRERO</t>
+        </is>
+      </c>
+      <c r="N104" t="inlineStr">
+        <is>
+          <t>ón: KR 55 44 110</t>
+        </is>
+      </c>
+      <c r="O104" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Humanidades y lengua castellana</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Abejorral</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>01/05/2026 a las 12:37</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Oriente</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>I. E. R. DE PANTANILLO</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>C. E. R. INES GUZMAN</t>
+        </is>
+      </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>VDA. MATA DE GUADUA</t>
+        </is>
+      </c>
+      <c r="N105" t="inlineStr">
+        <is>
+          <t>ón: VDA MATA DE GUADUA</t>
+        </is>
+      </c>
+      <c r="O105" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Abejorral</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>01/05/2026 a las 12:37</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Oriente</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>I. E. R. DE PANTANILLO</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>C. E. R. CALIFORNIA</t>
+        </is>
+      </c>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>VDA. LA PERDIDA</t>
+        </is>
+      </c>
+      <c r="N106" t="inlineStr">
+        <is>
+          <t>ón: VDA LA PERDIDA</t>
+        </is>
+      </c>
+      <c r="O106" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Tecnología e informática</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Andes</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>01/05/2026 a las 12:37</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>Suroeste</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>I. E. SANTA RITA</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>I. E. SANTA RITA - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>CORREG SANTA RITA</t>
+        </is>
+      </c>
+      <c r="N107" t="inlineStr">
+        <is>
+          <t>ón: CORREG. SANTA RITA</t>
+        </is>
+      </c>
+      <c r="O107" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Matemáticas</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Argelia</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>01/05/2026 a las 12:37</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>Argelia</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>I. E. R. PRESBITERO MARIO ANGEL</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>C. E. R. RANCHO LARGO</t>
+        </is>
+      </c>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>VDA. RANCHO LARGO</t>
+        </is>
+      </c>
+      <c r="N108" t="inlineStr">
+        <is>
+          <t>ón: VDA RANCHO LARGO</t>
+        </is>
+      </c>
+      <c r="O108" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Ciencias sociales</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Armenia</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>01/05/2026 a las 12:37</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>Occidente</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>I. E. ROSA MESA DE MEJIA</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>I. E. ROSA MESA DE MEJIA - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>Dirección: KR 7 10 13</t>
+        </is>
+      </c>
+      <c r="N109" t="inlineStr">
+        <is>
+          <t>ón: KR 7 10 13</t>
+        </is>
+      </c>
+      <c r="O109" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Humanidades y lengua castellana</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>Briceño</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>01/05/2026 a las 12:37</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>Briceño</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>I. E. ANTONIO ROLDAN BETANCUR</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>C. E. R. ALTO DE CHIRI</t>
+        </is>
+      </c>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>VDA. ALTO CHIRI</t>
+        </is>
+      </c>
+      <c r="N110" t="inlineStr">
+        <is>
+          <t>ón: VDA. ALTO CHIRI</t>
+        </is>
+      </c>
+      <c r="O110" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Idioma extranjero inglés</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Cáceres</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>01/05/2026 a las 12:37</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>Cáceres</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>C. E. R. SANTA INES DEL MONTE</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>ESCUELA GETSEMANY</t>
+        </is>
+      </c>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>VDA. ISLA LA AMARGURA</t>
+        </is>
+      </c>
+      <c r="N111" t="inlineStr">
+        <is>
+          <t>ón: VDA. ISLA LA AMARGURA</t>
+        </is>
+      </c>
+      <c r="O111" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Preescolar</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>Cáceres</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>01/05/2026 a las 12:37</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>Cáceres</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>I. E. MANIZALES</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>E. U. MANIZALES - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>CORREG. MANIZALES</t>
+        </is>
+      </c>
+      <c r="N112" t="inlineStr">
+        <is>
+          <t>ón: CORREG. MANIZALES</t>
+        </is>
+      </c>
+      <c r="O112" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Educación artística - artes escénicas</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Cáceres</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>01/05/2026 a las 12:37</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>Cáceres</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>I. E. GUARUMO</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>COLEGIO GUARUMO - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>CORREG. EL GUARUMO</t>
+        </is>
+      </c>
+      <c r="N113" t="inlineStr">
+        <is>
+          <t>ón: VDA. EL GUARUMO</t>
+        </is>
+      </c>
+      <c r="O113" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Matemáticas</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>Cáceres</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>01/05/2026 a las 12:37</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>Cáceres</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>I. E. GASPAR DE RODAS</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>LICEO GASPAR DE RODAS - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>CORRREG. JARDIN</t>
+        </is>
+      </c>
+      <c r="N114" t="inlineStr">
+        <is>
+          <t>ón: SALIDA A MANIZALES KM1</t>
+        </is>
+      </c>
+      <c r="O114" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Educación física, recreación y deporte</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>Carepa</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>01/05/2026 a las 12:37</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>Carepa</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>I. E. R. ZUNGO EMBARCADERO</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>COLEGIO ZUNGO EMBARCADERO - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L115" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>B. PUEBLO NUEVO</t>
+        </is>
+      </c>
+      <c r="N115" t="inlineStr">
+        <is>
+          <t>ón: CORREG. ZUNGO EMBARCADERO</t>
+        </is>
+      </c>
+      <c r="O115" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Educación ética y en valores</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>Caucasia</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>01/05/2026 a las 12:37</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>Caucasia</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>I.E.R. LAS MALVINAS</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>I.E.R LAS MALVINAS - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L116" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>VDA. LAS MALVINAS</t>
+        </is>
+      </c>
+      <c r="N116" t="inlineStr">
+        <is>
+          <t>ón: VDA. LAS MALVINAS</t>
+        </is>
+      </c>
+      <c r="O116" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Matemáticas</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Caucasia</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>01/05/2026 a las 12:37</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>Caucasia</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>I. E. LICEO CONCEJO MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>LICEO CONCEJO MUNICIPAL - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L117" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>EL PAJONAL</t>
+        </is>
+      </c>
+      <c r="N117" t="inlineStr">
+        <is>
+          <t>ón: IND CARRET.TRONCAL CON AV. EL PAJONAL</t>
+        </is>
+      </c>
+      <c r="O117" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>Caucasia</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>01/05/2026 a las 12:37</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>Caucasia</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>I. E. SANTO DOMINGO</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>CER EL CAMELLO</t>
+        </is>
+      </c>
+      <c r="L118" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>.</t>
+        </is>
+      </c>
+      <c r="N118" t="inlineStr">
+        <is>
+          <t>ón: CL 28 C KR 2 A</t>
+        </is>
+      </c>
+      <c r="O118" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>Caucasia</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>01/05/2026 a las 12:37</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>Caucasia</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>I. E. MARGENTO</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>E R I VILLA DEL SOCORRO</t>
+        </is>
+      </c>
+      <c r="L119" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>VDA. VILLA DEL SOCORRO</t>
+        </is>
+      </c>
+      <c r="N119" t="inlineStr">
+        <is>
+          <t>ón: VDA. VILLA DEL SOCORRO</t>
+        </is>
+      </c>
+      <c r="O119" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Priorizadas para jóvenes entre 18 y 28 años</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Educación física, recreación y deporte</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Chigorodó</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>01/05/2026 a las 12:37</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>Chigorodó</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>I. E. MARIA AUXILIADORA</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>I. E. MARIA AUXILIADORA - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L120" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>BR LOS OLIVOS</t>
+        </is>
+      </c>
+      <c r="N120" t="inlineStr">
+        <is>
+          <t>ón: KR 111 93 35</t>
+        </is>
+      </c>
+      <c r="O120" t="inlineStr">
         <is>
           <t>A</t>
         </is>

--- a/nuevas_plazas.xlsx
+++ b/nuevas_plazas.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O120"/>
+  <dimension ref="A1:O121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8031,10 +8031,8 @@
           <t>01/05/2026 a las 12:37</t>
         </is>
       </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
+      <c r="F102" t="n">
+        <v>18</v>
       </c>
       <c r="G102" t="inlineStr">
         <is>
@@ -8108,10 +8106,8 @@
           <t>01/05/2026 a las 12:37</t>
         </is>
       </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="F103" t="n">
+        <v>6</v>
       </c>
       <c r="G103" t="inlineStr">
         <is>
@@ -8185,10 +8181,8 @@
           <t>01/05/2026 a las 12:37</t>
         </is>
       </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
+      <c r="F104" t="n">
+        <v>11</v>
       </c>
       <c r="G104" t="inlineStr">
         <is>
@@ -8262,10 +8256,8 @@
           <t>01/05/2026 a las 12:37</t>
         </is>
       </c>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
+      <c r="F105" t="n">
+        <v>10</v>
       </c>
       <c r="G105" t="inlineStr">
         <is>
@@ -8339,10 +8331,8 @@
           <t>01/05/2026 a las 12:37</t>
         </is>
       </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
+      <c r="F106" t="n">
+        <v>16</v>
       </c>
       <c r="G106" t="inlineStr">
         <is>
@@ -8416,10 +8406,8 @@
           <t>01/05/2026 a las 12:37</t>
         </is>
       </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
+      <c r="F107" t="n">
+        <v>7</v>
       </c>
       <c r="G107" t="inlineStr">
         <is>
@@ -8493,10 +8481,8 @@
           <t>01/05/2026 a las 12:37</t>
         </is>
       </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="F108" t="n">
+        <v>3</v>
       </c>
       <c r="G108" t="inlineStr">
         <is>
@@ -8570,10 +8556,8 @@
           <t>01/05/2026 a las 12:37</t>
         </is>
       </c>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F109" t="n">
+        <v>0</v>
       </c>
       <c r="G109" t="inlineStr">
         <is>
@@ -8647,10 +8631,8 @@
           <t>01/05/2026 a las 12:37</t>
         </is>
       </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
+      <c r="F110" t="n">
+        <v>7</v>
       </c>
       <c r="G110" t="inlineStr">
         <is>
@@ -8724,10 +8706,8 @@
           <t>01/05/2026 a las 12:37</t>
         </is>
       </c>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="F111" t="n">
+        <v>6</v>
       </c>
       <c r="G111" t="inlineStr">
         <is>
@@ -8801,10 +8781,8 @@
           <t>01/05/2026 a las 12:37</t>
         </is>
       </c>
-      <c r="F112" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
+      <c r="F112" t="n">
+        <v>9</v>
       </c>
       <c r="G112" t="inlineStr">
         <is>
@@ -8878,10 +8856,8 @@
           <t>01/05/2026 a las 12:37</t>
         </is>
       </c>
-      <c r="F113" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="F113" t="n">
+        <v>2</v>
       </c>
       <c r="G113" t="inlineStr">
         <is>
@@ -8955,10 +8931,8 @@
           <t>01/05/2026 a las 12:37</t>
         </is>
       </c>
-      <c r="F114" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="F114" t="n">
+        <v>3</v>
       </c>
       <c r="G114" t="inlineStr">
         <is>
@@ -9032,10 +9006,8 @@
           <t>01/05/2026 a las 12:37</t>
         </is>
       </c>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="F115" t="n">
+        <v>8</v>
       </c>
       <c r="G115" t="inlineStr">
         <is>
@@ -9109,10 +9081,8 @@
           <t>01/05/2026 a las 12:37</t>
         </is>
       </c>
-      <c r="F116" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="F116" t="n">
+        <v>3</v>
       </c>
       <c r="G116" t="inlineStr">
         <is>
@@ -9186,10 +9156,8 @@
           <t>01/05/2026 a las 12:37</t>
         </is>
       </c>
-      <c r="F117" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="F117" t="n">
+        <v>5</v>
       </c>
       <c r="G117" t="inlineStr">
         <is>
@@ -9263,10 +9231,8 @@
           <t>01/05/2026 a las 12:37</t>
         </is>
       </c>
-      <c r="F118" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
+      <c r="F118" t="n">
+        <v>13</v>
       </c>
       <c r="G118" t="inlineStr">
         <is>
@@ -9340,10 +9306,8 @@
           <t>01/05/2026 a las 12:37</t>
         </is>
       </c>
-      <c r="F119" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
+      <c r="F119" t="n">
+        <v>14</v>
       </c>
       <c r="G119" t="inlineStr">
         <is>
@@ -9417,10 +9381,8 @@
           <t>01/05/2026 a las 12:37</t>
         </is>
       </c>
-      <c r="F120" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
+      <c r="F120" t="n">
+        <v>10</v>
       </c>
       <c r="G120" t="inlineStr">
         <is>
@@ -9463,6 +9425,83 @@
         </is>
       </c>
       <c r="O120" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Ciencias sociales</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>Armenia</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>02/05/2026 a las 12:37</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>Occidente</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>I. E. ROSA MESA DE MEJIA</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>I. E. ROSA MESA DE MEJIA - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L121" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>Dirección: KR 7 10 13</t>
+        </is>
+      </c>
+      <c r="N121" t="inlineStr">
+        <is>
+          <t>ón: KR 7 10 13</t>
+        </is>
+      </c>
+      <c r="O121" t="inlineStr">
         <is>
           <t>A</t>
         </is>

--- a/nuevas_plazas.xlsx
+++ b/nuevas_plazas.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O121"/>
+  <dimension ref="A1:O122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9456,52 +9456,127 @@
           <t>02/05/2026 a las 12:37</t>
         </is>
       </c>
-      <c r="F121" t="inlineStr">
+      <c r="F121" t="n">
+        <v>0</v>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>Occidente</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>I. E. ROSA MESA DE MEJIA</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>I. E. ROSA MESA DE MEJIA - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L121" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>Dirección: KR 7 10 13</t>
+        </is>
+      </c>
+      <c r="N121" t="inlineStr">
+        <is>
+          <t>ón: KR 7 10 13</t>
+        </is>
+      </c>
+      <c r="O121" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Ciencias sociales</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>Armenia</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>03/05/2026 a las 12:37</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G121" t="inlineStr">
+      <c r="G122" t="inlineStr">
         <is>
           <t>Occidente</t>
         </is>
       </c>
-      <c r="H121" t="inlineStr">
-        <is>
-          <t>Antioquia</t>
-        </is>
-      </c>
-      <c r="I121" t="inlineStr">
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
         <is>
           <t>ía de Educación: Antioquia</t>
         </is>
       </c>
-      <c r="J121" t="inlineStr">
+      <c r="J122" t="inlineStr">
         <is>
           <t>I. E. ROSA MESA DE MEJIA</t>
         </is>
       </c>
-      <c r="K121" t="inlineStr">
+      <c r="K122" t="inlineStr">
         <is>
           <t>I. E. ROSA MESA DE MEJIA - SEDE PRINCIPAL</t>
         </is>
       </c>
-      <c r="L121" t="inlineStr">
+      <c r="L122" t="inlineStr">
         <is>
           <t>URBANA</t>
         </is>
       </c>
-      <c r="M121" t="inlineStr">
+      <c r="M122" t="inlineStr">
         <is>
           <t>Dirección: KR 7 10 13</t>
         </is>
       </c>
-      <c r="N121" t="inlineStr">
+      <c r="N122" t="inlineStr">
         <is>
           <t>ón: KR 7 10 13</t>
         </is>
       </c>
-      <c r="O121" t="inlineStr">
+      <c r="O122" t="inlineStr">
         <is>
           <t>A</t>
         </is>

--- a/nuevas_plazas.xlsx
+++ b/nuevas_plazas.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O122"/>
+  <dimension ref="A1:O123"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9531,10 +9531,8 @@
           <t>03/05/2026 a las 12:37</t>
         </is>
       </c>
-      <c r="F122" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F122" t="n">
+        <v>0</v>
       </c>
       <c r="G122" t="inlineStr">
         <is>
@@ -9577,6 +9575,83 @@
         </is>
       </c>
       <c r="O122" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Educación ética y en valores</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>Rionegro</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>06/05/2026 a las 07:05</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>Rionegro</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>ía de Educación: Rionegro</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>I.E QUEBRADA ARRIBA BALDOMERO SANIN CANO</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>I.E QUEBRADA ARRIBA BALDOMERO SANIN CANO-SEDE PPAL</t>
+        </is>
+      </c>
+      <c r="L123" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>QUEBRADA ARRIBA</t>
+        </is>
+      </c>
+      <c r="N123" t="inlineStr">
+        <is>
+          <t>ón: KR 57 D 52 14</t>
+        </is>
+      </c>
+      <c r="O123" t="inlineStr">
         <is>
           <t>A</t>
         </is>

--- a/nuevas_plazas.xlsx
+++ b/nuevas_plazas.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O123"/>
+  <dimension ref="A1:O124"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9606,10 +9606,8 @@
           <t>06/05/2026 a las 07:05</t>
         </is>
       </c>
-      <c r="F123" t="inlineStr">
-        <is>
-          <t>113</t>
-        </is>
+      <c r="F123" t="n">
+        <v>113</v>
       </c>
       <c r="G123" t="inlineStr">
         <is>
@@ -9652,6 +9650,83 @@
         </is>
       </c>
       <c r="O123" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Ciencias naturales y educación ambiental</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Rionegro</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>06/05/2026 a las 14:06</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>Rionegro</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>ía de Educación: Rionegro</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>I.E QUEBRADA ARRIBA BALDOMERO SANIN CANO</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>I.E QUEBRADA ARRIBA BALDOMERO SANIN CANO-SEDE PPAL</t>
+        </is>
+      </c>
+      <c r="L124" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>QUEBRADA ARRIBA</t>
+        </is>
+      </c>
+      <c r="N124" t="inlineStr">
+        <is>
+          <t>ón: KR 57 D 52 14</t>
+        </is>
+      </c>
+      <c r="O124" t="inlineStr">
         <is>
           <t>A</t>
         </is>

--- a/nuevas_plazas.xlsx
+++ b/nuevas_plazas.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O124"/>
+  <dimension ref="A1:O139"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9681,10 +9681,8 @@
           <t>06/05/2026 a las 14:06</t>
         </is>
       </c>
-      <c r="F124" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
+      <c r="F124" t="n">
+        <v>30</v>
       </c>
       <c r="G124" t="inlineStr">
         <is>
@@ -9727,6 +9725,1161 @@
         </is>
       </c>
       <c r="O124" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Educación física, recreación y deporte</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>Envigado</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>09/05/2026 a las 09:32</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>Envigado</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>ía de Educación: Envigado</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>I.E. MARIA POUSSEPIN</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>Sede Maria Poussepin</t>
+        </is>
+      </c>
+      <c r="L125" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>.</t>
+        </is>
+      </c>
+      <c r="N125" t="inlineStr">
+        <is>
+          <t>ón: KR 44 38 S 15</t>
+        </is>
+      </c>
+      <c r="O125" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Educación artística – música</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>Caucasia</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>09/05/2026 a las 11:22</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>Caucasia</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>I. E. CUTURU</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>I. E. CUTURU - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L126" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>CORREG.CUTURU</t>
+        </is>
+      </c>
+      <c r="N126" t="inlineStr">
+        <is>
+          <t>ón: CORREG.CUTURU</t>
+        </is>
+      </c>
+      <c r="O126" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Educación artística – danzas</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>Tarazá</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>09/05/2026 a las 11:22</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>Tarazá</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>I. E. LA INMACULADA</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>I.E. LA INMACULADA - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L127" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>CORREG. EL DOCE</t>
+        </is>
+      </c>
+      <c r="N127" t="inlineStr">
+        <is>
+          <t>ón: CORREG. EL DOCE</t>
+        </is>
+      </c>
+      <c r="O127" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Educación artística – música</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>Zaragoza</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>09/05/2026 a las 11:22</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>Zaragoza</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>I.E.R. LA PAJUILA</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>I.E.R. LA PAJUILA - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L128" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>VDA LA PAJUILA</t>
+        </is>
+      </c>
+      <c r="N128" t="inlineStr">
+        <is>
+          <t>ón: VDA LA PAJUILA</t>
+        </is>
+      </c>
+      <c r="O128" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Educación artística – música</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>Yondó</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>09/05/2026 a las 11:22</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>Yondó</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>I. E. LUIS EDUARDO DIAZ</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>I. E. LUIS EDUARDO DIAZ - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L129" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>BARRIO. EL PROGRESO</t>
+        </is>
+      </c>
+      <c r="N129" t="inlineStr">
+        <is>
+          <t>ón: KR 45 50 52</t>
+        </is>
+      </c>
+      <c r="O129" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Educación física, recreación y deporte</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>Yondó</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>09/05/2026 a las 11:23</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>Yondó</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>I. E. R. SAN MIGUEL DEL TIGRE</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>I. E. R. SAN MIGUEL DEL TIGRE - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L130" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>CORREG.SAN MIGUEL DEL TIGRE</t>
+        </is>
+      </c>
+      <c r="N130" t="inlineStr">
+        <is>
+          <t>ón: CORREG.SAN MIGUEL DEL TIGRE</t>
+        </is>
+      </c>
+      <c r="O130" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Educación artística – música</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>Briceño</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>09/05/2026 a las 11:23</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>Briceño</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>C. E. R. MORRON</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>C. E. R. MORRON - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L131" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>VDA. ABEJORRAL</t>
+        </is>
+      </c>
+      <c r="N131" t="inlineStr">
+        <is>
+          <t>ón: VDA. ABEJORRAL</t>
+        </is>
+      </c>
+      <c r="O131" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Priorizadas para jóvenes entre 18 y 28 años</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Educación artística – música</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>Santa Rosa De Osos</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>09/05/2026 a las 11:23</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>Santa Rosa de Osos</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>I.E.R. SAN ISIDRO</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>I.E.R. SAN ISIDRO - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L132" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>CORREG. SAN ISIDRO</t>
+        </is>
+      </c>
+      <c r="N132" t="inlineStr">
+        <is>
+          <t>ón: CORREG. SAN ISIDRO</t>
+        </is>
+      </c>
+      <c r="O132" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Educación artística – música</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>Yarumal</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>09/05/2026 a las 11:23</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>Yarumal</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>I. E. EL CEDRO</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>I. E. EL CEDRO - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L133" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>CORREG. EL CEDRO</t>
+        </is>
+      </c>
+      <c r="N133" t="inlineStr">
+        <is>
+          <t>ón: CORREG. EL CEDRO</t>
+        </is>
+      </c>
+      <c r="O133" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Priorizadas para jóvenes entre 18 y 28 años</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Educación artística – danzas</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>Dabeiba</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>09/05/2026 a las 11:23</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>Dabeiba</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>I. E. R. INDIGENISTA LLANO GORDO</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>I. E. R. INDIGENISTA LLANO GORDO - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L134" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>Dirección: VDA.LLANOGORDO</t>
+        </is>
+      </c>
+      <c r="N134" t="inlineStr">
+        <is>
+          <t>ón: VDA.LLANOGORDO</t>
+        </is>
+      </c>
+      <c r="O134" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Educación artística – danzas</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>Andes</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>09/05/2026 a las 11:23</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>Suroeste</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>I. E. R. CARBONERA</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>I. E. R. CARBONERA - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L135" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>CORREG SAN BARTOLO</t>
+        </is>
+      </c>
+      <c r="N135" t="inlineStr">
+        <is>
+          <t>ón: CORREG SAN BARTOLO</t>
+        </is>
+      </c>
+      <c r="O135" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Educación artística - artes escénicas</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>Santa Barbara</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>09/05/2026 a las 11:23</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>Suroeste</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>I. E. DAMASCO</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>I. E. DAMASCO - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L136" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>CORREG. DAMASCO</t>
+        </is>
+      </c>
+      <c r="N136" t="inlineStr">
+        <is>
+          <t>ón: CORREG. DAMASCO</t>
+        </is>
+      </c>
+      <c r="O136" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Educación artística – danzas</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>Carepa</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>09/05/2026 a las 11:23</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>Carepa</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>I. E. COLOMBIA</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>COLEGIO COLOMBIA - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L137" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>B. GAITAN</t>
+        </is>
+      </c>
+      <c r="N137" t="inlineStr">
+        <is>
+          <t>ón: CL. 83 CRA67</t>
+        </is>
+      </c>
+      <c r="O137" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Preescolar</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>San Pedro De Urabá</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>09/05/2026 a las 11:23</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>San Pedro de Urabá</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>I.E.R. SAN PABLO APOSTOL</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>I. E. R. SAN PABLO APOSTOL - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L138" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M138" t="inlineStr">
+        <is>
+          <t>VDA. EL CAIMAN</t>
+        </is>
+      </c>
+      <c r="N138" t="inlineStr">
+        <is>
+          <t>ón: VDA. EL CAIMÁN</t>
+        </is>
+      </c>
+      <c r="O138" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>Amalfi</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>09/05/2026 a las 11:23</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>Amalfi</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>C. E. R. TINITACITA</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>I. E. R. CRUCES</t>
+        </is>
+      </c>
+      <c r="L139" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>VDA. CRUCES</t>
+        </is>
+      </c>
+      <c r="N139" t="inlineStr">
+        <is>
+          <t>ón: VDA CRUCES</t>
+        </is>
+      </c>
+      <c r="O139" t="inlineStr">
         <is>
           <t>A</t>
         </is>

--- a/nuevas_plazas.xlsx
+++ b/nuevas_plazas.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O139"/>
+  <dimension ref="A1:O140"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9756,10 +9756,8 @@
           <t>09/05/2026 a las 09:32</t>
         </is>
       </c>
-      <c r="F125" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
+      <c r="F125" t="n">
+        <v>42</v>
       </c>
       <c r="G125" t="inlineStr">
         <is>
@@ -9833,10 +9831,8 @@
           <t>09/05/2026 a las 11:22</t>
         </is>
       </c>
-      <c r="F126" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="F126" t="n">
+        <v>1</v>
       </c>
       <c r="G126" t="inlineStr">
         <is>
@@ -9910,10 +9906,8 @@
           <t>09/05/2026 a las 11:22</t>
         </is>
       </c>
-      <c r="F127" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F127" t="n">
+        <v>0</v>
       </c>
       <c r="G127" t="inlineStr">
         <is>
@@ -9987,10 +9981,8 @@
           <t>09/05/2026 a las 11:22</t>
         </is>
       </c>
-      <c r="F128" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F128" t="n">
+        <v>0</v>
       </c>
       <c r="G128" t="inlineStr">
         <is>
@@ -10064,10 +10056,8 @@
           <t>09/05/2026 a las 11:22</t>
         </is>
       </c>
-      <c r="F129" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F129" t="n">
+        <v>0</v>
       </c>
       <c r="G129" t="inlineStr">
         <is>
@@ -10141,10 +10131,8 @@
           <t>09/05/2026 a las 11:23</t>
         </is>
       </c>
-      <c r="F130" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="F130" t="n">
+        <v>2</v>
       </c>
       <c r="G130" t="inlineStr">
         <is>
@@ -10218,10 +10206,8 @@
           <t>09/05/2026 a las 11:23</t>
         </is>
       </c>
-      <c r="F131" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F131" t="n">
+        <v>0</v>
       </c>
       <c r="G131" t="inlineStr">
         <is>
@@ -10295,10 +10281,8 @@
           <t>09/05/2026 a las 11:23</t>
         </is>
       </c>
-      <c r="F132" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F132" t="n">
+        <v>0</v>
       </c>
       <c r="G132" t="inlineStr">
         <is>
@@ -10372,10 +10356,8 @@
           <t>09/05/2026 a las 11:23</t>
         </is>
       </c>
-      <c r="F133" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F133" t="n">
+        <v>0</v>
       </c>
       <c r="G133" t="inlineStr">
         <is>
@@ -10449,10 +10431,8 @@
           <t>09/05/2026 a las 11:23</t>
         </is>
       </c>
-      <c r="F134" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F134" t="n">
+        <v>0</v>
       </c>
       <c r="G134" t="inlineStr">
         <is>
@@ -10526,10 +10506,8 @@
           <t>09/05/2026 a las 11:23</t>
         </is>
       </c>
-      <c r="F135" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F135" t="n">
+        <v>0</v>
       </c>
       <c r="G135" t="inlineStr">
         <is>
@@ -10603,10 +10581,8 @@
           <t>09/05/2026 a las 11:23</t>
         </is>
       </c>
-      <c r="F136" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F136" t="n">
+        <v>0</v>
       </c>
       <c r="G136" t="inlineStr">
         <is>
@@ -10680,10 +10656,8 @@
           <t>09/05/2026 a las 11:23</t>
         </is>
       </c>
-      <c r="F137" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="F137" t="n">
+        <v>1</v>
       </c>
       <c r="G137" t="inlineStr">
         <is>
@@ -10757,10 +10731,8 @@
           <t>09/05/2026 a las 11:23</t>
         </is>
       </c>
-      <c r="F138" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="F138" t="n">
+        <v>5</v>
       </c>
       <c r="G138" t="inlineStr">
         <is>
@@ -10834,10 +10806,8 @@
           <t>09/05/2026 a las 11:23</t>
         </is>
       </c>
-      <c r="F139" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
+      <c r="F139" t="n">
+        <v>14</v>
       </c>
       <c r="G139" t="inlineStr">
         <is>
@@ -10880,6 +10850,83 @@
         </is>
       </c>
       <c r="O139" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Idioma extranjero inglés</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>Envigado</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>09/05/2026 a las 11:54</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>Envigado</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>ía de Educación: Envigado</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>I. E. LETICIA ARANGO DE AVENDANO</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>ESCUELA LETICIA ARANGO DE AVENDANO</t>
+        </is>
+      </c>
+      <c r="L140" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>Dirección: IND CL. 45 B S 42 C 91</t>
+        </is>
+      </c>
+      <c r="N140" t="inlineStr">
+        <is>
+          <t>ón: IND CL. 45 B S 42 C 91</t>
+        </is>
+      </c>
+      <c r="O140" t="inlineStr">
         <is>
           <t>A</t>
         </is>

--- a/nuevas_plazas.xlsx
+++ b/nuevas_plazas.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O140"/>
+  <dimension ref="A1:O142"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10881,10 +10881,8 @@
           <t>09/05/2026 a las 11:54</t>
         </is>
       </c>
-      <c r="F140" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="F140" t="n">
+        <v>4</v>
       </c>
       <c r="G140" t="inlineStr">
         <is>
@@ -10927,6 +10925,160 @@
         </is>
       </c>
       <c r="O140" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Tecnología e informática</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>San Juan De Urabá</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>12/05/2026 a las 16:01</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>San Juan de Urabá</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>I. E. SAN JUAN DE URABA</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>VILLA VIKINGOS</t>
+        </is>
+      </c>
+      <c r="L141" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>Dirección: IND VILLA VIKINGOS</t>
+        </is>
+      </c>
+      <c r="N141" t="inlineStr">
+        <is>
+          <t>ón: IND VILLA VIKINGOS</t>
+        </is>
+      </c>
+      <c r="O141" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Ciencias naturales química</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>San Juan De Urabá</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>12/05/2026 a las 16:01</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>San Juan de Urabá</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>I. E. SAN JUAN DE URABA</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>VILLA VIKINGOS</t>
+        </is>
+      </c>
+      <c r="L142" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M142" t="inlineStr">
+        <is>
+          <t>Dirección: IND VILLA VIKINGOS</t>
+        </is>
+      </c>
+      <c r="N142" t="inlineStr">
+        <is>
+          <t>ón: IND VILLA VIKINGOS</t>
+        </is>
+      </c>
+      <c r="O142" t="inlineStr">
         <is>
           <t>A</t>
         </is>

--- a/nuevas_plazas.xlsx
+++ b/nuevas_plazas.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O142"/>
+  <dimension ref="A1:O143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10956,10 +10956,8 @@
           <t>12/05/2026 a las 16:01</t>
         </is>
       </c>
-      <c r="F141" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
+      <c r="F141" t="n">
+        <v>7</v>
       </c>
       <c r="G141" t="inlineStr">
         <is>
@@ -11033,10 +11031,8 @@
           <t>12/05/2026 a las 16:01</t>
         </is>
       </c>
-      <c r="F142" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="F142" t="n">
+        <v>5</v>
       </c>
       <c r="G142" t="inlineStr">
         <is>
@@ -11079,6 +11075,83 @@
         </is>
       </c>
       <c r="O142" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Educación religiosa</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>14/05/2026 a las 12:30</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>ía de Educación: Medellín</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>INST EDUC CARLOS VIECO ORTIZ</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>INST EDUC CARLOS VIECO ORTIZ - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L143" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M143" t="inlineStr">
+        <is>
+          <t>SAN JAVIER</t>
+        </is>
+      </c>
+      <c r="N143" t="inlineStr">
+        <is>
+          <t>ón: CL 40 105 36</t>
+        </is>
+      </c>
+      <c r="O143" t="inlineStr">
         <is>
           <t>A</t>
         </is>

--- a/nuevas_plazas.xlsx
+++ b/nuevas_plazas.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O143"/>
+  <dimension ref="A1:O144"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11106,10 +11106,8 @@
           <t>14/05/2026 a las 12:30</t>
         </is>
       </c>
-      <c r="F143" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F143" t="n">
+        <v>0</v>
       </c>
       <c r="G143" t="inlineStr">
         <is>
@@ -11152,6 +11150,83 @@
         </is>
       </c>
       <c r="O143" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Preescolar</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>Rionegro</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>14/05/2026 a las 14:17</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>Rionegro</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>ía de Educación: Rionegro</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>I. E. ANA GOMEZ DE SIERRA</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>I. E. ANA GOMEZ DE SIERRA - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L144" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M144" t="inlineStr">
+        <is>
+          <t>SECTOR LA MOSCA</t>
+        </is>
+      </c>
+      <c r="N144" t="inlineStr">
+        <is>
+          <t>ón: AUTOPISTA MEDELLIN/BOGOTA KM 34</t>
+        </is>
+      </c>
+      <c r="O144" t="inlineStr">
         <is>
           <t>A</t>
         </is>

--- a/nuevas_plazas.xlsx
+++ b/nuevas_plazas.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O144"/>
+  <dimension ref="A1:O149"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11181,10 +11181,8 @@
           <t>14/05/2026 a las 14:17</t>
         </is>
       </c>
-      <c r="F144" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="F144" t="n">
+        <v>2</v>
       </c>
       <c r="G144" t="inlineStr">
         <is>
@@ -11227,6 +11225,391 @@
         </is>
       </c>
       <c r="O144" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Preescolar</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>Rionegro</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>14/05/2026 a las 14:17</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>Rionegro</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>ía de Educación: Rionegro</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>I.E QUEBRADA ARRIBA BALDOMERO SANIN CANO</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>I.E QUEBRADA ARRIBA BALDOMERO SANIN CANO-SEDE PPAL</t>
+        </is>
+      </c>
+      <c r="L145" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>QUEBRADA ARRIBA</t>
+        </is>
+      </c>
+      <c r="N145" t="inlineStr">
+        <is>
+          <t>ón: KR 57 D 52 14</t>
+        </is>
+      </c>
+      <c r="O145" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Preescolar</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>Rionegro</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>14/05/2026 a las 14:17</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>Rionegro</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>ía de Educación: Rionegro</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>I. E. CONCEJO MUNICIPAL EL PORVENIR</t>
+        </is>
+      </c>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>SEDE EDUARDO URIBE BOTERO</t>
+        </is>
+      </c>
+      <c r="L146" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M146" t="inlineStr">
+        <is>
+          <t>B. EL PORVENIR</t>
+        </is>
+      </c>
+      <c r="N146" t="inlineStr">
+        <is>
+          <t>ón: CRA. 65A 75A-01</t>
+        </is>
+      </c>
+      <c r="O146" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Preescolar</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>Rionegro</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>14/05/2026 a las 14:17</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>Rionegro</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>ía de Educación: Rionegro</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>I. E. GUILLERMO GAVIRIA CORREA</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>I. E. GUILLERMO GAVIRIA CORREA - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L147" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M147" t="inlineStr">
+        <is>
+          <t>VDA. YARUMAL</t>
+        </is>
+      </c>
+      <c r="N147" t="inlineStr">
+        <is>
+          <t>ón: VDA. YARUMAL</t>
+        </is>
+      </c>
+      <c r="O147" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Preescolar</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>Rionegro</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>14/05/2026 a las 14:18</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>Rionegro</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>ía de Educación: Rionegro</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>I. E. JOSEFINA MU OZ GONZALEZ</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>I. E. JOSEFINA MU OZ GONZALEZ -SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L148" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M148" t="inlineStr">
+        <is>
+          <t>BARRIO OBRERO</t>
+        </is>
+      </c>
+      <c r="N148" t="inlineStr">
+        <is>
+          <t>ón: KR 41 36 83</t>
+        </is>
+      </c>
+      <c r="O148" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Priorizadas para jóvenes entre 18 y 28 años</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Preescolar</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>Rionegro</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>14/05/2026 a las 14:18</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>Rionegro</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>ía de Educación: Rionegro</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>I. E. ESCUELA NORMAL SUPERIOR DE MARIA</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>I. E. ESCUELA NORMAL SUPERIOR DE MARIA - SEDE PRIN</t>
+        </is>
+      </c>
+      <c r="L149" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M149" t="inlineStr">
+        <is>
+          <t>BARRIO. SANTA ANA SECTOR SAN JOAQUIN</t>
+        </is>
+      </c>
+      <c r="N149" t="inlineStr">
+        <is>
+          <t>ón: CRA. 52 30-48</t>
+        </is>
+      </c>
+      <c r="O149" t="inlineStr">
         <is>
           <t>A</t>
         </is>

--- a/nuevas_plazas.xlsx
+++ b/nuevas_plazas.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O149"/>
+  <dimension ref="A1:O151"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11256,10 +11256,8 @@
           <t>14/05/2026 a las 14:17</t>
         </is>
       </c>
-      <c r="F145" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
+      <c r="F145" t="n">
+        <v>10</v>
       </c>
       <c r="G145" t="inlineStr">
         <is>
@@ -11333,10 +11331,8 @@
           <t>14/05/2026 a las 14:17</t>
         </is>
       </c>
-      <c r="F146" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
+      <c r="F146" t="n">
+        <v>9</v>
       </c>
       <c r="G146" t="inlineStr">
         <is>
@@ -11410,10 +11406,8 @@
           <t>14/05/2026 a las 14:17</t>
         </is>
       </c>
-      <c r="F147" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
+      <c r="F147" t="n">
+        <v>9</v>
       </c>
       <c r="G147" t="inlineStr">
         <is>
@@ -11487,10 +11481,8 @@
           <t>14/05/2026 a las 14:18</t>
         </is>
       </c>
-      <c r="F148" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="F148" t="n">
+        <v>8</v>
       </c>
       <c r="G148" t="inlineStr">
         <is>
@@ -11564,10 +11556,8 @@
           <t>14/05/2026 a las 14:18</t>
         </is>
       </c>
-      <c r="F149" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
+      <c r="F149" t="n">
+        <v>15</v>
       </c>
       <c r="G149" t="inlineStr">
         <is>
@@ -11610,6 +11600,160 @@
         </is>
       </c>
       <c r="O149" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Preescolar</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>Rionegro</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>20/05/2026 a las 07:20</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>Rionegro</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>ía de Educación: Rionegro</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>I. E. ANA GOMEZ DE SIERRA</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>I. E. ANA GOMEZ DE SIERRA - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L150" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M150" t="inlineStr">
+        <is>
+          <t>SECTOR LA MOSCA</t>
+        </is>
+      </c>
+      <c r="N150" t="inlineStr">
+        <is>
+          <t>ón: AUTOPISTA MEDELLIN/BOGOTA KM 34</t>
+        </is>
+      </c>
+      <c r="O150" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Preescolar</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>Rionegro</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>20/05/2026 a las 11:46</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>Rionegro</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>ía de Educación: Rionegro</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>I. E. ESCUELA NORMAL SUPERIOR DE MARIA</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>I. E. ESCUELA NORMAL SUPERIOR DE MARIA - SEDE PRIN</t>
+        </is>
+      </c>
+      <c r="L151" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M151" t="inlineStr">
+        <is>
+          <t>BARRIO. SANTA ANA SECTOR SAN JOAQUIN</t>
+        </is>
+      </c>
+      <c r="N151" t="inlineStr">
+        <is>
+          <t>ón: CRA. 52 30-48</t>
+        </is>
+      </c>
+      <c r="O151" t="inlineStr">
         <is>
           <t>A</t>
         </is>

--- a/nuevas_plazas.xlsx
+++ b/nuevas_plazas.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O151"/>
+  <dimension ref="A1:O165"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11631,10 +11631,8 @@
           <t>20/05/2026 a las 07:20</t>
         </is>
       </c>
-      <c r="F150" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
+      <c r="F150" t="n">
+        <v>74</v>
       </c>
       <c r="G150" t="inlineStr">
         <is>
@@ -11708,10 +11706,8 @@
           <t>20/05/2026 a las 11:46</t>
         </is>
       </c>
-      <c r="F151" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
+      <c r="F151" t="n">
+        <v>20</v>
       </c>
       <c r="G151" t="inlineStr">
         <is>
@@ -11754,6 +11750,1084 @@
         </is>
       </c>
       <c r="O151" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Ciencias sociales</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>21/05/2026 a las 10:44</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>ía de Educación: Medellín</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>INST EDUC MANUEL J. BETANCUR</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>INST EDUC MANUEL J. BETANCUR - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L152" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M152" t="inlineStr">
+        <is>
+          <t>Dirección: IND KR 81 # 43 SUR 38</t>
+        </is>
+      </c>
+      <c r="N152" t="inlineStr">
+        <is>
+          <t>ón: IND KR 81 # 43 SUR 38</t>
+        </is>
+      </c>
+      <c r="O152" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>Abejorral</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>21/05/2026 a las 11:54</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>Oriente</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>I. E. FUNDACION CELIA DUQUE DE DUQUE</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>C. E. R. VILLA INES</t>
+        </is>
+      </c>
+      <c r="L153" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M153" t="inlineStr">
+        <is>
+          <t>VDA. LA SALTADERA</t>
+        </is>
+      </c>
+      <c r="N153" t="inlineStr">
+        <is>
+          <t>ón: VDA LA SALTADERA</t>
+        </is>
+      </c>
+      <c r="O153" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>Cargo Docente orientador</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Sin asignación directa</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>Ituango</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>21/05/2026 a las 11:54</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>Ituango</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>I. E. R. LA PEREZ</t>
+        </is>
+      </c>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>I. E. R. LA PEREZ - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L154" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M154" t="inlineStr">
+        <is>
+          <t>VDA. QUEBRADA DEL MEDIO</t>
+        </is>
+      </c>
+      <c r="N154" t="inlineStr">
+        <is>
+          <t>ón: VDA. QUEBRADA DEL MEDIO</t>
+        </is>
+      </c>
+      <c r="O154" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>Remedios</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>21/05/2026 a las 11:54</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>Remedios</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>I. E. R. LA CRUZADA</t>
+        </is>
+      </c>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>C. E. R. CARRIZAL</t>
+        </is>
+      </c>
+      <c r="L155" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M155" t="inlineStr">
+        <is>
+          <t>VDA. CARRIZAL</t>
+        </is>
+      </c>
+      <c r="N155" t="inlineStr">
+        <is>
+          <t>ón: VDA CARRIZAL</t>
+        </is>
+      </c>
+      <c r="O155" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>Caucasia</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>21/05/2026 a las 11:54</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>Caucasia</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J156" t="inlineStr">
+        <is>
+          <t>C. E. R. KILOMETRO 18</t>
+        </is>
+      </c>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>EL TORO</t>
+        </is>
+      </c>
+      <c r="L156" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M156" t="inlineStr">
+        <is>
+          <t>Dirección: VDA EL TORO</t>
+        </is>
+      </c>
+      <c r="N156" t="inlineStr">
+        <is>
+          <t>ón: VDA EL TORO</t>
+        </is>
+      </c>
+      <c r="O156" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Matemáticas</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>Toledo</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>21/05/2026 a las 11:54</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>Toledo</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>I. E. J. EMILIO VALDERRAMA AGUDELO</t>
+        </is>
+      </c>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>I. E. R. LA FLORIDA</t>
+        </is>
+      </c>
+      <c r="L157" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M157" t="inlineStr">
+        <is>
+          <t>Dirección: VDA LA FLORIDA</t>
+        </is>
+      </c>
+      <c r="N157" t="inlineStr">
+        <is>
+          <t>ón: VDA LA FLORIDA</t>
+        </is>
+      </c>
+      <c r="O157" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Educación artística - artes plásticas</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>Santa Rosa De Osos</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>21/05/2026 a las 11:54</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>Santa Rosa de Osos</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>I.E. MARCO TOBON MEJIA</t>
+        </is>
+      </c>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>I.E. MARCO TOBON MEJIA - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L158" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M158" t="inlineStr">
+        <is>
+          <t>CL CAMELLON GONZALEZ</t>
+        </is>
+      </c>
+      <c r="N158" t="inlineStr">
+        <is>
+          <t>ón: CL 27 26 92</t>
+        </is>
+      </c>
+      <c r="O158" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>Caucasia</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>21/05/2026 a las 11:55</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>Caucasia</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>C. E. R. RIVERAS DEL CAUCA</t>
+        </is>
+      </c>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>C. E. R. RIVERAS DEL CAUCA - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L159" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M159" t="inlineStr">
+        <is>
+          <t>CORREG. LA PALANCA</t>
+        </is>
+      </c>
+      <c r="N159" t="inlineStr">
+        <is>
+          <t>ón: CORREG. LA PALANCA</t>
+        </is>
+      </c>
+      <c r="O159" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Humanidades y lengua castellana</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>Ituango</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>21/05/2026 a las 11:55</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>Ituango</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>I. E. JESUS MARIA VALLE JARAMILLO</t>
+        </is>
+      </c>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>C. E. R. EL OLIVAR</t>
+        </is>
+      </c>
+      <c r="L160" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M160" t="inlineStr">
+        <is>
+          <t>VDA. EL OLIVAR</t>
+        </is>
+      </c>
+      <c r="N160" t="inlineStr">
+        <is>
+          <t>ón: VDA. EL OLIVAR</t>
+        </is>
+      </c>
+      <c r="O160" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Ciencias naturales y educación ambiental</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>Sonsón</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>21/05/2026 a las 11:55</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>Sonsón</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J161" t="inlineStr">
+        <is>
+          <t>I. E. ESCUELA NORMAL SUPERIOR PRESBITERO JOSE GOMEZ ISAZA</t>
+        </is>
+      </c>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>C. E. R. EL RODEO</t>
+        </is>
+      </c>
+      <c r="L161" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M161" t="inlineStr">
+        <is>
+          <t>VDA. EL RODEO</t>
+        </is>
+      </c>
+      <c r="N161" t="inlineStr">
+        <is>
+          <t>ón: VDA EL RODEO</t>
+        </is>
+      </c>
+      <c r="O161" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>Humanidades y lengua castellana</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>Tarazá</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>21/05/2026 a las 11:55</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>Tarazá</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J162" t="inlineStr">
+        <is>
+          <t>I. E. ANTONIO ROLDAN BETANCUR</t>
+        </is>
+      </c>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>COLEGIO ANTONIO ROLDAN BETANCUR - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L162" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M162" t="inlineStr">
+        <is>
+          <t>BARRIO. GARZON</t>
+        </is>
+      </c>
+      <c r="N162" t="inlineStr">
+        <is>
+          <t>ón: KR 36 32 114</t>
+        </is>
+      </c>
+      <c r="O162" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>Angostura</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>21/05/2026 a las 11:55</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>Angostura</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J163" t="inlineStr">
+        <is>
+          <t>C. E. R. SAN FERNANDO</t>
+        </is>
+      </c>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>C. E. R. EL ORIENTE</t>
+        </is>
+      </c>
+      <c r="L163" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M163" t="inlineStr">
+        <is>
+          <t>VDA. EL ORIENTE</t>
+        </is>
+      </c>
+      <c r="N163" t="inlineStr">
+        <is>
+          <t>ón: VDA EL ORIENTE</t>
+        </is>
+      </c>
+      <c r="O163" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Priorizadas para jóvenes entre 18 y 28 años</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Ciencias sociales</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>Yolombó</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>21/05/2026 a las 11:55</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>Yolombó</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J164" t="inlineStr">
+        <is>
+          <t>I. E. ESCUELA NORMAL SUPERIOR DEL NORDESTE</t>
+        </is>
+      </c>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>I. E. ESCUELA NORMAL SUPERIOR DEL NORDESTE - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L164" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M164" t="inlineStr">
+        <is>
+          <t>B. EL CARIÑO</t>
+        </is>
+      </c>
+      <c r="N164" t="inlineStr">
+        <is>
+          <t>ón: CL 15 18 57</t>
+        </is>
+      </c>
+      <c r="O164" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>Educación artística - artes escénicas</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>Ciudad Bolívar</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>21/05/2026 a las 11:55</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>Suroeste</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J165" t="inlineStr">
+        <is>
+          <t>I. E. SAN JOSE DEL CITARA</t>
+        </is>
+      </c>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>LICEO SAN JOSE DEL CITARA - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L165" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M165" t="inlineStr">
+        <is>
+          <t>B. UNICO</t>
+        </is>
+      </c>
+      <c r="N165" t="inlineStr">
+        <is>
+          <t>ón: KR 47 B 46 A 139</t>
+        </is>
+      </c>
+      <c r="O165" t="inlineStr">
         <is>
           <t>A</t>
         </is>

--- a/nuevas_plazas.xlsx
+++ b/nuevas_plazas.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O165"/>
+  <dimension ref="A1:O166"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11781,10 +11781,8 @@
           <t>21/05/2026 a las 10:44</t>
         </is>
       </c>
-      <c r="F152" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
+      <c r="F152" t="n">
+        <v>41</v>
       </c>
       <c r="G152" t="inlineStr">
         <is>
@@ -11858,10 +11856,8 @@
           <t>21/05/2026 a las 11:54</t>
         </is>
       </c>
-      <c r="F153" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
+      <c r="F153" t="n">
+        <v>9</v>
       </c>
       <c r="G153" t="inlineStr">
         <is>
@@ -11935,10 +11931,8 @@
           <t>21/05/2026 a las 11:54</t>
         </is>
       </c>
-      <c r="F154" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="F154" t="n">
+        <v>5</v>
       </c>
       <c r="G154" t="inlineStr">
         <is>
@@ -12012,10 +12006,8 @@
           <t>21/05/2026 a las 11:54</t>
         </is>
       </c>
-      <c r="F155" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="F155" t="n">
+        <v>6</v>
       </c>
       <c r="G155" t="inlineStr">
         <is>
@@ -12089,10 +12081,8 @@
           <t>21/05/2026 a las 11:54</t>
         </is>
       </c>
-      <c r="F156" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
+      <c r="F156" t="n">
+        <v>7</v>
       </c>
       <c r="G156" t="inlineStr">
         <is>
@@ -12166,10 +12156,8 @@
           <t>21/05/2026 a las 11:54</t>
         </is>
       </c>
-      <c r="F157" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
+      <c r="F157" t="n">
+        <v>7</v>
       </c>
       <c r="G157" t="inlineStr">
         <is>
@@ -12243,10 +12231,8 @@
           <t>21/05/2026 a las 11:54</t>
         </is>
       </c>
-      <c r="F158" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="F158" t="n">
+        <v>6</v>
       </c>
       <c r="G158" t="inlineStr">
         <is>
@@ -12320,10 +12306,8 @@
           <t>21/05/2026 a las 11:55</t>
         </is>
       </c>
-      <c r="F159" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="F159" t="n">
+        <v>6</v>
       </c>
       <c r="G159" t="inlineStr">
         <is>
@@ -12397,10 +12381,8 @@
           <t>21/05/2026 a las 11:55</t>
         </is>
       </c>
-      <c r="F160" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="F160" t="n">
+        <v>3</v>
       </c>
       <c r="G160" t="inlineStr">
         <is>
@@ -12474,10 +12456,8 @@
           <t>21/05/2026 a las 11:55</t>
         </is>
       </c>
-      <c r="F161" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="F161" t="n">
+        <v>8</v>
       </c>
       <c r="G161" t="inlineStr">
         <is>
@@ -12551,10 +12531,8 @@
           <t>21/05/2026 a las 11:55</t>
         </is>
       </c>
-      <c r="F162" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="F162" t="n">
+        <v>6</v>
       </c>
       <c r="G162" t="inlineStr">
         <is>
@@ -12628,10 +12606,8 @@
           <t>21/05/2026 a las 11:55</t>
         </is>
       </c>
-      <c r="F163" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="F163" t="n">
+        <v>6</v>
       </c>
       <c r="G163" t="inlineStr">
         <is>
@@ -12705,10 +12681,8 @@
           <t>21/05/2026 a las 11:55</t>
         </is>
       </c>
-      <c r="F164" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="F164" t="n">
+        <v>8</v>
       </c>
       <c r="G164" t="inlineStr">
         <is>
@@ -12782,10 +12756,8 @@
           <t>21/05/2026 a las 11:55</t>
         </is>
       </c>
-      <c r="F165" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F165" t="n">
+        <v>0</v>
       </c>
       <c r="G165" t="inlineStr">
         <is>
@@ -12828,6 +12800,83 @@
         </is>
       </c>
       <c r="O165" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>Educación ética y en valores</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>Rionegro</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>23/05/2026 a las 10:25</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>Rionegro</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>ía de Educación: Rionegro</t>
+        </is>
+      </c>
+      <c r="J166" t="inlineStr">
+        <is>
+          <t>I. E. JOSE MARIA CORDOBA</t>
+        </is>
+      </c>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>I. E. LICEO JOSE MARIA CORDOBA - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L166" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M166" t="inlineStr">
+        <is>
+          <t>ALTOS DE LA PEREIRA</t>
+        </is>
+      </c>
+      <c r="N166" t="inlineStr">
+        <is>
+          <t>ón: CR 52 40-86</t>
+        </is>
+      </c>
+      <c r="O166" t="inlineStr">
         <is>
           <t>A</t>
         </is>

--- a/nuevas_plazas.xlsx
+++ b/nuevas_plazas.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O166"/>
+  <dimension ref="A1:O168"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12831,10 +12831,8 @@
           <t>23/05/2026 a las 10:25</t>
         </is>
       </c>
-      <c r="F166" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
+      <c r="F166" t="n">
+        <v>28</v>
       </c>
       <c r="G166" t="inlineStr">
         <is>
@@ -12877,6 +12875,160 @@
         </is>
       </c>
       <c r="O166" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>Turbo</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>28/05/2026 a las 15:36</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>Turbo</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>ía de Educación: Turbo</t>
+        </is>
+      </c>
+      <c r="J167" t="inlineStr">
+        <is>
+          <t>I.E. Pueblo Bello</t>
+        </is>
+      </c>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>Sede San Pablo Tulapa</t>
+        </is>
+      </c>
+      <c r="L167" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M167" t="inlineStr">
+        <is>
+          <t>Dirección: VDA. SAN PABLO TULAPA</t>
+        </is>
+      </c>
+      <c r="N167" t="inlineStr">
+        <is>
+          <t>ón: VDA. SAN PABLO TULAPA</t>
+        </is>
+      </c>
+      <c r="O167" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>Tecnología e informática</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>Turbo</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>28/05/2026 a las 15:36</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>Turbo</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>ía de Educación: Turbo</t>
+        </is>
+      </c>
+      <c r="J168" t="inlineStr">
+        <is>
+          <t>I.E. Pueblo Bello</t>
+        </is>
+      </c>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>I.E. Pueblo Bello - Sede Principal</t>
+        </is>
+      </c>
+      <c r="L168" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M168" t="inlineStr">
+        <is>
+          <t>Dirección: CORREG. PUEBLO BELLO</t>
+        </is>
+      </c>
+      <c r="N168" t="inlineStr">
+        <is>
+          <t>ón: CORREG. PUEBLO BELLO</t>
+        </is>
+      </c>
+      <c r="O168" t="inlineStr">
         <is>
           <t>A</t>
         </is>

--- a/nuevas_plazas.xlsx
+++ b/nuevas_plazas.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O168"/>
+  <dimension ref="A1:O169"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12906,10 +12906,8 @@
           <t>28/05/2026 a las 15:36</t>
         </is>
       </c>
-      <c r="F167" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
+      <c r="F167" t="n">
+        <v>25</v>
       </c>
       <c r="G167" t="inlineStr">
         <is>
@@ -12983,10 +12981,8 @@
           <t>28/05/2026 a las 15:36</t>
         </is>
       </c>
-      <c r="F168" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
+      <c r="F168" t="n">
+        <v>19</v>
       </c>
       <c r="G168" t="inlineStr">
         <is>
@@ -13029,6 +13025,83 @@
         </is>
       </c>
       <c r="O168" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>Educación ética y en valores</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>Rionegro</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>29/05/2026 a las 08:27</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>Rionegro</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>ía de Educación: Rionegro</t>
+        </is>
+      </c>
+      <c r="J169" t="inlineStr">
+        <is>
+          <t>I. E. JOSE MARIA CORDOBA</t>
+        </is>
+      </c>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>I. E. LICEO JOSE MARIA CORDOBA - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L169" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M169" t="inlineStr">
+        <is>
+          <t>ALTOS DE LA PEREIRA</t>
+        </is>
+      </c>
+      <c r="N169" t="inlineStr">
+        <is>
+          <t>ón: CR 52 40-86</t>
+        </is>
+      </c>
+      <c r="O169" t="inlineStr">
         <is>
           <t>A</t>
         </is>

--- a/nuevas_plazas.xlsx
+++ b/nuevas_plazas.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O169"/>
+  <dimension ref="A1:O170"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13056,10 +13056,8 @@
           <t>29/05/2026 a las 08:27</t>
         </is>
       </c>
-      <c r="F169" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
+      <c r="F169" t="n">
+        <v>27</v>
       </c>
       <c r="G169" t="inlineStr">
         <is>
@@ -13102,6 +13100,83 @@
         </is>
       </c>
       <c r="O169" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>Itaguí</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>29/05/2026 a las 15:47</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>Itaguí</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>ía de Educación: Itaguí</t>
+        </is>
+      </c>
+      <c r="J170" t="inlineStr">
+        <is>
+          <t>INSTITUCION EDUCATIVA ANTONIO JOSE DE SUCRE</t>
+        </is>
+      </c>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>INSTITUCION EDUCATIVA ANTONIO JOSE DE SUCRE SEDE P</t>
+        </is>
+      </c>
+      <c r="L170" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M170" t="inlineStr">
+        <is>
+          <t>Dirección: CL 37 42 10</t>
+        </is>
+      </c>
+      <c r="N170" t="inlineStr">
+        <is>
+          <t>ón: CL 37 42 10</t>
+        </is>
+      </c>
+      <c r="O170" t="inlineStr">
         <is>
           <t>A</t>
         </is>

--- a/nuevas_plazas.xlsx
+++ b/nuevas_plazas.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O170"/>
+  <dimension ref="A1:O171"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13131,10 +13131,8 @@
           <t>29/05/2026 a las 15:47</t>
         </is>
       </c>
-      <c r="F170" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
+      <c r="F170" t="n">
+        <v>68</v>
       </c>
       <c r="G170" t="inlineStr">
         <is>
@@ -13177,6 +13175,83 @@
         </is>
       </c>
       <c r="O170" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>Ciencias naturales y educación ambiental</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>Sonsón</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>30/05/2026 a las 11:25</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>Sonsón</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J171" t="inlineStr">
+        <is>
+          <t>I. E. ESCUELA NORMAL SUPERIOR PRESBITERO JOSE GOMEZ ISAZA</t>
+        </is>
+      </c>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>C. E. R. EL RODEO</t>
+        </is>
+      </c>
+      <c r="L171" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M171" t="inlineStr">
+        <is>
+          <t>VDA. EL RODEO</t>
+        </is>
+      </c>
+      <c r="N171" t="inlineStr">
+        <is>
+          <t>ón: VDA EL RODEO</t>
+        </is>
+      </c>
+      <c r="O171" t="inlineStr">
         <is>
           <t>A</t>
         </is>

--- a/nuevas_plazas.xlsx
+++ b/nuevas_plazas.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O171"/>
+  <dimension ref="A1:O174"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13206,10 +13206,8 @@
           <t>30/05/2026 a las 11:25</t>
         </is>
       </c>
-      <c r="F171" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
+      <c r="F171" t="n">
+        <v>36</v>
       </c>
       <c r="G171" t="inlineStr">
         <is>
@@ -13252,6 +13250,237 @@
         </is>
       </c>
       <c r="O171" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>Idioma extranjero inglés</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>02/06/2026 a las 14:42</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>ía de Educación: Medellín</t>
+        </is>
+      </c>
+      <c r="J172" t="inlineStr">
+        <is>
+          <t>INST EDUC GABRIEL RESTREPO MORENO</t>
+        </is>
+      </c>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>INST EDUC GABRIEL RESTREPO MORENO - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L172" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M172" t="inlineStr">
+        <is>
+          <t>Dirección: KR 39 A 85 59</t>
+        </is>
+      </c>
+      <c r="N172" t="inlineStr">
+        <is>
+          <t>ón: KR 39 A 85 59</t>
+        </is>
+      </c>
+      <c r="O172" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>Preescolar</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>Rionegro</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>02/06/2026 a las 14:44</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>Rionegro</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>ía de Educación: Rionegro</t>
+        </is>
+      </c>
+      <c r="J173" t="inlineStr">
+        <is>
+          <t>I. E. CONCEJO MUNICIPAL EL PORVENIR</t>
+        </is>
+      </c>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>SEDE EDUARDO URIBE BOTERO</t>
+        </is>
+      </c>
+      <c r="L173" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M173" t="inlineStr">
+        <is>
+          <t>B. EL PORVENIR</t>
+        </is>
+      </c>
+      <c r="N173" t="inlineStr">
+        <is>
+          <t>ón: CRA. 65A 75A-01</t>
+        </is>
+      </c>
+      <c r="O173" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>Idioma extranjero inglés</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>Envigado</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>02/06/2026 a las 15:38</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>Envigado</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>ía de Educación: Envigado</t>
+        </is>
+      </c>
+      <c r="J174" t="inlineStr">
+        <is>
+          <t>I. E. JOSE MANUEL RESTREPO VELEZ</t>
+        </is>
+      </c>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>SEDE JOSE MANUEL RESTREPO VELEZ</t>
+        </is>
+      </c>
+      <c r="L174" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M174" t="inlineStr">
+        <is>
+          <t>Dirección: CL 38 S 45 A 67</t>
+        </is>
+      </c>
+      <c r="N174" t="inlineStr">
+        <is>
+          <t>ón: CL 38 S 45 A 67</t>
+        </is>
+      </c>
+      <c r="O174" t="inlineStr">
         <is>
           <t>A</t>
         </is>

--- a/nuevas_plazas.xlsx
+++ b/nuevas_plazas.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O174"/>
+  <dimension ref="A1:O190"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13281,10 +13281,8 @@
           <t>02/06/2026 a las 14:42</t>
         </is>
       </c>
-      <c r="F172" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
+      <c r="F172" t="n">
+        <v>12</v>
       </c>
       <c r="G172" t="inlineStr">
         <is>
@@ -13358,10 +13356,8 @@
           <t>02/06/2026 a las 14:44</t>
         </is>
       </c>
-      <c r="F173" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
+      <c r="F173" t="n">
+        <v>37</v>
       </c>
       <c r="G173" t="inlineStr">
         <is>
@@ -13435,10 +13431,8 @@
           <t>02/06/2026 a las 15:38</t>
         </is>
       </c>
-      <c r="F174" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="F174" t="n">
+        <v>2</v>
       </c>
       <c r="G174" t="inlineStr">
         <is>
@@ -13481,6 +13475,1238 @@
         </is>
       </c>
       <c r="O174" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>Yondó</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>04/06/2026 a las 10:03</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>Yondó</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J175" t="inlineStr">
+        <is>
+          <t>I. E. R. SAN MIGUEL DEL TIGRE</t>
+        </is>
+      </c>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>C. E. R. CIENAGA</t>
+        </is>
+      </c>
+      <c r="L175" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M175" t="inlineStr">
+        <is>
+          <t>VDA. CIENAGA DE BARBACOAS</t>
+        </is>
+      </c>
+      <c r="N175" t="inlineStr">
+        <is>
+          <t>ón: VDA CIENAGA DE BARBACOAS</t>
+        </is>
+      </c>
+      <c r="O175" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>Ciencias naturales y educación ambiental</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>El Bagre</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>04/06/2026 a las 10:03</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>El Bagre</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J176" t="inlineStr">
+        <is>
+          <t>I. E. 20 DE JULIO</t>
+        </is>
+      </c>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>COLEGIO VEINTE DE JULIO - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L176" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M176" t="inlineStr">
+        <is>
+          <t>BARRIO. 20 DE JULIO</t>
+        </is>
+      </c>
+      <c r="N176" t="inlineStr">
+        <is>
+          <t>ón: KR 41 48 B 31</t>
+        </is>
+      </c>
+      <c r="O176" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>Cargo Docente Orientador</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>Sin asignación directa</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>Caucasia</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>04/06/2026 a las 10:03</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>Caucasia</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J177" t="inlineStr">
+        <is>
+          <t>C. E. R. SANTA ROSITA</t>
+        </is>
+      </c>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>C. E. R. SANTA ROSITA - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L177" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M177" t="inlineStr">
+        <is>
+          <t>VDA. SANTA ROSITA</t>
+        </is>
+      </c>
+      <c r="N177" t="inlineStr">
+        <is>
+          <t>ón: VDA. SANTA ROSITA</t>
+        </is>
+      </c>
+      <c r="O177" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>Cargo Docente Orientador</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>Sin asignación directa</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>Caucasia</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>04/06/2026 a las 10:03</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>Caucasia</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J178" t="inlineStr">
+        <is>
+          <t>C. E. R. KILOMETRO 18</t>
+        </is>
+      </c>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>E R I KILOMETRO 18 - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L178" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M178" t="inlineStr">
+        <is>
+          <t>KM. 18</t>
+        </is>
+      </c>
+      <c r="N178" t="inlineStr">
+        <is>
+          <t>ón: VDA KILOMETRO 18</t>
+        </is>
+      </c>
+      <c r="O178" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>Idioma extranjero inglés</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>Zaragoza</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>04/06/2026 a las 10:03</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>Zaragoza</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J179" t="inlineStr">
+        <is>
+          <t>I. E. SANTO CRISTO DE ZARAGOZA</t>
+        </is>
+      </c>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>LICEO SANTO CRISTO DE ZARAGOZA - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L179" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M179" t="inlineStr">
+        <is>
+          <t>SANTA ELENA</t>
+        </is>
+      </c>
+      <c r="N179" t="inlineStr">
+        <is>
+          <t>ón: CLL 39B 37 10</t>
+        </is>
+      </c>
+      <c r="O179" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Priorizadas para jóvenes entre 18 y 28 años</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>Preescolar</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>Remedios</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>04/06/2026 a las 10:03</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>Remedios</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J180" t="inlineStr">
+        <is>
+          <t>I. E. LLANO DE CORDOBA</t>
+        </is>
+      </c>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>I. E. LLANO DE CORDOBA - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L180" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M180" t="inlineStr">
+        <is>
+          <t>KR 18 9 271</t>
+        </is>
+      </c>
+      <c r="N180" t="inlineStr">
+        <is>
+          <t>ón: KR 18 9 271</t>
+        </is>
+      </c>
+      <c r="O180" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Priorizadas para jóvenes entre 18 y 28 años</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>Educación física, recreación y deporte</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>Caucasia</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>04/06/2026 a las 10:03</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>Caucasia</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J181" t="inlineStr">
+        <is>
+          <t>I. E. LICEO CONCEJO MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>LICEO CONCEJO MUNICIPAL - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L181" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M181" t="inlineStr">
+        <is>
+          <t>EL PAJONAL</t>
+        </is>
+      </c>
+      <c r="N181" t="inlineStr">
+        <is>
+          <t>ón: IND CARRET.TRONCAL CON AV. EL PAJONAL</t>
+        </is>
+      </c>
+      <c r="O181" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>Idioma extranjero inglés</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>Puerto Nare</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>04/06/2026 a las 10:03</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>Puerto Nare</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J182" t="inlineStr">
+        <is>
+          <t>INSTITUCION EDUCATIVA RURAL JORGE ENRIQUE VILLEGAS</t>
+        </is>
+      </c>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>I. E. R JORGE ENRIQUE VILLEGAS - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L182" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M182" t="inlineStr">
+        <is>
+          <t>CORREG. LA PESCA</t>
+        </is>
+      </c>
+      <c r="N182" t="inlineStr">
+        <is>
+          <t>ón: KR 10 01 60</t>
+        </is>
+      </c>
+      <c r="O182" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>Ciencias naturales y educación ambiental</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>Cáceres</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>04/06/2026 a las 10:03</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>Cáceres</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J183" t="inlineStr">
+        <is>
+          <t>I. E. R. EL TIGRE</t>
+        </is>
+      </c>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>E R I MURIBA</t>
+        </is>
+      </c>
+      <c r="L183" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M183" t="inlineStr">
+        <is>
+          <t>VDA. MURIBA</t>
+        </is>
+      </c>
+      <c r="N183" t="inlineStr">
+        <is>
+          <t>ón: VDA. MURIBA</t>
+        </is>
+      </c>
+      <c r="O183" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>Ituango</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>04/06/2026 a las 10:03</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>Ituango</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J184" t="inlineStr">
+        <is>
+          <t>I. E. LUIS MARIA PRECIADO ECHAVARRIA</t>
+        </is>
+      </c>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>C. E. R. LOS VENADOS</t>
+        </is>
+      </c>
+      <c r="L184" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M184" t="inlineStr">
+        <is>
+          <t>VDA. LOS VENADOS</t>
+        </is>
+      </c>
+      <c r="N184" t="inlineStr">
+        <is>
+          <t>ón: VDA. LOS VENADOS</t>
+        </is>
+      </c>
+      <c r="O184" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>Ciencias sociales</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>Nechí</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>04/06/2026 a las 10:03</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>Nechí</t>
+        </is>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J185" t="inlineStr">
+        <is>
+          <t>I.E.R TRINIDAD ARRIBA</t>
+        </is>
+      </c>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>C. E. R. TRINIDAD ABAJO</t>
+        </is>
+      </c>
+      <c r="L185" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M185" t="inlineStr">
+        <is>
+          <t>Dirección: VDA TRINIDAD ABAJO</t>
+        </is>
+      </c>
+      <c r="N185" t="inlineStr">
+        <is>
+          <t>ón: VDA TRINIDAD ABAJO</t>
+        </is>
+      </c>
+      <c r="O185" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>Filosofía</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>Segovia</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>04/06/2026 a las 10:03</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>Segovia</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J186" t="inlineStr">
+        <is>
+          <t>I. E. LIBORIO BATALLER</t>
+        </is>
+      </c>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>C.E.R CUTURU MEDIO</t>
+        </is>
+      </c>
+      <c r="L186" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M186" t="inlineStr">
+        <is>
+          <t>Dirección: VDA CUTURU MEDIO</t>
+        </is>
+      </c>
+      <c r="N186" t="inlineStr">
+        <is>
+          <t>ón: VDA CUTURU MEDIO</t>
+        </is>
+      </c>
+      <c r="O186" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>Ciencias naturales y educación ambiental</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>Vegachí</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>04/06/2026 a las 10:03</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>Vegachí</t>
+        </is>
+      </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I187" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J187" t="inlineStr">
+        <is>
+          <t>I. E. EFE GOMEZ</t>
+        </is>
+      </c>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>LICEO EFE GOMEZ - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L187" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M187" t="inlineStr">
+        <is>
+          <t>CABECEERA MPAL</t>
+        </is>
+      </c>
+      <c r="N187" t="inlineStr">
+        <is>
+          <t>ón: KR 47 50 40</t>
+        </is>
+      </c>
+      <c r="O187" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>Amalfi</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>04/06/2026 a las 10:03</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>Amalfi</t>
+        </is>
+      </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I188" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J188" t="inlineStr">
+        <is>
+          <t>I. E. R. PORTACHUELO</t>
+        </is>
+      </c>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>I. E. R. LA PICARDIA</t>
+        </is>
+      </c>
+      <c r="L188" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M188" t="inlineStr">
+        <is>
+          <t>VDA. LA PICARDIA</t>
+        </is>
+      </c>
+      <c r="N188" t="inlineStr">
+        <is>
+          <t>ón: VDA LA PICARDIA</t>
+        </is>
+      </c>
+      <c r="O188" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>Idioma extranjero inglés</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>Arboletes</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>04/06/2026 a las 10:03</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>Arboletes</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I189" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J189" t="inlineStr">
+        <is>
+          <t>I. E. JOSE MANUEL RESTREPO</t>
+        </is>
+      </c>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>COLEGIO JOSE MANUEL RESTREPO - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L189" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M189" t="inlineStr">
+        <is>
+          <t>BRR KENNEDY</t>
+        </is>
+      </c>
+      <c r="N189" t="inlineStr">
+        <is>
+          <t>ón: KR 33 27 51</t>
+        </is>
+      </c>
+      <c r="O189" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>San Pedro De Urabá</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>04/06/2026 a las 10:03</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>San Pedro de Urabá</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J190" t="inlineStr">
+        <is>
+          <t>I. E. R. SANTA CATALINA</t>
+        </is>
+      </c>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>C.E.R LOS OLIVOS</t>
+        </is>
+      </c>
+      <c r="L190" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M190" t="inlineStr">
+        <is>
+          <t>Dirección: VDA. CABAÑA ARRIBA</t>
+        </is>
+      </c>
+      <c r="N190" t="inlineStr">
+        <is>
+          <t>ón: VDA. CABAÑA ARRIBA</t>
+        </is>
+      </c>
+      <c r="O190" t="inlineStr">
         <is>
           <t>A</t>
         </is>

--- a/nuevas_plazas.xlsx
+++ b/nuevas_plazas.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O190"/>
+  <dimension ref="A1:O202"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13506,10 +13506,8 @@
           <t>04/06/2026 a las 10:03</t>
         </is>
       </c>
-      <c r="F175" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
+      <c r="F175" t="n">
+        <v>23</v>
       </c>
       <c r="G175" t="inlineStr">
         <is>
@@ -13583,10 +13581,8 @@
           <t>04/06/2026 a las 10:03</t>
         </is>
       </c>
-      <c r="F176" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
+      <c r="F176" t="n">
+        <v>10</v>
       </c>
       <c r="G176" t="inlineStr">
         <is>
@@ -13660,10 +13656,8 @@
           <t>04/06/2026 a las 10:03</t>
         </is>
       </c>
-      <c r="F177" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
+      <c r="F177" t="n">
+        <v>16</v>
       </c>
       <c r="G177" t="inlineStr">
         <is>
@@ -13737,10 +13731,8 @@
           <t>04/06/2026 a las 10:03</t>
         </is>
       </c>
-      <c r="F178" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
+      <c r="F178" t="n">
+        <v>19</v>
       </c>
       <c r="G178" t="inlineStr">
         <is>
@@ -13814,10 +13806,8 @@
           <t>04/06/2026 a las 10:03</t>
         </is>
       </c>
-      <c r="F179" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
+      <c r="F179" t="n">
+        <v>9</v>
       </c>
       <c r="G179" t="inlineStr">
         <is>
@@ -13891,10 +13881,8 @@
           <t>04/06/2026 a las 10:03</t>
         </is>
       </c>
-      <c r="F180" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
+      <c r="F180" t="n">
+        <v>21</v>
       </c>
       <c r="G180" t="inlineStr">
         <is>
@@ -13968,10 +13956,8 @@
           <t>04/06/2026 a las 10:03</t>
         </is>
       </c>
-      <c r="F181" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
+      <c r="F181" t="n">
+        <v>24</v>
       </c>
       <c r="G181" t="inlineStr">
         <is>
@@ -14045,10 +14031,8 @@
           <t>04/06/2026 a las 10:03</t>
         </is>
       </c>
-      <c r="F182" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="F182" t="n">
+        <v>6</v>
       </c>
       <c r="G182" t="inlineStr">
         <is>
@@ -14122,10 +14106,8 @@
           <t>04/06/2026 a las 10:03</t>
         </is>
       </c>
-      <c r="F183" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="F183" t="n">
+        <v>8</v>
       </c>
       <c r="G183" t="inlineStr">
         <is>
@@ -14199,10 +14181,8 @@
           <t>04/06/2026 a las 10:03</t>
         </is>
       </c>
-      <c r="F184" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
+      <c r="F184" t="n">
+        <v>21</v>
       </c>
       <c r="G184" t="inlineStr">
         <is>
@@ -14276,10 +14256,8 @@
           <t>04/06/2026 a las 10:03</t>
         </is>
       </c>
-      <c r="F185" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
+      <c r="F185" t="n">
+        <v>18</v>
       </c>
       <c r="G185" t="inlineStr">
         <is>
@@ -14353,10 +14331,8 @@
           <t>04/06/2026 a las 10:03</t>
         </is>
       </c>
-      <c r="F186" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
+      <c r="F186" t="n">
+        <v>13</v>
       </c>
       <c r="G186" t="inlineStr">
         <is>
@@ -14430,10 +14406,8 @@
           <t>04/06/2026 a las 10:03</t>
         </is>
       </c>
-      <c r="F187" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="F187" t="n">
+        <v>8</v>
       </c>
       <c r="G187" t="inlineStr">
         <is>
@@ -14507,10 +14481,8 @@
           <t>04/06/2026 a las 10:03</t>
         </is>
       </c>
-      <c r="F188" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
+      <c r="F188" t="n">
+        <v>26</v>
       </c>
       <c r="G188" t="inlineStr">
         <is>
@@ -14584,10 +14556,8 @@
           <t>04/06/2026 a las 10:03</t>
         </is>
       </c>
-      <c r="F189" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
+      <c r="F189" t="n">
+        <v>9</v>
       </c>
       <c r="G189" t="inlineStr">
         <is>
@@ -14661,10 +14631,8 @@
           <t>04/06/2026 a las 10:03</t>
         </is>
       </c>
-      <c r="F190" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
+      <c r="F190" t="n">
+        <v>32</v>
       </c>
       <c r="G190" t="inlineStr">
         <is>
@@ -14707,6 +14675,930 @@
         </is>
       </c>
       <c r="O190" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>Cargo Docente tutor (Planta Temporal PTA)</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>Betulia</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>05/06/2026 a las 15:04</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>Betulia</t>
+        </is>
+      </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J191" t="inlineStr">
+        <is>
+          <t>I E FRANCISCO CESAR</t>
+        </is>
+      </c>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>E U FRANCISCO CESAR</t>
+        </is>
+      </c>
+      <c r="L191" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M191" t="inlineStr">
+        <is>
+          <t>CORREG. DE ALTAMIRA</t>
+        </is>
+      </c>
+      <c r="N191" t="inlineStr">
+        <is>
+          <t>ón: CORREG.DE ALTAMIRA</t>
+        </is>
+      </c>
+      <c r="O191" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>Cargo Docente tutor (Planta Temporal PTA)</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>Cañasgordas</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>05/06/2026 a las 15:04</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>Cañasgordas</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I192" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J192" t="inlineStr">
+        <is>
+          <t>I. E. NICOLAS GAVIRIA</t>
+        </is>
+      </c>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>COLEGIO NICOLAS GAVIRIA - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L192" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M192" t="inlineStr">
+        <is>
+          <t>BRR IMANTANGO</t>
+        </is>
+      </c>
+      <c r="N192" t="inlineStr">
+        <is>
+          <t>ón: KR 26 47 84</t>
+        </is>
+      </c>
+      <c r="O192" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>Cargo Docente tutor (Planta Temporal PTA)</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>Carepa</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>05/06/2026 a las 15:04</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>Carepa</t>
+        </is>
+      </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I193" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J193" t="inlineStr">
+        <is>
+          <t>C. E. R. 25 DE AGOSTO</t>
+        </is>
+      </c>
+      <c r="K193" t="inlineStr">
+        <is>
+          <t>C. E. R. 25 DE AGOSTO - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L193" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M193" t="inlineStr">
+        <is>
+          <t>VDA.25 DE AGOSTO</t>
+        </is>
+      </c>
+      <c r="N193" t="inlineStr">
+        <is>
+          <t>ón: VDA.25 DE AGOSTO</t>
+        </is>
+      </c>
+      <c r="O193" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>Cargo Docente tutor (Planta Temporal PTA)</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>Copacabana</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>05/06/2026 a las 15:04</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>Valle del Aburrá</t>
+        </is>
+      </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J194" t="inlineStr">
+        <is>
+          <t>I. E. JOSE MIGUEL DE RESTREPO Y PUERTA</t>
+        </is>
+      </c>
+      <c r="K194" t="inlineStr">
+        <is>
+          <t>COLEGIO JOSE MIGUEL DE RESTREPO Y PUERTA - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L194" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M194" t="inlineStr">
+        <is>
+          <t>BR SAN FRANCISCO</t>
+        </is>
+      </c>
+      <c r="N194" t="inlineStr">
+        <is>
+          <t>ón: KR 47 47 A 05</t>
+        </is>
+      </c>
+      <c r="O194" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>Cargo Docente tutor (Planta Temporal PTA)</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>Hispania</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>05/06/2026 a las 15:04</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>Suroeste</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J195" t="inlineStr">
+        <is>
+          <t>I. E. AURA MARIA VALENCIA</t>
+        </is>
+      </c>
+      <c r="K195" t="inlineStr">
+        <is>
+          <t>I. E. AURA MARIA VALENCIA - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L195" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M195" t="inlineStr">
+        <is>
+          <t>CL. 50 47 08 PRIMARIA</t>
+        </is>
+      </c>
+      <c r="N195" t="inlineStr">
+        <is>
+          <t>ón: CL 49 52 51</t>
+        </is>
+      </c>
+      <c r="O195" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>Cargo Docente tutor (Planta Temporal PTA)</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>Necoclí</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>05/06/2026 a las 15:04</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>Necoclí</t>
+        </is>
+      </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I196" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J196" t="inlineStr">
+        <is>
+          <t>I.E.R. MELLO VILLAVICENCIO</t>
+        </is>
+      </c>
+      <c r="K196" t="inlineStr">
+        <is>
+          <t>I. E. R. MELLO VILLAVICENCIO - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L196" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M196" t="inlineStr">
+        <is>
+          <t>CORREG. MELLO VILLAVICENCIO</t>
+        </is>
+      </c>
+      <c r="N196" t="inlineStr">
+        <is>
+          <t>ón: CORREG. MELLO VILLAVICENCIO</t>
+        </is>
+      </c>
+      <c r="O196" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>Cargo Docente tutor (Planta Temporal PTA)</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>Puerto Nare</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>05/06/2026 a las 15:04</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>Puerto Nare</t>
+        </is>
+      </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J197" t="inlineStr">
+        <is>
+          <t>INSTITUCION EDUCATIVA RURAL JORGE ENRIQUE VILLEGAS</t>
+        </is>
+      </c>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>I. E. R JORGE ENRIQUE VILLEGAS - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L197" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M197" t="inlineStr">
+        <is>
+          <t>CORREG. LA PESCA</t>
+        </is>
+      </c>
+      <c r="N197" t="inlineStr">
+        <is>
+          <t>ón: KR 10 01 60</t>
+        </is>
+      </c>
+      <c r="O197" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>Cargo Docente tutor (Planta Temporal PTA)</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>Segovia</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>05/06/2026 a las 15:04</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>Segovia</t>
+        </is>
+      </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J198" t="inlineStr">
+        <is>
+          <t>I. E. R. FRAY MARTIN DE PORRES</t>
+        </is>
+      </c>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>COLEGIO FRAY MARTIN DE PORRES - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L198" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M198" t="inlineStr">
+        <is>
+          <t>CORREG. DE FRAGUAS</t>
+        </is>
+      </c>
+      <c r="N198" t="inlineStr">
+        <is>
+          <t>ón: CORREG. DE FRAGUAS.</t>
+        </is>
+      </c>
+      <c r="O198" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>Cargo Docente tutor (Planta Temporal PTA)</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>Titiribí</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>05/06/2026 a las 15:04</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>Suroeste</t>
+        </is>
+      </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J199" t="inlineStr">
+        <is>
+          <t>C. E. R. LOS MICOS</t>
+        </is>
+      </c>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>C. E. R. LOS MICOS - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L199" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M199" t="inlineStr">
+        <is>
+          <t>Dirección: VDA. LOS MICOS</t>
+        </is>
+      </c>
+      <c r="N199" t="inlineStr">
+        <is>
+          <t>ón: VDA. LOS MICOS</t>
+        </is>
+      </c>
+      <c r="O199" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>Cargo Docente tutor (Planta Temporal PTA)</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>Valdivia</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>05/06/2026 a las 15:04</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>Valdivia</t>
+        </is>
+      </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J200" t="inlineStr">
+        <is>
+          <t>I. E. VALDIVIA</t>
+        </is>
+      </c>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>I. E. VALDIVIA - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L200" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M200" t="inlineStr">
+        <is>
+          <t>BARRIO. LA FLORESTA</t>
+        </is>
+      </c>
+      <c r="N200" t="inlineStr">
+        <is>
+          <t>ón: CL LA FLORESTA 3 194</t>
+        </is>
+      </c>
+      <c r="O200" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>Cargo Docente tutor (Planta Temporal PTA)</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>Zaragoza</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>05/06/2026 a las 15:04</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>Zaragoza</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J201" t="inlineStr">
+        <is>
+          <t>I.E.R. LA PAJUILA</t>
+        </is>
+      </c>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>I.E.R. LA PAJUILA - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L201" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M201" t="inlineStr">
+        <is>
+          <t>VDA LA PAJUILA</t>
+        </is>
+      </c>
+      <c r="N201" t="inlineStr">
+        <is>
+          <t>ón: VDA LA PAJUILA</t>
+        </is>
+      </c>
+      <c r="O201" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>Cargo Docente tutor (Planta Temporal PTA)</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>Zaragoza</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>05/06/2026 a las 15:04</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>Zaragoza</t>
+        </is>
+      </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J202" t="inlineStr">
+        <is>
+          <t>I. E. R. EL SALTILLO</t>
+        </is>
+      </c>
+      <c r="K202" t="inlineStr">
+        <is>
+          <t>I. E. R. EL SALTILLO - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L202" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M202" t="inlineStr">
+        <is>
+          <t>VDA. EL SALTILLO</t>
+        </is>
+      </c>
+      <c r="N202" t="inlineStr">
+        <is>
+          <t>ón: VDA. EL SALTILLO</t>
+        </is>
+      </c>
+      <c r="O202" t="inlineStr">
         <is>
           <t>A</t>
         </is>

--- a/nuevas_plazas.xlsx
+++ b/nuevas_plazas.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O202"/>
+  <dimension ref="A1:O204"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14706,10 +14706,8 @@
           <t>05/06/2026 a las 15:04</t>
         </is>
       </c>
-      <c r="F191" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
+      <c r="F191" t="n">
+        <v>9</v>
       </c>
       <c r="G191" t="inlineStr">
         <is>
@@ -14783,10 +14781,8 @@
           <t>05/06/2026 a las 15:04</t>
         </is>
       </c>
-      <c r="F192" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="F192" t="n">
+        <v>8</v>
       </c>
       <c r="G192" t="inlineStr">
         <is>
@@ -14860,10 +14856,8 @@
           <t>05/06/2026 a las 15:04</t>
         </is>
       </c>
-      <c r="F193" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
+      <c r="F193" t="n">
+        <v>11</v>
       </c>
       <c r="G193" t="inlineStr">
         <is>
@@ -14937,10 +14931,8 @@
           <t>05/06/2026 a las 15:04</t>
         </is>
       </c>
-      <c r="F194" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
+      <c r="F194" t="n">
+        <v>23</v>
       </c>
       <c r="G194" t="inlineStr">
         <is>
@@ -15014,10 +15006,8 @@
           <t>05/06/2026 a las 15:04</t>
         </is>
       </c>
-      <c r="F195" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="F195" t="n">
+        <v>8</v>
       </c>
       <c r="G195" t="inlineStr">
         <is>
@@ -15091,10 +15081,8 @@
           <t>05/06/2026 a las 15:04</t>
         </is>
       </c>
-      <c r="F196" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
+      <c r="F196" t="n">
+        <v>14</v>
       </c>
       <c r="G196" t="inlineStr">
         <is>
@@ -15168,10 +15156,8 @@
           <t>05/06/2026 a las 15:04</t>
         </is>
       </c>
-      <c r="F197" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="F197" t="n">
+        <v>6</v>
       </c>
       <c r="G197" t="inlineStr">
         <is>
@@ -15245,10 +15231,8 @@
           <t>05/06/2026 a las 15:04</t>
         </is>
       </c>
-      <c r="F198" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
+      <c r="F198" t="n">
+        <v>7</v>
       </c>
       <c r="G198" t="inlineStr">
         <is>
@@ -15322,10 +15306,8 @@
           <t>05/06/2026 a las 15:04</t>
         </is>
       </c>
-      <c r="F199" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
+      <c r="F199" t="n">
+        <v>7</v>
       </c>
       <c r="G199" t="inlineStr">
         <is>
@@ -15399,10 +15381,8 @@
           <t>05/06/2026 a las 15:04</t>
         </is>
       </c>
-      <c r="F200" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
+      <c r="F200" t="n">
+        <v>9</v>
       </c>
       <c r="G200" t="inlineStr">
         <is>
@@ -15476,10 +15456,8 @@
           <t>05/06/2026 a las 15:04</t>
         </is>
       </c>
-      <c r="F201" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
+      <c r="F201" t="n">
+        <v>9</v>
       </c>
       <c r="G201" t="inlineStr">
         <is>
@@ -15553,10 +15531,8 @@
           <t>05/06/2026 a las 15:04</t>
         </is>
       </c>
-      <c r="F202" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="F202" t="n">
+        <v>8</v>
       </c>
       <c r="G202" t="inlineStr">
         <is>
@@ -15599,6 +15575,160 @@
         </is>
       </c>
       <c r="O202" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>Cargo Docente tutor (Planta Temporal PTA)</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>Venecia</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>05/06/2026 a las 15:04</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>Suroeste</t>
+        </is>
+      </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J203" t="inlineStr">
+        <is>
+          <t>I. E. ORLANDO VELASQUEZ ARANGO</t>
+        </is>
+      </c>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>I. E. ORLANDO VELASQUEZ ARANGO - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L203" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M203" t="inlineStr">
+        <is>
+          <t>CORREG. BOLOMBOLO</t>
+        </is>
+      </c>
+      <c r="N203" t="inlineStr">
+        <is>
+          <t>ón: KR 5 10 A 50</t>
+        </is>
+      </c>
+      <c r="O203" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>Cargo Docente tutor (Planta Temporal PTA)</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>Zaragoza</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>05/06/2026 a las 15:04</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>Zaragoza</t>
+        </is>
+      </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J204" t="inlineStr">
+        <is>
+          <t>I. E.R. SIMON BOLIVAR</t>
+        </is>
+      </c>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>I.E.R. SIMON BOLIVAR - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L204" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M204" t="inlineStr">
+        <is>
+          <t>CORREG. EL PATO</t>
+        </is>
+      </c>
+      <c r="N204" t="inlineStr">
+        <is>
+          <t>ón: CORREG.EL PATO - CALLE NUEVA</t>
+        </is>
+      </c>
+      <c r="O204" t="inlineStr">
         <is>
           <t>A</t>
         </is>

--- a/nuevas_plazas.xlsx
+++ b/nuevas_plazas.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O204"/>
+  <dimension ref="A1:O208"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15606,10 +15606,8 @@
           <t>05/06/2026 a las 15:04</t>
         </is>
       </c>
-      <c r="F203" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
+      <c r="F203" t="n">
+        <v>13</v>
       </c>
       <c r="G203" t="inlineStr">
         <is>
@@ -15683,10 +15681,8 @@
           <t>05/06/2026 a las 15:04</t>
         </is>
       </c>
-      <c r="F204" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
+      <c r="F204" t="n">
+        <v>16</v>
       </c>
       <c r="G204" t="inlineStr">
         <is>
@@ -15729,6 +15725,314 @@
         </is>
       </c>
       <c r="O204" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>Ciencias sociales</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>10/06/2026 a las 13:52</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>ía de Educación: Medellín</t>
+        </is>
+      </c>
+      <c r="J205" t="inlineStr">
+        <is>
+          <t>INST EDUC SEBASTIAN DE BELALCAZAR</t>
+        </is>
+      </c>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>INST EDUC SEBASTIAN DE BELALCAZAR - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L205" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M205" t="inlineStr">
+        <is>
+          <t>Dirección: CLL 103E NO 63D-185</t>
+        </is>
+      </c>
+      <c r="N205" t="inlineStr">
+        <is>
+          <t>ón: CLL 103E NO 63D-185</t>
+        </is>
+      </c>
+      <c r="O205" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>Humanidades y lengua castellana</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>10/06/2026 a las 13:52</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t>ía de Educación: Medellín</t>
+        </is>
+      </c>
+      <c r="J206" t="inlineStr">
+        <is>
+          <t>INST EDUC CAPILLA DEL ROSARIO</t>
+        </is>
+      </c>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>INST EDUC CAPILLA DEL ROSARIO - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L206" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M206" t="inlineStr">
+        <is>
+          <t>BELEN RINCON</t>
+        </is>
+      </c>
+      <c r="N206" t="inlineStr">
+        <is>
+          <t>ón: CL 6 SUR 79 195</t>
+        </is>
+      </c>
+      <c r="O206" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>Preescolar</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>10/06/2026 a las 13:52</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>ía de Educación: Medellín</t>
+        </is>
+      </c>
+      <c r="J207" t="inlineStr">
+        <is>
+          <t>INST EDUC ALFONSO LOPEZ PUMAREJO</t>
+        </is>
+      </c>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>SEC ESC JULIA AGUDELO</t>
+        </is>
+      </c>
+      <c r="L207" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M207" t="inlineStr">
+        <is>
+          <t>ENCISO</t>
+        </is>
+      </c>
+      <c r="N207" t="inlineStr">
+        <is>
+          <t>ón: CL 58 28 58</t>
+        </is>
+      </c>
+      <c r="O207" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>Preescolar</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>10/06/2026 a las 13:52</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I208" t="inlineStr">
+        <is>
+          <t>ía de Educación: Medellín</t>
+        </is>
+      </c>
+      <c r="J208" t="inlineStr">
+        <is>
+          <t>INST EDUC SANTA CATALINA DE SIENA</t>
+        </is>
+      </c>
+      <c r="K208" t="inlineStr">
+        <is>
+          <t>INST EDUC SANTA CATALINA DE SIENA - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L208" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M208" t="inlineStr">
+        <is>
+          <t>Dirección: CL 1 SUR 29 300</t>
+        </is>
+      </c>
+      <c r="N208" t="inlineStr">
+        <is>
+          <t>ón: CL 1 SUR 29 300</t>
+        </is>
+      </c>
+      <c r="O208" t="inlineStr">
         <is>
           <t>A</t>
         </is>

--- a/nuevas_plazas.xlsx
+++ b/nuevas_plazas.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O208"/>
+  <dimension ref="A1:O210"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15756,10 +15756,8 @@
           <t>10/06/2026 a las 13:52</t>
         </is>
       </c>
-      <c r="F205" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
+      <c r="F205" t="n">
+        <v>46</v>
       </c>
       <c r="G205" t="inlineStr">
         <is>
@@ -15833,10 +15831,8 @@
           <t>10/06/2026 a las 13:52</t>
         </is>
       </c>
-      <c r="F206" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
+      <c r="F206" t="n">
+        <v>40</v>
       </c>
       <c r="G206" t="inlineStr">
         <is>
@@ -15910,10 +15906,8 @@
           <t>10/06/2026 a las 13:52</t>
         </is>
       </c>
-      <c r="F207" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
+      <c r="F207" t="n">
+        <v>31</v>
       </c>
       <c r="G207" t="inlineStr">
         <is>
@@ -15987,10 +15981,8 @@
           <t>10/06/2026 a las 13:52</t>
         </is>
       </c>
-      <c r="F208" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
+      <c r="F208" t="n">
+        <v>31</v>
       </c>
       <c r="G208" t="inlineStr">
         <is>
@@ -16033,6 +16025,160 @@
         </is>
       </c>
       <c r="O208" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>Ciencias naturales y educación ambiental</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>Vegachí</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>10/06/2026 a las 16:45</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>Vegachí</t>
+        </is>
+      </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I209" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J209" t="inlineStr">
+        <is>
+          <t>I. E. EFE GOMEZ</t>
+        </is>
+      </c>
+      <c r="K209" t="inlineStr">
+        <is>
+          <t>LICEO EFE GOMEZ - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L209" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M209" t="inlineStr">
+        <is>
+          <t>CABECEERA MPAL</t>
+        </is>
+      </c>
+      <c r="N209" t="inlineStr">
+        <is>
+          <t>ón: KR 47 50 40</t>
+        </is>
+      </c>
+      <c r="O209" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Priorizadas para jóvenes entre 18 y 28 años</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>Educación física, recreación y deporte</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>Caucasia</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>10/06/2026 a las 17:12</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>Caucasia</t>
+        </is>
+      </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I210" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J210" t="inlineStr">
+        <is>
+          <t>I. E. LICEO CONCEJO MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="K210" t="inlineStr">
+        <is>
+          <t>LICEO CONCEJO MUNICIPAL - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L210" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M210" t="inlineStr">
+        <is>
+          <t>EL PAJONAL</t>
+        </is>
+      </c>
+      <c r="N210" t="inlineStr">
+        <is>
+          <t>ón: IND CARRET.TRONCAL CON AV. EL PAJONAL</t>
+        </is>
+      </c>
+      <c r="O210" t="inlineStr">
         <is>
           <t>A</t>
         </is>

--- a/nuevas_plazas.xlsx
+++ b/nuevas_plazas.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O210"/>
+  <dimension ref="A1:O212"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16056,10 +16056,8 @@
           <t>10/06/2026 a las 16:45</t>
         </is>
       </c>
-      <c r="F209" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
+      <c r="F209" t="n">
+        <v>10</v>
       </c>
       <c r="G209" t="inlineStr">
         <is>
@@ -16133,10 +16131,8 @@
           <t>10/06/2026 a las 17:12</t>
         </is>
       </c>
-      <c r="F210" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
+      <c r="F210" t="n">
+        <v>11</v>
       </c>
       <c r="G210" t="inlineStr">
         <is>
@@ -16179,6 +16175,160 @@
         </is>
       </c>
       <c r="O210" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>Ciencias naturales y educación ambiental</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>Turbo</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>12/06/2026 a las 10:27</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>Turbo</t>
+        </is>
+      </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I211" t="inlineStr">
+        <is>
+          <t>ía de Educación: Turbo</t>
+        </is>
+      </c>
+      <c r="J211" t="inlineStr">
+        <is>
+          <t>I.E. Pueblo Bello</t>
+        </is>
+      </c>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>Sede Santa Barbara Arriba</t>
+        </is>
+      </c>
+      <c r="L211" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M211" t="inlineStr">
+        <is>
+          <t>Dirección: VDA. SANTA BARBARA</t>
+        </is>
+      </c>
+      <c r="N211" t="inlineStr">
+        <is>
+          <t>ón: VDA. SANTA BARBARA</t>
+        </is>
+      </c>
+      <c r="O211" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>Turbo</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>12/06/2026 a las 10:27</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>Turbo</t>
+        </is>
+      </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I212" t="inlineStr">
+        <is>
+          <t>ía de Educación: Turbo</t>
+        </is>
+      </c>
+      <c r="J212" t="inlineStr">
+        <is>
+          <t>I.E. Nuevo Antioquia</t>
+        </is>
+      </c>
+      <c r="K212" t="inlineStr">
+        <is>
+          <t>Sede las Pavas</t>
+        </is>
+      </c>
+      <c r="L212" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M212" t="inlineStr">
+        <is>
+          <t>Dirección: VDA LAS PAVAS</t>
+        </is>
+      </c>
+      <c r="N212" t="inlineStr">
+        <is>
+          <t>ón: VDA LAS PAVAS</t>
+        </is>
+      </c>
+      <c r="O212" t="inlineStr">
         <is>
           <t>A</t>
         </is>

--- a/nuevas_plazas.xlsx
+++ b/nuevas_plazas.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O212"/>
+  <dimension ref="A1:O213"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16206,10 +16206,8 @@
           <t>12/06/2026 a las 10:27</t>
         </is>
       </c>
-      <c r="F211" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
+      <c r="F211" t="n">
+        <v>32</v>
       </c>
       <c r="G211" t="inlineStr">
         <is>
@@ -16283,10 +16281,8 @@
           <t>12/06/2026 a las 10:27</t>
         </is>
       </c>
-      <c r="F212" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
+      <c r="F212" t="n">
+        <v>82</v>
       </c>
       <c r="G212" t="inlineStr">
         <is>
@@ -16329,6 +16325,83 @@
         </is>
       </c>
       <c r="O212" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>Idioma extranjero inglés</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>Zaragoza</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>17/06/2026 a las 15:34</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>Zaragoza</t>
+        </is>
+      </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I213" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J213" t="inlineStr">
+        <is>
+          <t>I. E. SANTO CRISTO DE ZARAGOZA</t>
+        </is>
+      </c>
+      <c r="K213" t="inlineStr">
+        <is>
+          <t>LICEO SANTO CRISTO DE ZARAGOZA - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L213" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M213" t="inlineStr">
+        <is>
+          <t>SANTA ELENA</t>
+        </is>
+      </c>
+      <c r="N213" t="inlineStr">
+        <is>
+          <t>ón: CLL 39B 37 10</t>
+        </is>
+      </c>
+      <c r="O213" t="inlineStr">
         <is>
           <t>A</t>
         </is>

--- a/nuevas_plazas.xlsx
+++ b/nuevas_plazas.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O213"/>
+  <dimension ref="A1:O232"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16356,52 +16356,1513 @@
           <t>17/06/2026 a las 15:34</t>
         </is>
       </c>
-      <c r="F213" t="inlineStr">
+      <c r="F213" t="n">
+        <v>10</v>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>Zaragoza</t>
+        </is>
+      </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I213" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J213" t="inlineStr">
+        <is>
+          <t>I. E. SANTO CRISTO DE ZARAGOZA</t>
+        </is>
+      </c>
+      <c r="K213" t="inlineStr">
+        <is>
+          <t>LICEO SANTO CRISTO DE ZARAGOZA - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L213" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M213" t="inlineStr">
+        <is>
+          <t>SANTA ELENA</t>
+        </is>
+      </c>
+      <c r="N213" t="inlineStr">
+        <is>
+          <t>ón: CLL 39B 37 10</t>
+        </is>
+      </c>
+      <c r="O213" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>Preescolar</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>Cáceres</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>19/06/2026 a las 15:30</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>Cáceres</t>
+        </is>
+      </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I214" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J214" t="inlineStr">
+        <is>
+          <t>I. E. GUARUMO</t>
+        </is>
+      </c>
+      <c r="K214" t="inlineStr">
+        <is>
+          <t>COLEGIO GUARUMO - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L214" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M214" t="inlineStr">
+        <is>
+          <t>CORREG. EL GUARUMO</t>
+        </is>
+      </c>
+      <c r="N214" t="inlineStr">
+        <is>
+          <t>ón: VDA. EL GUARUMO</t>
+        </is>
+      </c>
+      <c r="O214" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>Educación religiosa</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>El Bagre</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>19/06/2026 a las 15:30</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>El Bagre</t>
+        </is>
+      </c>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I215" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J215" t="inlineStr">
+        <is>
+          <t>I. E. LA ESMERALDA</t>
+        </is>
+      </c>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>COLEGIO LA ESMERALDA - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L215" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M215" t="inlineStr">
+        <is>
+          <t>BARRIO LA ESMERALDA</t>
+        </is>
+      </c>
+      <c r="N215" t="inlineStr">
+        <is>
+          <t>ón: KR 38 69 B 75</t>
+        </is>
+      </c>
+      <c r="O215" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>San Carlos</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>19/06/2026 a las 15:30</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>San Carlos</t>
+        </is>
+      </c>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I216" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J216" t="inlineStr">
+        <is>
+          <t>I. E. RURAL PUERTO GARZA</t>
+        </is>
+      </c>
+      <c r="K216" t="inlineStr">
+        <is>
+          <t>C.E.R EL PRADO</t>
+        </is>
+      </c>
+      <c r="L216" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M216" t="inlineStr">
+        <is>
+          <t>Dirección: VEREDA EL PRADO</t>
+        </is>
+      </c>
+      <c r="N216" t="inlineStr">
+        <is>
+          <t>ón: VEREDA EL PRADO</t>
+        </is>
+      </c>
+      <c r="O216" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>Zaragoza</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>19/06/2026 a las 15:30</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>Zaragoza</t>
+        </is>
+      </c>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I217" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J217" t="inlineStr">
+        <is>
+          <t>I. E.R. SIMON BOLIVAR</t>
+        </is>
+      </c>
+      <c r="K217" t="inlineStr">
+        <is>
+          <t>E R QUEBRADA DE PATO ARRIBA</t>
+        </is>
+      </c>
+      <c r="L217" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M217" t="inlineStr">
+        <is>
+          <t>Dirección: VDA. QUEBRADA DE PATO</t>
+        </is>
+      </c>
+      <c r="N217" t="inlineStr">
+        <is>
+          <t>ón: VDA. QUEBRADA DE PATO</t>
+        </is>
+      </c>
+      <c r="O217" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>Ciencias naturales física</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>San Carlos</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>19/06/2026 a las 15:30</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>San Carlos</t>
+        </is>
+      </c>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I218" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J218" t="inlineStr">
+        <is>
+          <t>I. E. JOAQUIN CARDENAS GOMEZ</t>
+        </is>
+      </c>
+      <c r="K218" t="inlineStr">
+        <is>
+          <t>LICEO JOAQUIN CARDENAS GOMEZ - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L218" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M218" t="inlineStr">
+        <is>
+          <t>CABECERA MPAL</t>
+        </is>
+      </c>
+      <c r="N218" t="inlineStr">
+        <is>
+          <t>ón: CL 19 A 15 06</t>
+        </is>
+      </c>
+      <c r="O218" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>Preescolar</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>Caucasia</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>19/06/2026 a las 15:31</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>Caucasia</t>
+        </is>
+      </c>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I219" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J219" t="inlineStr">
+        <is>
+          <t>I. E. LICEO CONCEJO MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="K219" t="inlineStr">
+        <is>
+          <t>LICEO CONCEJO MUNICIPAL - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L219" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M219" t="inlineStr">
+        <is>
+          <t>EL PAJONAL</t>
+        </is>
+      </c>
+      <c r="N219" t="inlineStr">
+        <is>
+          <t>ón: IND CARRET.TRONCAL CON AV. EL PAJONAL</t>
+        </is>
+      </c>
+      <c r="O219" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>Ciencias sociales</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>Nechí</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>19/06/2026 a las 15:31</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>Nechí</t>
+        </is>
+      </c>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I220" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J220" t="inlineStr">
+        <is>
+          <t>I. E. JORGE ELIECER GAITAN</t>
+        </is>
+      </c>
+      <c r="K220" t="inlineStr">
+        <is>
+          <t>COLEGIO JORGE ELIECER GAITAN - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L220" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M220" t="inlineStr">
+        <is>
+          <t>CORREG. CARGUEROS</t>
+        </is>
+      </c>
+      <c r="N220" t="inlineStr">
+        <is>
+          <t>ón: CORREG. CARGUEROS</t>
+        </is>
+      </c>
+      <c r="O220" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Priorizadas para jóvenes entre 18 y 28 años</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>Tecnología e informática</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>Sopetrán</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>19/06/2026 a las 15:31</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>Occidente</t>
+        </is>
+      </c>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I221" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J221" t="inlineStr">
+        <is>
+          <t>I. E. ESCUELA NORMAL SUPERIOR SANTA TERESITA</t>
+        </is>
+      </c>
+      <c r="K221" t="inlineStr">
+        <is>
+          <t>ESCUELA NORMAL SUPERIOR SANTA TERESITA - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L221" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M221" t="inlineStr">
+        <is>
+          <t>SECTOR LA AGUAMALA</t>
+        </is>
+      </c>
+      <c r="N221" t="inlineStr">
+        <is>
+          <t>ón: CL 14 10 09</t>
+        </is>
+      </c>
+      <c r="O221" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>Preescolar</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>Cocorná</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>19/06/2026 a las 15:31</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>Cocorná</t>
+        </is>
+      </c>
+      <c r="H222" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I222" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J222" t="inlineStr">
+        <is>
+          <t>I. E. EVA TULIA QUINTERO DE TORO</t>
+        </is>
+      </c>
+      <c r="K222" t="inlineStr">
+        <is>
+          <t>C. E. R. SAN VICENTE</t>
+        </is>
+      </c>
+      <c r="L222" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M222" t="inlineStr">
+        <is>
+          <t>VDA. SAN VICENTE</t>
+        </is>
+      </c>
+      <c r="N222" t="inlineStr">
+        <is>
+          <t>ón: VDA SAN VICENTE</t>
+        </is>
+      </c>
+      <c r="O222" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>Ciencias naturales y educación ambiental</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>Nariño</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>19/06/2026 a las 15:31</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="G213" t="inlineStr">
-        <is>
-          <t>Zaragoza</t>
-        </is>
-      </c>
-      <c r="H213" t="inlineStr">
-        <is>
-          <t>Antioquia</t>
-        </is>
-      </c>
-      <c r="I213" t="inlineStr">
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>Nariño</t>
+        </is>
+      </c>
+      <c r="H223" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I223" t="inlineStr">
         <is>
           <t>ía de Educación: Antioquia</t>
         </is>
       </c>
-      <c r="J213" t="inlineStr">
-        <is>
-          <t>I. E. SANTO CRISTO DE ZARAGOZA</t>
-        </is>
-      </c>
-      <c r="K213" t="inlineStr">
-        <is>
-          <t>LICEO SANTO CRISTO DE ZARAGOZA - SEDE PRINCIPAL</t>
-        </is>
-      </c>
-      <c r="L213" t="inlineStr">
+      <c r="J223" t="inlineStr">
+        <is>
+          <t>C. E. R. UVITAL</t>
+        </is>
+      </c>
+      <c r="K223" t="inlineStr">
+        <is>
+          <t>C. E. R. EL PALMAR</t>
+        </is>
+      </c>
+      <c r="L223" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M223" t="inlineStr">
+        <is>
+          <t>VDA EL PALMAR</t>
+        </is>
+      </c>
+      <c r="N223" t="inlineStr">
+        <is>
+          <t>ón: VDA. EL PALMAR</t>
+        </is>
+      </c>
+      <c r="O223" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>Educación física, recreación y deporte</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>Anorí</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>19/06/2026 a las 15:31</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>Anorí</t>
+        </is>
+      </c>
+      <c r="H224" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I224" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J224" t="inlineStr">
+        <is>
+          <t>I. E. ANORI</t>
+        </is>
+      </c>
+      <c r="K224" t="inlineStr">
+        <is>
+          <t>LICEO JESUS MARIA URREA - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L224" t="inlineStr">
         <is>
           <t>URBANA</t>
         </is>
       </c>
-      <c r="M213" t="inlineStr">
-        <is>
-          <t>SANTA ELENA</t>
-        </is>
-      </c>
-      <c r="N213" t="inlineStr">
-        <is>
-          <t>ón: CLL 39B 37 10</t>
-        </is>
-      </c>
-      <c r="O213" t="inlineStr">
+      <c r="M224" t="inlineStr">
+        <is>
+          <t>BARRIO. LOS ANGELES</t>
+        </is>
+      </c>
+      <c r="N224" t="inlineStr">
+        <is>
+          <t>ón: KR 35 26 380</t>
+        </is>
+      </c>
+      <c r="O224" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Priorizadas para jóvenes entre 18 y 28 años</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>Preescolar</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>San Carlos</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>19/06/2026 a las 15:31</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>San Carlos</t>
+        </is>
+      </c>
+      <c r="H225" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I225" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J225" t="inlineStr">
+        <is>
+          <t>I. E. JOAQUIN CARDENAS GOMEZ</t>
+        </is>
+      </c>
+      <c r="K225" t="inlineStr">
+        <is>
+          <t>E.U. JOHN F. KENNEDY</t>
+        </is>
+      </c>
+      <c r="L225" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M225" t="inlineStr">
+        <is>
+          <t>Dirección: CL 18 19 49</t>
+        </is>
+      </c>
+      <c r="N225" t="inlineStr">
+        <is>
+          <t>ón: CL 18 19 49</t>
+        </is>
+      </c>
+      <c r="O225" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>Idioma extranjero inglés</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>Necoclí</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>19/06/2026 a las 15:31</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>Necoclí</t>
+        </is>
+      </c>
+      <c r="H226" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I226" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J226" t="inlineStr">
+        <is>
+          <t>I. E. EDUARDO ESPITIA ROMERO</t>
+        </is>
+      </c>
+      <c r="K226" t="inlineStr">
+        <is>
+          <t>I. E. EDUARDO ESPITIA ROMERO - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L226" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M226" t="inlineStr">
+        <is>
+          <t>B. SIMON BOLIVAR</t>
+        </is>
+      </c>
+      <c r="N226" t="inlineStr">
+        <is>
+          <t>ón: CL 57 44 50</t>
+        </is>
+      </c>
+      <c r="O226" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Priorizadas para jóvenes entre 18 y 28 años</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>Arboletes</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>19/06/2026 a las 15:31</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>Arboletes</t>
+        </is>
+      </c>
+      <c r="H227" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I227" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J227" t="inlineStr">
+        <is>
+          <t>I. E. R. BUENOS AIRES</t>
+        </is>
+      </c>
+      <c r="K227" t="inlineStr">
+        <is>
+          <t>C. E. R. PELAYITO</t>
+        </is>
+      </c>
+      <c r="L227" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M227" t="inlineStr">
+        <is>
+          <t>VDA. PELAYO</t>
+        </is>
+      </c>
+      <c r="N227" t="inlineStr">
+        <is>
+          <t>ón: VDA. PELAYO</t>
+        </is>
+      </c>
+      <c r="O227" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>Educación física, recreación y deporte</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>Necoclí</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>19/06/2026 a las 15:31</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G228" t="inlineStr">
+        <is>
+          <t>Necoclí</t>
+        </is>
+      </c>
+      <c r="H228" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I228" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J228" t="inlineStr">
+        <is>
+          <t>I. E. R. MULATOS</t>
+        </is>
+      </c>
+      <c r="K228" t="inlineStr">
+        <is>
+          <t>I. E. R. MULATOS - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L228" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M228" t="inlineStr">
+        <is>
+          <t>CORREG. MULATOS</t>
+        </is>
+      </c>
+      <c r="N228" t="inlineStr">
+        <is>
+          <t>ón: IND CORREG MULATOS</t>
+        </is>
+      </c>
+      <c r="O228" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Priorizadas para jóvenes entre 18 y 28 años</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>Ciencias sociales</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>Puerto Triunfo</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>19/06/2026 a las 15:31</t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>Puerto Triunfo</t>
+        </is>
+      </c>
+      <c r="H229" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I229" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J229" t="inlineStr">
+        <is>
+          <t>I. E. PABLO VI</t>
+        </is>
+      </c>
+      <c r="K229" t="inlineStr">
+        <is>
+          <t>I. E. PABLO VI - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L229" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M229" t="inlineStr">
+        <is>
+          <t>AV. LA ESTACIÓN</t>
+        </is>
+      </c>
+      <c r="N229" t="inlineStr">
+        <is>
+          <t>ón: CL 14 12 58 &lt;EOF&gt;</t>
+        </is>
+      </c>
+      <c r="O229" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>Educación artística – música</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>Arboletes</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>19/06/2026 a las 15:31</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>Arboletes</t>
+        </is>
+      </c>
+      <c r="H230" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I230" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J230" t="inlineStr">
+        <is>
+          <t>I. E. R. GUADUAL ARRIBA</t>
+        </is>
+      </c>
+      <c r="K230" t="inlineStr">
+        <is>
+          <t>I. E. R. GUADUAL ARRIBA - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L230" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M230" t="inlineStr">
+        <is>
+          <t>CORREG. GUADUAL ARRIBA</t>
+        </is>
+      </c>
+      <c r="N230" t="inlineStr">
+        <is>
+          <t>ón: CORREG. GUADUAL ARRIBA</t>
+        </is>
+      </c>
+      <c r="O230" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>Ciencias sociales</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>San Juan De Urabá</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>19/06/2026 a las 15:31</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>San Juan de Urabá</t>
+        </is>
+      </c>
+      <c r="H231" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I231" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J231" t="inlineStr">
+        <is>
+          <t>I. E. R. MONSENOR ESCOBAR VELEZ</t>
+        </is>
+      </c>
+      <c r="K231" t="inlineStr">
+        <is>
+          <t>COLEGIO MONSENOR ESCOBAR VELEZ - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L231" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M231" t="inlineStr">
+        <is>
+          <t>Dirección: CORREG. DAMAQUIEL</t>
+        </is>
+      </c>
+      <c r="N231" t="inlineStr">
+        <is>
+          <t>ón: CORREG. DAMAQUIEL</t>
+        </is>
+      </c>
+      <c r="O231" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>Amalfi</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>19/06/2026 a las 15:31</t>
+        </is>
+      </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G232" t="inlineStr">
+        <is>
+          <t>Amalfi</t>
+        </is>
+      </c>
+      <c r="H232" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I232" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J232" t="inlineStr">
+        <is>
+          <t>I. E. R. PORTACHUELO</t>
+        </is>
+      </c>
+      <c r="K232" t="inlineStr">
+        <is>
+          <t>I. E. R. GABRIELA MISTRAL</t>
+        </is>
+      </c>
+      <c r="L232" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M232" t="inlineStr">
+        <is>
+          <t>VDA. LA MARIA</t>
+        </is>
+      </c>
+      <c r="N232" t="inlineStr">
+        <is>
+          <t>ón: VDA LA MARIA</t>
+        </is>
+      </c>
+      <c r="O232" t="inlineStr">
         <is>
           <t>A</t>
         </is>

--- a/nuevas_plazas.xlsx
+++ b/nuevas_plazas.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O232"/>
+  <dimension ref="A1:O244"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16431,10 +16431,8 @@
           <t>19/06/2026 a las 15:30</t>
         </is>
       </c>
-      <c r="F214" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
+      <c r="F214" t="n">
+        <v>7</v>
       </c>
       <c r="G214" t="inlineStr">
         <is>
@@ -16508,10 +16506,8 @@
           <t>19/06/2026 a las 15:30</t>
         </is>
       </c>
-      <c r="F215" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="F215" t="n">
+        <v>5</v>
       </c>
       <c r="G215" t="inlineStr">
         <is>
@@ -16585,10 +16581,8 @@
           <t>19/06/2026 a las 15:30</t>
         </is>
       </c>
-      <c r="F216" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
+      <c r="F216" t="n">
+        <v>9</v>
       </c>
       <c r="G216" t="inlineStr">
         <is>
@@ -16662,10 +16656,8 @@
           <t>19/06/2026 a las 15:30</t>
         </is>
       </c>
-      <c r="F217" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="F217" t="n">
+        <v>5</v>
       </c>
       <c r="G217" t="inlineStr">
         <is>
@@ -16739,10 +16731,8 @@
           <t>19/06/2026 a las 15:30</t>
         </is>
       </c>
-      <c r="F218" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="F218" t="n">
+        <v>2</v>
       </c>
       <c r="G218" t="inlineStr">
         <is>
@@ -16816,10 +16806,8 @@
           <t>19/06/2026 a las 15:31</t>
         </is>
       </c>
-      <c r="F219" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="F219" t="n">
+        <v>4</v>
       </c>
       <c r="G219" t="inlineStr">
         <is>
@@ -16893,10 +16881,8 @@
           <t>19/06/2026 a las 15:31</t>
         </is>
       </c>
-      <c r="F220" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="F220" t="n">
+        <v>5</v>
       </c>
       <c r="G220" t="inlineStr">
         <is>
@@ -16970,10 +16956,8 @@
           <t>19/06/2026 a las 15:31</t>
         </is>
       </c>
-      <c r="F221" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
+      <c r="F221" t="n">
+        <v>9</v>
       </c>
       <c r="G221" t="inlineStr">
         <is>
@@ -17047,10 +17031,8 @@
           <t>19/06/2026 a las 15:31</t>
         </is>
       </c>
-      <c r="F222" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="F222" t="n">
+        <v>5</v>
       </c>
       <c r="G222" t="inlineStr">
         <is>
@@ -17124,10 +17106,8 @@
           <t>19/06/2026 a las 15:31</t>
         </is>
       </c>
-      <c r="F223" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
+      <c r="F223" t="n">
+        <v>10</v>
       </c>
       <c r="G223" t="inlineStr">
         <is>
@@ -17201,10 +17181,8 @@
           <t>19/06/2026 a las 15:31</t>
         </is>
       </c>
-      <c r="F224" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
+      <c r="F224" t="n">
+        <v>10</v>
       </c>
       <c r="G224" t="inlineStr">
         <is>
@@ -17278,10 +17256,8 @@
           <t>19/06/2026 a las 15:31</t>
         </is>
       </c>
-      <c r="F225" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="F225" t="n">
+        <v>5</v>
       </c>
       <c r="G225" t="inlineStr">
         <is>
@@ -17355,10 +17331,8 @@
           <t>19/06/2026 a las 15:31</t>
         </is>
       </c>
-      <c r="F226" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="F226" t="n">
+        <v>3</v>
       </c>
       <c r="G226" t="inlineStr">
         <is>
@@ -17432,10 +17406,8 @@
           <t>19/06/2026 a las 15:31</t>
         </is>
       </c>
-      <c r="F227" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="F227" t="n">
+        <v>6</v>
       </c>
       <c r="G227" t="inlineStr">
         <is>
@@ -17509,10 +17481,8 @@
           <t>19/06/2026 a las 15:31</t>
         </is>
       </c>
-      <c r="F228" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="F228" t="n">
+        <v>8</v>
       </c>
       <c r="G228" t="inlineStr">
         <is>
@@ -17586,10 +17556,8 @@
           <t>19/06/2026 a las 15:31</t>
         </is>
       </c>
-      <c r="F229" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="F229" t="n">
+        <v>5</v>
       </c>
       <c r="G229" t="inlineStr">
         <is>
@@ -17663,10 +17631,8 @@
           <t>19/06/2026 a las 15:31</t>
         </is>
       </c>
-      <c r="F230" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="F230" t="n">
+        <v>4</v>
       </c>
       <c r="G230" t="inlineStr">
         <is>
@@ -17740,10 +17706,8 @@
           <t>19/06/2026 a las 15:31</t>
         </is>
       </c>
-      <c r="F231" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
+      <c r="F231" t="n">
+        <v>7</v>
       </c>
       <c r="G231" t="inlineStr">
         <is>
@@ -17817,52 +17781,974 @@
           <t>19/06/2026 a las 15:31</t>
         </is>
       </c>
-      <c r="F232" t="inlineStr">
+      <c r="F232" t="n">
+        <v>6</v>
+      </c>
+      <c r="G232" t="inlineStr">
+        <is>
+          <t>Amalfi</t>
+        </is>
+      </c>
+      <c r="H232" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I232" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J232" t="inlineStr">
+        <is>
+          <t>I. E. R. PORTACHUELO</t>
+        </is>
+      </c>
+      <c r="K232" t="inlineStr">
+        <is>
+          <t>I. E. R. GABRIELA MISTRAL</t>
+        </is>
+      </c>
+      <c r="L232" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M232" t="inlineStr">
+        <is>
+          <t>VDA. LA MARIA</t>
+        </is>
+      </c>
+      <c r="N232" t="inlineStr">
+        <is>
+          <t>ón: VDA LA MARIA</t>
+        </is>
+      </c>
+      <c r="O232" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>Matemáticas</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>Frontino</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>19/06/2026 a las 15:31</t>
+        </is>
+      </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="G233" t="inlineStr">
+        <is>
+          <t>Frontino</t>
+        </is>
+      </c>
+      <c r="H233" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I233" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J233" t="inlineStr">
+        <is>
+          <t>I. E. R. LA BLANQUITA DEL MURRI</t>
+        </is>
+      </c>
+      <c r="K233" t="inlineStr">
+        <is>
+          <t>I. E. R. LA BLANQUITA DEL MURRI - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L233" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M233" t="inlineStr">
+        <is>
+          <t>CORREG. LA BLANQUITA MURRI</t>
+        </is>
+      </c>
+      <c r="N233" t="inlineStr">
+        <is>
+          <t>ón: CORREG. LA BLANQUITA MURRI</t>
+        </is>
+      </c>
+      <c r="O233" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Priorizadas para jóvenes entre 18 y 28 años</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>Segovia</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>19/06/2026 a las 15:31</t>
+        </is>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="G234" t="inlineStr">
+        <is>
+          <t>Segovia</t>
+        </is>
+      </c>
+      <c r="H234" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I234" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J234" t="inlineStr">
+        <is>
+          <t>I. E. LIBORIO BATALLER</t>
+        </is>
+      </c>
+      <c r="K234" t="inlineStr">
+        <is>
+          <t>C. E. R. SANTA ISABEL DE AMARA</t>
+        </is>
+      </c>
+      <c r="L234" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M234" t="inlineStr">
+        <is>
+          <t>VDA. SANTA ISABEL</t>
+        </is>
+      </c>
+      <c r="N234" t="inlineStr">
+        <is>
+          <t>ón: VDA.SANTA ISABEL DE AMARA</t>
+        </is>
+      </c>
+      <c r="O234" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>Humanidades y lengua castellana</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>San Juan De Urabá</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>19/06/2026 a las 15:31</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="G235" t="inlineStr">
+        <is>
+          <t>San Juan de Urabá</t>
+        </is>
+      </c>
+      <c r="H235" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I235" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J235" t="inlineStr">
+        <is>
+          <t>I. E. R. SIETE VUELTAS</t>
+        </is>
+      </c>
+      <c r="K235" t="inlineStr">
+        <is>
+          <t>I. E. R. SIETE VUELTAS - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L235" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M235" t="inlineStr">
+        <is>
+          <t>CORREG. SIETE VUELTAS</t>
+        </is>
+      </c>
+      <c r="N235" t="inlineStr">
+        <is>
+          <t>ón: CORREG. SIETE VUELTAS</t>
+        </is>
+      </c>
+      <c r="O235" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>Cargo Docente orientador</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>Sin asignación directa</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>San Roque</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>19/06/2026 a las 15:31</t>
+        </is>
+      </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="G236" t="inlineStr">
+        <is>
+          <t>San Roque</t>
+        </is>
+      </c>
+      <c r="H236" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I236" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J236" t="inlineStr">
+        <is>
+          <t>I. E. R. SAN JOSE DEL NUS</t>
+        </is>
+      </c>
+      <c r="K236" t="inlineStr">
+        <is>
+          <t>COLEGIO SAN JOSE DEL NUS - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L236" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M236" t="inlineStr">
+        <is>
+          <t>B. JUAN XXIII</t>
+        </is>
+      </c>
+      <c r="N236" t="inlineStr">
+        <is>
+          <t>ón: CORREG.SAN JOSE DEL NUS</t>
+        </is>
+      </c>
+      <c r="O236" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>Cargo Docente orientador</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>Sin asignación directa</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>Segovia</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>19/06/2026 a las 15:31</t>
+        </is>
+      </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="G237" t="inlineStr">
+        <is>
+          <t>Segovia</t>
+        </is>
+      </c>
+      <c r="H237" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I237" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J237" t="inlineStr">
+        <is>
+          <t>I. E. LIBORIO BATALLER</t>
+        </is>
+      </c>
+      <c r="K237" t="inlineStr">
+        <is>
+          <t>COLEGIO LIBORIO BATALLER - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L237" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M237" t="inlineStr">
+        <is>
+          <t>BARRIO GUANANA</t>
+        </is>
+      </c>
+      <c r="N237" t="inlineStr">
+        <is>
+          <t>ón: KR 55 47 65</t>
+        </is>
+      </c>
+      <c r="O237" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>Idioma extranjero inglés</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>San Luis</t>
+        </is>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>19/06/2026 a las 15:31</t>
+        </is>
+      </c>
+      <c r="F238" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="G232" t="inlineStr">
-        <is>
-          <t>Amalfi</t>
-        </is>
-      </c>
-      <c r="H232" t="inlineStr">
-        <is>
-          <t>Antioquia</t>
-        </is>
-      </c>
-      <c r="I232" t="inlineStr">
+      <c r="G238" t="inlineStr">
+        <is>
+          <t>San Luis</t>
+        </is>
+      </c>
+      <c r="H238" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I238" t="inlineStr">
         <is>
           <t>ía de Educación: Antioquia</t>
         </is>
       </c>
-      <c r="J232" t="inlineStr">
-        <is>
-          <t>I. E. R. PORTACHUELO</t>
-        </is>
-      </c>
-      <c r="K232" t="inlineStr">
-        <is>
-          <t>I. E. R. GABRIELA MISTRAL</t>
-        </is>
-      </c>
-      <c r="L232" t="inlineStr">
+      <c r="J238" t="inlineStr">
+        <is>
+          <t>I. E. SAN LUIS</t>
+        </is>
+      </c>
+      <c r="K238" t="inlineStr">
+        <is>
+          <t>E U MADRE LAURA</t>
+        </is>
+      </c>
+      <c r="L238" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M238" t="inlineStr">
+        <is>
+          <t>ZONA URBANA</t>
+        </is>
+      </c>
+      <c r="N238" t="inlineStr">
+        <is>
+          <t>ón: KR 22 21 56</t>
+        </is>
+      </c>
+      <c r="O238" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>Humanidades y lengua castellana</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>Segovia</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>19/06/2026 a las 15:31</t>
+        </is>
+      </c>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="G239" t="inlineStr">
+        <is>
+          <t>Segovia</t>
+        </is>
+      </c>
+      <c r="H239" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I239" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J239" t="inlineStr">
+        <is>
+          <t>I. E. LIBORIO BATALLER</t>
+        </is>
+      </c>
+      <c r="K239" t="inlineStr">
+        <is>
+          <t>COLEGIO LIBORIO BATALLER - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L239" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M239" t="inlineStr">
+        <is>
+          <t>BARRIO GUANANA</t>
+        </is>
+      </c>
+      <c r="N239" t="inlineStr">
+        <is>
+          <t>ón: KR 55 47 65</t>
+        </is>
+      </c>
+      <c r="O239" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>Ciencias naturales química</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>San Pedro De Urabá</t>
+        </is>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>19/06/2026 a las 15:32</t>
+        </is>
+      </c>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="G240" t="inlineStr">
+        <is>
+          <t>San Pedro de Urabá</t>
+        </is>
+      </c>
+      <c r="H240" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I240" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J240" t="inlineStr">
+        <is>
+          <t>I. E. R. ANTONIO NARINO</t>
+        </is>
+      </c>
+      <c r="K240" t="inlineStr">
+        <is>
+          <t>I. E. R. ANTONIO NARINO - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L240" t="inlineStr">
         <is>
           <t>RURAL</t>
         </is>
       </c>
-      <c r="M232" t="inlineStr">
-        <is>
-          <t>VDA. LA MARIA</t>
-        </is>
-      </c>
-      <c r="N232" t="inlineStr">
-        <is>
-          <t>ón: VDA LA MARIA</t>
-        </is>
-      </c>
-      <c r="O232" t="inlineStr">
+      <c r="M240" t="inlineStr">
+        <is>
+          <t>CORREG.ZAPINDONGA</t>
+        </is>
+      </c>
+      <c r="N240" t="inlineStr">
+        <is>
+          <t>ón: CORREG. ZAPINDONGA</t>
+        </is>
+      </c>
+      <c r="O240" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>Itaguí</t>
+        </is>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>19/06/2026 a las 16:14</t>
+        </is>
+      </c>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="G241" t="inlineStr">
+        <is>
+          <t>Itaguí</t>
+        </is>
+      </c>
+      <c r="H241" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I241" t="inlineStr">
+        <is>
+          <t>ía de Educación: Itaguí</t>
+        </is>
+      </c>
+      <c r="J241" t="inlineStr">
+        <is>
+          <t>INSTITUCION EDUCATIVA SIMON BOLIVAR</t>
+        </is>
+      </c>
+      <c r="K241" t="inlineStr">
+        <is>
+          <t>INSTITUCION EDUCATIVA SIMON BOLIVAR SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L241" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M241" t="inlineStr">
+        <is>
+          <t>Dirección: CL 65 46 A 95</t>
+        </is>
+      </c>
+      <c r="N241" t="inlineStr">
+        <is>
+          <t>ón: CL 65 46 A 95</t>
+        </is>
+      </c>
+      <c r="O241" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>Itaguí</t>
+        </is>
+      </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>19/06/2026 a las 16:14</t>
+        </is>
+      </c>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="G242" t="inlineStr">
+        <is>
+          <t>Itaguí</t>
+        </is>
+      </c>
+      <c r="H242" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I242" t="inlineStr">
+        <is>
+          <t>ía de Educación: Itaguí</t>
+        </is>
+      </c>
+      <c r="J242" t="inlineStr">
+        <is>
+          <t>I.E. MARIA JOSEFA ESCOBAR</t>
+        </is>
+      </c>
+      <c r="K242" t="inlineStr">
+        <is>
+          <t>I.E. MARIA JOSEFA ESCOBAR SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L242" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M242" t="inlineStr">
+        <is>
+          <t>Dirección: VDA. EL PEDREGAL</t>
+        </is>
+      </c>
+      <c r="N242" t="inlineStr">
+        <is>
+          <t>ón: VDA. EL PEDREGAL</t>
+        </is>
+      </c>
+      <c r="O242" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>Ciencias naturales química</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>Itaguí</t>
+        </is>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>19/06/2026 a las 16:14</t>
+        </is>
+      </c>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="G243" t="inlineStr">
+        <is>
+          <t>Itaguí</t>
+        </is>
+      </c>
+      <c r="H243" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I243" t="inlineStr">
+        <is>
+          <t>ía de Educación: Itaguí</t>
+        </is>
+      </c>
+      <c r="J243" t="inlineStr">
+        <is>
+          <t>INSTITUCION EDUCATIVA CARLOS ENRIQUE CORTES</t>
+        </is>
+      </c>
+      <c r="K243" t="inlineStr">
+        <is>
+          <t>INSTITUCION EDUCATIVA CARLOS E. CORTES SEDE PRINCI</t>
+        </is>
+      </c>
+      <c r="L243" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M243" t="inlineStr">
+        <is>
+          <t>LA ALDEA</t>
+        </is>
+      </c>
+      <c r="N243" t="inlineStr">
+        <is>
+          <t>ón: CL 63 54 B 41</t>
+        </is>
+      </c>
+      <c r="O243" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>Ciencias naturales química</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>Itaguí</t>
+        </is>
+      </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>19/06/2026 a las 16:15</t>
+        </is>
+      </c>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G244" t="inlineStr">
+        <is>
+          <t>Itaguí</t>
+        </is>
+      </c>
+      <c r="H244" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I244" t="inlineStr">
+        <is>
+          <t>ía de Educación: Itaguí</t>
+        </is>
+      </c>
+      <c r="J244" t="inlineStr">
+        <is>
+          <t>INSTITUCION EDUCATIVA PEDRO ESTRADA</t>
+        </is>
+      </c>
+      <c r="K244" t="inlineStr">
+        <is>
+          <t>INSTITUCION EDUCATIVA PEDRO ESTRADA SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L244" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M244" t="inlineStr">
+        <is>
+          <t>Dirección: CRA 49 #85-170</t>
+        </is>
+      </c>
+      <c r="N244" t="inlineStr">
+        <is>
+          <t>ón: CRA 49 #85-170</t>
+        </is>
+      </c>
+      <c r="O244" t="inlineStr">
         <is>
           <t>A</t>
         </is>

--- a/nuevas_plazas.xlsx
+++ b/nuevas_plazas.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O244"/>
+  <dimension ref="A1:O245"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17856,10 +17856,8 @@
           <t>19/06/2026 a las 15:31</t>
         </is>
       </c>
-      <c r="F233" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
+      <c r="F233" t="n">
+        <v>18</v>
       </c>
       <c r="G233" t="inlineStr">
         <is>
@@ -17933,10 +17931,8 @@
           <t>19/06/2026 a las 15:31</t>
         </is>
       </c>
-      <c r="F234" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
+      <c r="F234" t="n">
+        <v>19</v>
       </c>
       <c r="G234" t="inlineStr">
         <is>
@@ -18010,10 +18006,8 @@
           <t>19/06/2026 a las 15:31</t>
         </is>
       </c>
-      <c r="F235" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
+      <c r="F235" t="n">
+        <v>22</v>
       </c>
       <c r="G235" t="inlineStr">
         <is>
@@ -18087,10 +18081,8 @@
           <t>19/06/2026 a las 15:31</t>
         </is>
       </c>
-      <c r="F236" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
+      <c r="F236" t="n">
+        <v>20</v>
       </c>
       <c r="G236" t="inlineStr">
         <is>
@@ -18164,10 +18156,8 @@
           <t>19/06/2026 a las 15:31</t>
         </is>
       </c>
-      <c r="F237" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
+      <c r="F237" t="n">
+        <v>15</v>
       </c>
       <c r="G237" t="inlineStr">
         <is>
@@ -18241,10 +18231,8 @@
           <t>19/06/2026 a las 15:31</t>
         </is>
       </c>
-      <c r="F238" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="F238" t="n">
+        <v>6</v>
       </c>
       <c r="G238" t="inlineStr">
         <is>
@@ -18318,10 +18306,8 @@
           <t>19/06/2026 a las 15:31</t>
         </is>
       </c>
-      <c r="F239" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
+      <c r="F239" t="n">
+        <v>19</v>
       </c>
       <c r="G239" t="inlineStr">
         <is>
@@ -18395,10 +18381,8 @@
           <t>19/06/2026 a las 15:32</t>
         </is>
       </c>
-      <c r="F240" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
+      <c r="F240" t="n">
+        <v>12</v>
       </c>
       <c r="G240" t="inlineStr">
         <is>
@@ -18472,10 +18456,8 @@
           <t>19/06/2026 a las 16:14</t>
         </is>
       </c>
-      <c r="F241" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
+      <c r="F241" t="n">
+        <v>21</v>
       </c>
       <c r="G241" t="inlineStr">
         <is>
@@ -18549,10 +18531,8 @@
           <t>19/06/2026 a las 16:14</t>
         </is>
       </c>
-      <c r="F242" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
+      <c r="F242" t="n">
+        <v>20</v>
       </c>
       <c r="G242" t="inlineStr">
         <is>
@@ -18626,10 +18606,8 @@
           <t>19/06/2026 a las 16:14</t>
         </is>
       </c>
-      <c r="F243" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
+      <c r="F243" t="n">
+        <v>9</v>
       </c>
       <c r="G243" t="inlineStr">
         <is>
@@ -18703,10 +18681,8 @@
           <t>19/06/2026 a las 16:15</t>
         </is>
       </c>
-      <c r="F244" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
+      <c r="F244" t="n">
+        <v>10</v>
       </c>
       <c r="G244" t="inlineStr">
         <is>
@@ -18749,6 +18725,83 @@
         </is>
       </c>
       <c r="O244" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>La Estrella</t>
+        </is>
+      </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>23/06/2026 a las 09:13</t>
+        </is>
+      </c>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="G245" t="inlineStr">
+        <is>
+          <t>La Estrella</t>
+        </is>
+      </c>
+      <c r="H245" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I245" t="inlineStr">
+        <is>
+          <t>ía de Educación: La Estrella</t>
+        </is>
+      </c>
+      <c r="J245" t="inlineStr">
+        <is>
+          <t>I. E. BERNARDO ARANGO MACIAS</t>
+        </is>
+      </c>
+      <c r="K245" t="inlineStr">
+        <is>
+          <t>RAFAEL POMBO</t>
+        </is>
+      </c>
+      <c r="L245" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M245" t="inlineStr">
+        <is>
+          <t>PARQUE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="N245" t="inlineStr">
+        <is>
+          <t>ón: KR 60 79 S 29</t>
+        </is>
+      </c>
+      <c r="O245" t="inlineStr">
         <is>
           <t>A</t>
         </is>

--- a/nuevas_plazas.xlsx
+++ b/nuevas_plazas.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O245"/>
+  <dimension ref="A1:O249"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18756,10 +18756,8 @@
           <t>23/06/2026 a las 09:13</t>
         </is>
       </c>
-      <c r="F245" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
+      <c r="F245" t="n">
+        <v>65</v>
       </c>
       <c r="G245" t="inlineStr">
         <is>
@@ -18802,6 +18800,314 @@
         </is>
       </c>
       <c r="O245" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>Urrao</t>
+        </is>
+      </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>25/06/2026 a las 11:38</t>
+        </is>
+      </c>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="G246" t="inlineStr">
+        <is>
+          <t>Urrao</t>
+        </is>
+      </c>
+      <c r="H246" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I246" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J246" t="inlineStr">
+        <is>
+          <t>I. E. R. LA CALDASIA</t>
+        </is>
+      </c>
+      <c r="K246" t="inlineStr">
+        <is>
+          <t>C.E.R. TAITA</t>
+        </is>
+      </c>
+      <c r="L246" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M246" t="inlineStr">
+        <is>
+          <t>VDA. TAITA</t>
+        </is>
+      </c>
+      <c r="N246" t="inlineStr">
+        <is>
+          <t>ón: VDA TAITA</t>
+        </is>
+      </c>
+      <c r="O246" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>Peque</t>
+        </is>
+      </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>25/06/2026 a las 11:38</t>
+        </is>
+      </c>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="G247" t="inlineStr">
+        <is>
+          <t>Peque</t>
+        </is>
+      </c>
+      <c r="H247" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I247" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J247" t="inlineStr">
+        <is>
+          <t>INSTITUCION EDUCATIVA RURAL FLORENCIO SALAS TUBERQUIA</t>
+        </is>
+      </c>
+      <c r="K247" t="inlineStr">
+        <is>
+          <t>C. E. R. JUAN IGNACIO TAMAYO</t>
+        </is>
+      </c>
+      <c r="L247" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M247" t="inlineStr">
+        <is>
+          <t>CORREG. EL AGRIO</t>
+        </is>
+      </c>
+      <c r="N247" t="inlineStr">
+        <is>
+          <t>ón: CORREG. EL AGRIO</t>
+        </is>
+      </c>
+      <c r="O247" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>Murindó</t>
+        </is>
+      </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>25/06/2026 a las 11:38</t>
+        </is>
+      </c>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="G248" t="inlineStr">
+        <is>
+          <t>Murindó</t>
+        </is>
+      </c>
+      <c r="H248" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I248" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J248" t="inlineStr">
+        <is>
+          <t>I. E. MURINDO</t>
+        </is>
+      </c>
+      <c r="K248" t="inlineStr">
+        <is>
+          <t>C. E. R. BEBARAMEÂ¿O</t>
+        </is>
+      </c>
+      <c r="L248" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M248" t="inlineStr">
+        <is>
+          <t>VDA. BEBARAMEÑO</t>
+        </is>
+      </c>
+      <c r="N248" t="inlineStr">
+        <is>
+          <t>ón: VDA BABARAMEÑO</t>
+        </is>
+      </c>
+      <c r="O248" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>Preescolar</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>Rionegro</t>
+        </is>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>25/06/2026 a las 11:48</t>
+        </is>
+      </c>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="G249" t="inlineStr">
+        <is>
+          <t>Rionegro</t>
+        </is>
+      </c>
+      <c r="H249" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I249" t="inlineStr">
+        <is>
+          <t>ía de Educación: Rionegro</t>
+        </is>
+      </c>
+      <c r="J249" t="inlineStr">
+        <is>
+          <t>I. E. ANTONIO DONADO CAMACHO</t>
+        </is>
+      </c>
+      <c r="K249" t="inlineStr">
+        <is>
+          <t>I. E. ANTONIO DONADO CAMACHO - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L249" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M249" t="inlineStr">
+        <is>
+          <t>VDA. EL TABLAZO</t>
+        </is>
+      </c>
+      <c r="N249" t="inlineStr">
+        <is>
+          <t>ón: VDA. EL TABLAZO</t>
+        </is>
+      </c>
+      <c r="O249" t="inlineStr">
         <is>
           <t>A</t>
         </is>

--- a/nuevas_plazas.xlsx
+++ b/nuevas_plazas.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O249"/>
+  <dimension ref="A1:O256"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18831,10 +18831,8 @@
           <t>25/06/2026 a las 11:38</t>
         </is>
       </c>
-      <c r="F246" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
+      <c r="F246" t="n">
+        <v>12</v>
       </c>
       <c r="G246" t="inlineStr">
         <is>
@@ -18908,10 +18906,8 @@
           <t>25/06/2026 a las 11:38</t>
         </is>
       </c>
-      <c r="F247" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
+      <c r="F247" t="n">
+        <v>14</v>
       </c>
       <c r="G247" t="inlineStr">
         <is>
@@ -18985,10 +18981,8 @@
           <t>25/06/2026 a las 11:38</t>
         </is>
       </c>
-      <c r="F248" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
+      <c r="F248" t="n">
+        <v>11</v>
       </c>
       <c r="G248" t="inlineStr">
         <is>
@@ -19062,10 +19056,8 @@
           <t>25/06/2026 a las 11:48</t>
         </is>
       </c>
-      <c r="F249" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
+      <c r="F249" t="n">
+        <v>16</v>
       </c>
       <c r="G249" t="inlineStr">
         <is>
@@ -19108,6 +19100,545 @@
         </is>
       </c>
       <c r="O249" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>01/07/2026 a las 11:00</t>
+        </is>
+      </c>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G250" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="H250" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I250" t="inlineStr">
+        <is>
+          <t>ía de Educación: Medellín</t>
+        </is>
+      </c>
+      <c r="J250" t="inlineStr">
+        <is>
+          <t>INST EDUC GONZALO RESTREPO JARAMILLO</t>
+        </is>
+      </c>
+      <c r="K250" t="inlineStr">
+        <is>
+          <t>SEC ESC JUAN CANCIO RESTREPO</t>
+        </is>
+      </c>
+      <c r="L250" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M250" t="inlineStr">
+        <is>
+          <t>Dirección: CL 45 31 63</t>
+        </is>
+      </c>
+      <c r="N250" t="inlineStr">
+        <is>
+          <t>ón: CL 45 31 63</t>
+        </is>
+      </c>
+      <c r="O250" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>Preescolar</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>01/07/2026 a las 11:00</t>
+        </is>
+      </c>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G251" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="H251" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I251" t="inlineStr">
+        <is>
+          <t>ía de Educación: Medellín</t>
+        </is>
+      </c>
+      <c r="J251" t="inlineStr">
+        <is>
+          <t>INST EDUC SAN ROBERTO BELARMINO</t>
+        </is>
+      </c>
+      <c r="K251" t="inlineStr">
+        <is>
+          <t>INST EDUC SAN ROBERTO BELARMINO - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L251" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M251" t="inlineStr">
+        <is>
+          <t>LAS MERCEDES</t>
+        </is>
+      </c>
+      <c r="N251" t="inlineStr">
+        <is>
+          <t>ón: CL 32 B 83 39</t>
+        </is>
+      </c>
+      <c r="O251" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Priorizadas para jóvenes entre 18 y 28 años</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>01/07/2026 a las 11:00</t>
+        </is>
+      </c>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G252" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="H252" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I252" t="inlineStr">
+        <is>
+          <t>ía de Educación: Medellín</t>
+        </is>
+      </c>
+      <c r="J252" t="inlineStr">
+        <is>
+          <t>INST EDUC MARISCAL ROBLEDO</t>
+        </is>
+      </c>
+      <c r="K252" t="inlineStr">
+        <is>
+          <t>INST EDUC MARISCAL ROBLEDO - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L252" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M252" t="inlineStr">
+        <is>
+          <t>ROBLEDO</t>
+        </is>
+      </c>
+      <c r="N252" t="inlineStr">
+        <is>
+          <t>ón: CL 65 84 87</t>
+        </is>
+      </c>
+      <c r="O252" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>01/07/2026 a las 11:00</t>
+        </is>
+      </c>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G253" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="H253" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I253" t="inlineStr">
+        <is>
+          <t>ía de Educación: Medellín</t>
+        </is>
+      </c>
+      <c r="J253" t="inlineStr">
+        <is>
+          <t>INST EDUC SAN PABLO</t>
+        </is>
+      </c>
+      <c r="K253" t="inlineStr">
+        <is>
+          <t>SEC ESC MEDELLIN</t>
+        </is>
+      </c>
+      <c r="L253" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M253" t="inlineStr">
+        <is>
+          <t>Dirección: CL 96 36 45</t>
+        </is>
+      </c>
+      <c r="N253" t="inlineStr">
+        <is>
+          <t>ón: CL 96 36 45</t>
+        </is>
+      </c>
+      <c r="O253" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>01/07/2026 a las 11:00</t>
+        </is>
+      </c>
+      <c r="F254" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G254" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="H254" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I254" t="inlineStr">
+        <is>
+          <t>ía de Educación: Medellín</t>
+        </is>
+      </c>
+      <c r="J254" t="inlineStr">
+        <is>
+          <t>INST EDUC MANUEL JOSE GOMEZ SERNA</t>
+        </is>
+      </c>
+      <c r="K254" t="inlineStr">
+        <is>
+          <t>SEC ESC ALEJO PIMIENTA</t>
+        </is>
+      </c>
+      <c r="L254" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M254" t="inlineStr">
+        <is>
+          <t>CASTILA</t>
+        </is>
+      </c>
+      <c r="N254" t="inlineStr">
+        <is>
+          <t>ón: CL 96 70 43</t>
+        </is>
+      </c>
+      <c r="O254" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>01/07/2026 a las 11:00</t>
+        </is>
+      </c>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G255" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="H255" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I255" t="inlineStr">
+        <is>
+          <t>ía de Educación: Medellín</t>
+        </is>
+      </c>
+      <c r="J255" t="inlineStr">
+        <is>
+          <t>INST EDUC JESUS MARIA VALLE</t>
+        </is>
+      </c>
+      <c r="K255" t="inlineStr">
+        <is>
+          <t>SEC ESC EL PICACHO</t>
+        </is>
+      </c>
+      <c r="L255" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M255" t="inlineStr">
+        <is>
+          <t>Dirección: KR 83 95 B 40</t>
+        </is>
+      </c>
+      <c r="N255" t="inlineStr">
+        <is>
+          <t>ón: KR 83 95 B 40</t>
+        </is>
+      </c>
+      <c r="O255" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>01/07/2026 a las 11:00</t>
+        </is>
+      </c>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G256" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="H256" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I256" t="inlineStr">
+        <is>
+          <t>ía de Educación: Medellín</t>
+        </is>
+      </c>
+      <c r="J256" t="inlineStr">
+        <is>
+          <t>INST EDUC ALFONSO LOPEZ PUMAREJO</t>
+        </is>
+      </c>
+      <c r="K256" t="inlineStr">
+        <is>
+          <t>SEC ESC JULIA AGUDELO</t>
+        </is>
+      </c>
+      <c r="L256" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M256" t="inlineStr">
+        <is>
+          <t>ENCISO</t>
+        </is>
+      </c>
+      <c r="N256" t="inlineStr">
+        <is>
+          <t>ón: CL 58 28 58</t>
+        </is>
+      </c>
+      <c r="O256" t="inlineStr">
         <is>
           <t>A</t>
         </is>

--- a/nuevas_plazas.xlsx
+++ b/nuevas_plazas.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O256"/>
+  <dimension ref="A1:O258"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19131,10 +19131,8 @@
           <t>01/07/2026 a las 11:00</t>
         </is>
       </c>
-      <c r="F250" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F250" t="n">
+        <v>0</v>
       </c>
       <c r="G250" t="inlineStr">
         <is>
@@ -19208,10 +19206,8 @@
           <t>01/07/2026 a las 11:00</t>
         </is>
       </c>
-      <c r="F251" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F251" t="n">
+        <v>0</v>
       </c>
       <c r="G251" t="inlineStr">
         <is>
@@ -19285,10 +19281,8 @@
           <t>01/07/2026 a las 11:00</t>
         </is>
       </c>
-      <c r="F252" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="F252" t="n">
+        <v>1</v>
       </c>
       <c r="G252" t="inlineStr">
         <is>
@@ -19362,10 +19356,8 @@
           <t>01/07/2026 a las 11:00</t>
         </is>
       </c>
-      <c r="F253" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F253" t="n">
+        <v>0</v>
       </c>
       <c r="G253" t="inlineStr">
         <is>
@@ -19439,10 +19431,8 @@
           <t>01/07/2026 a las 11:00</t>
         </is>
       </c>
-      <c r="F254" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F254" t="n">
+        <v>0</v>
       </c>
       <c r="G254" t="inlineStr">
         <is>
@@ -19516,10 +19506,8 @@
           <t>01/07/2026 a las 11:00</t>
         </is>
       </c>
-      <c r="F255" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F255" t="n">
+        <v>0</v>
       </c>
       <c r="G255" t="inlineStr">
         <is>
@@ -19593,10 +19581,8 @@
           <t>01/07/2026 a las 11:00</t>
         </is>
       </c>
-      <c r="F256" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F256" t="n">
+        <v>0</v>
       </c>
       <c r="G256" t="inlineStr">
         <is>
@@ -19639,6 +19625,160 @@
         </is>
       </c>
       <c r="O256" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>Ciencias naturales química</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>San Pedro De Urabá</t>
+        </is>
+      </c>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>02/07/2026 a las 15:05</t>
+        </is>
+      </c>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G257" t="inlineStr">
+        <is>
+          <t>San Pedro de Urabá</t>
+        </is>
+      </c>
+      <c r="H257" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I257" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J257" t="inlineStr">
+        <is>
+          <t>I. E. R. ANTONIO NARINO</t>
+        </is>
+      </c>
+      <c r="K257" t="inlineStr">
+        <is>
+          <t>I. E. R. ANTONIO NARINO - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L257" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M257" t="inlineStr">
+        <is>
+          <t>CORREG.ZAPINDONGA</t>
+        </is>
+      </c>
+      <c r="N257" t="inlineStr">
+        <is>
+          <t>ón: CORREG. ZAPINDONGA</t>
+        </is>
+      </c>
+      <c r="O257" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Priorizadas para jóvenes entre 18 y 28 años</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>Educación física, recreación y deporte</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>Caucasia</t>
+        </is>
+      </c>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>02/07/2026 a las 15:14</t>
+        </is>
+      </c>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="G258" t="inlineStr">
+        <is>
+          <t>Caucasia</t>
+        </is>
+      </c>
+      <c r="H258" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I258" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J258" t="inlineStr">
+        <is>
+          <t>I. E. LICEO CONCEJO MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="K258" t="inlineStr">
+        <is>
+          <t>LICEO CONCEJO MUNICIPAL - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L258" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M258" t="inlineStr">
+        <is>
+          <t>EL PAJONAL</t>
+        </is>
+      </c>
+      <c r="N258" t="inlineStr">
+        <is>
+          <t>ón: IND CARRET.TRONCAL CON AV. EL PAJONAL</t>
+        </is>
+      </c>
+      <c r="O258" t="inlineStr">
         <is>
           <t>A</t>
         </is>

--- a/nuevas_plazas.xlsx
+++ b/nuevas_plazas.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O258"/>
+  <dimension ref="A1:O289"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19656,10 +19656,8 @@
           <t>02/07/2026 a las 15:05</t>
         </is>
       </c>
-      <c r="F257" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
+      <c r="F257" t="n">
+        <v>7</v>
       </c>
       <c r="G257" t="inlineStr">
         <is>
@@ -19733,10 +19731,8 @@
           <t>02/07/2026 a las 15:14</t>
         </is>
       </c>
-      <c r="F258" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
+      <c r="F258" t="n">
+        <v>29</v>
       </c>
       <c r="G258" t="inlineStr">
         <is>
@@ -19779,6 +19775,2393 @@
         </is>
       </c>
       <c r="O258" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>Idioma extranjero inglés</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>Caucasia</t>
+        </is>
+      </c>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t>08/07/2026 a las 10:42</t>
+        </is>
+      </c>
+      <c r="F259" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G259" t="inlineStr">
+        <is>
+          <t>Caucasia</t>
+        </is>
+      </c>
+      <c r="H259" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I259" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J259" t="inlineStr">
+        <is>
+          <t>I. E. SANTO DOMINGO</t>
+        </is>
+      </c>
+      <c r="K259" t="inlineStr">
+        <is>
+          <t>CER EL CAMELLO</t>
+        </is>
+      </c>
+      <c r="L259" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M259" t="inlineStr">
+        <is>
+          <t>.</t>
+        </is>
+      </c>
+      <c r="N259" t="inlineStr">
+        <is>
+          <t>ón: CL 28 C KR 2 A</t>
+        </is>
+      </c>
+      <c r="O259" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>Educación física, recreación y deporte</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>Cañasgordas</t>
+        </is>
+      </c>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>08/07/2026 a las 10:42</t>
+        </is>
+      </c>
+      <c r="F260" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="G260" t="inlineStr">
+        <is>
+          <t>Cañasgordas</t>
+        </is>
+      </c>
+      <c r="H260" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I260" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J260" t="inlineStr">
+        <is>
+          <t>I. E. R. BERNARDO SIERRA</t>
+        </is>
+      </c>
+      <c r="K260" t="inlineStr">
+        <is>
+          <t>COLEGIO BERNARDO SIERRA - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L260" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M260" t="inlineStr">
+        <is>
+          <t>VDA CESTILLAL</t>
+        </is>
+      </c>
+      <c r="N260" t="inlineStr">
+        <is>
+          <t>ón: VDA CESTILLAL</t>
+        </is>
+      </c>
+      <c r="O260" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>Ciencias naturales y educación ambiental</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>Cáceres</t>
+        </is>
+      </c>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>08/07/2026 a las 10:42</t>
+        </is>
+      </c>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="G261" t="inlineStr">
+        <is>
+          <t>Cáceres</t>
+        </is>
+      </c>
+      <c r="H261" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I261" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J261" t="inlineStr">
+        <is>
+          <t>I. E. R. EL TIGRE</t>
+        </is>
+      </c>
+      <c r="K261" t="inlineStr">
+        <is>
+          <t>C.E.R. SAN PABLO</t>
+        </is>
+      </c>
+      <c r="L261" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M261" t="inlineStr">
+        <is>
+          <t>.</t>
+        </is>
+      </c>
+      <c r="N261" t="inlineStr">
+        <is>
+          <t>ón: VEREDA SAN PABLO</t>
+        </is>
+      </c>
+      <c r="O261" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Priorizadas para jóvenes entre 18 y 28 años</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>Preescolar</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>Caucasia</t>
+        </is>
+      </c>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>08/07/2026 a las 10:42</t>
+        </is>
+      </c>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="G262" t="inlineStr">
+        <is>
+          <t>Caucasia</t>
+        </is>
+      </c>
+      <c r="H262" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I262" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J262" t="inlineStr">
+        <is>
+          <t>I. E. LA MISERICORDIA</t>
+        </is>
+      </c>
+      <c r="K262" t="inlineStr">
+        <is>
+          <t>E U I SAN RAFAEL</t>
+        </is>
+      </c>
+      <c r="L262" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M262" t="inlineStr">
+        <is>
+          <t>CABECERA MPAL.</t>
+        </is>
+      </c>
+      <c r="N262" t="inlineStr">
+        <is>
+          <t>ón: CR. 9 CON CL. 18</t>
+        </is>
+      </c>
+      <c r="O262" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>Tecnología e informática</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>Zaragoza</t>
+        </is>
+      </c>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>08/07/2026 a las 10:42</t>
+        </is>
+      </c>
+      <c r="F263" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="G263" t="inlineStr">
+        <is>
+          <t>Zaragoza</t>
+        </is>
+      </c>
+      <c r="H263" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I263" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J263" t="inlineStr">
+        <is>
+          <t>I. E. SANTO CRISTO DE ZARAGOZA</t>
+        </is>
+      </c>
+      <c r="K263" t="inlineStr">
+        <is>
+          <t>LICEO SANTO CRISTO DE ZARAGOZA - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L263" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M263" t="inlineStr">
+        <is>
+          <t>SANTA ELENA</t>
+        </is>
+      </c>
+      <c r="N263" t="inlineStr">
+        <is>
+          <t>ón: CLL 39B 37 10</t>
+        </is>
+      </c>
+      <c r="O263" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>Educación física, recreación y deporte</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>Giraldo</t>
+        </is>
+      </c>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>08/07/2026 a las 10:43</t>
+        </is>
+      </c>
+      <c r="F264" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="G264" t="inlineStr">
+        <is>
+          <t>Occidente</t>
+        </is>
+      </c>
+      <c r="H264" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I264" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J264" t="inlineStr">
+        <is>
+          <t>I. E. LUIS ANDRADE VALDERRAMA</t>
+        </is>
+      </c>
+      <c r="K264" t="inlineStr">
+        <is>
+          <t>LICEO LUIS ANDRADE VALDERRAMA - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L264" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M264" t="inlineStr">
+        <is>
+          <t>VDA VALDERRAMA</t>
+        </is>
+      </c>
+      <c r="N264" t="inlineStr">
+        <is>
+          <t>ón: CL 10 8 12</t>
+        </is>
+      </c>
+      <c r="O264" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>Tecnología e informática</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>Nechí</t>
+        </is>
+      </c>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>08/07/2026 a las 10:43</t>
+        </is>
+      </c>
+      <c r="F265" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G265" t="inlineStr">
+        <is>
+          <t>Nechí</t>
+        </is>
+      </c>
+      <c r="H265" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I265" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J265" t="inlineStr">
+        <is>
+          <t>I. E. NECHI</t>
+        </is>
+      </c>
+      <c r="K265" t="inlineStr">
+        <is>
+          <t>COLEGIO DE NECHI - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L265" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M265" t="inlineStr">
+        <is>
+          <t>BARRIO. LA MISERICORDIA</t>
+        </is>
+      </c>
+      <c r="N265" t="inlineStr">
+        <is>
+          <t>ón: BARRIO. LA MISERICORDIA</t>
+        </is>
+      </c>
+      <c r="O265" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>Ciencias naturales física</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>Ituango</t>
+        </is>
+      </c>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>08/07/2026 a las 10:43</t>
+        </is>
+      </c>
+      <c r="F266" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G266" t="inlineStr">
+        <is>
+          <t>Ituango</t>
+        </is>
+      </c>
+      <c r="H266" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I266" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J266" t="inlineStr">
+        <is>
+          <t>I. E. JESUS MARIA VALLE JARAMILLO</t>
+        </is>
+      </c>
+      <c r="K266" t="inlineStr">
+        <is>
+          <t>I. E. JESUS MARIA VALLE JARAMILLO - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L266" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M266" t="inlineStr">
+        <is>
+          <t>CORREG. LA GRANJA</t>
+        </is>
+      </c>
+      <c r="N266" t="inlineStr">
+        <is>
+          <t>ón: CORREG. LA GRANJA</t>
+        </is>
+      </c>
+      <c r="O266" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>Valdivia</t>
+        </is>
+      </c>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>08/07/2026 a las 10:43</t>
+        </is>
+      </c>
+      <c r="F267" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="G267" t="inlineStr">
+        <is>
+          <t>Valdivia</t>
+        </is>
+      </c>
+      <c r="H267" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I267" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J267" t="inlineStr">
+        <is>
+          <t>C. E. R. LA PAULINA</t>
+        </is>
+      </c>
+      <c r="K267" t="inlineStr">
+        <is>
+          <t>C. E. R. PUQUI ABAJO</t>
+        </is>
+      </c>
+      <c r="L267" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M267" t="inlineStr">
+        <is>
+          <t>VDA. PUQUI ABAJO</t>
+        </is>
+      </c>
+      <c r="N267" t="inlineStr">
+        <is>
+          <t>ón: VDA PUQUI ABAJO</t>
+        </is>
+      </c>
+      <c r="O267" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>Nechí</t>
+        </is>
+      </c>
+      <c r="E268" t="inlineStr">
+        <is>
+          <t>08/07/2026 a las 10:43</t>
+        </is>
+      </c>
+      <c r="F268" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="G268" t="inlineStr">
+        <is>
+          <t>Nechí</t>
+        </is>
+      </c>
+      <c r="H268" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I268" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J268" t="inlineStr">
+        <is>
+          <t>I. E. NECHI</t>
+        </is>
+      </c>
+      <c r="K268" t="inlineStr">
+        <is>
+          <t>E U SAN NICOLAS</t>
+        </is>
+      </c>
+      <c r="L268" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M268" t="inlineStr">
+        <is>
+          <t>BARRIO. SAN NICOLAS</t>
+        </is>
+      </c>
+      <c r="N268" t="inlineStr">
+        <is>
+          <t>ón: BARRIO. SAN NICOLAS</t>
+        </is>
+      </c>
+      <c r="O268" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>Idioma extranjero inglés</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>Ebéjico</t>
+        </is>
+      </c>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>08/07/2026 a las 10:43</t>
+        </is>
+      </c>
+      <c r="F269" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="G269" t="inlineStr">
+        <is>
+          <t>Occidente</t>
+        </is>
+      </c>
+      <c r="H269" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I269" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J269" t="inlineStr">
+        <is>
+          <t>I. E. URBANA SAN JOSE</t>
+        </is>
+      </c>
+      <c r="K269" t="inlineStr">
+        <is>
+          <t>I. E. URBANA SAN JOSE - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L269" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M269" t="inlineStr">
+        <is>
+          <t>AV. LA REPUBLICA</t>
+        </is>
+      </c>
+      <c r="N269" t="inlineStr">
+        <is>
+          <t>ón: CL 19 14 22</t>
+        </is>
+      </c>
+      <c r="O269" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Priorizadas para jóvenes entre 18 y 28 años</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>Valdivia</t>
+        </is>
+      </c>
+      <c r="E270" t="inlineStr">
+        <is>
+          <t>08/07/2026 a las 10:44</t>
+        </is>
+      </c>
+      <c r="F270" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="G270" t="inlineStr">
+        <is>
+          <t>Valdivia</t>
+        </is>
+      </c>
+      <c r="H270" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I270" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J270" t="inlineStr">
+        <is>
+          <t>I. E. R. MARCO A ROJO</t>
+        </is>
+      </c>
+      <c r="K270" t="inlineStr">
+        <is>
+          <t>C. E. R. CACHIRIME</t>
+        </is>
+      </c>
+      <c r="L270" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M270" t="inlineStr">
+        <is>
+          <t>VDA. CACHIRIME</t>
+        </is>
+      </c>
+      <c r="N270" t="inlineStr">
+        <is>
+          <t>ón: VDA CACHIRIME</t>
+        </is>
+      </c>
+      <c r="O270" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>Matemáticas</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>Peque</t>
+        </is>
+      </c>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t>08/07/2026 a las 10:44</t>
+        </is>
+      </c>
+      <c r="F271" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G271" t="inlineStr">
+        <is>
+          <t>Peque</t>
+        </is>
+      </c>
+      <c r="H271" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I271" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J271" t="inlineStr">
+        <is>
+          <t>INSTITUCION EDUCATIVA RURAL FLORENCIO SALAS TUBERQUIA</t>
+        </is>
+      </c>
+      <c r="K271" t="inlineStr">
+        <is>
+          <t>C. E. R. LAS LOMAS</t>
+        </is>
+      </c>
+      <c r="L271" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M271" t="inlineStr">
+        <is>
+          <t>VDA. LAS LOMAS</t>
+        </is>
+      </c>
+      <c r="N271" t="inlineStr">
+        <is>
+          <t>ón: VDA LAS LOMAS</t>
+        </is>
+      </c>
+      <c r="O271" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>Educación artística – música</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>Ituango</t>
+        </is>
+      </c>
+      <c r="E272" t="inlineStr">
+        <is>
+          <t>08/07/2026 a las 10:44</t>
+        </is>
+      </c>
+      <c r="F272" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G272" t="inlineStr">
+        <is>
+          <t>Ituango</t>
+        </is>
+      </c>
+      <c r="H272" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I272" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J272" t="inlineStr">
+        <is>
+          <t>I. E. R. LA PEREZ</t>
+        </is>
+      </c>
+      <c r="K272" t="inlineStr">
+        <is>
+          <t>I. E. R. LA PEREZ - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L272" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M272" t="inlineStr">
+        <is>
+          <t>VDA. QUEBRADA DEL MEDIO</t>
+        </is>
+      </c>
+      <c r="N272" t="inlineStr">
+        <is>
+          <t>ón: VDA. QUEBRADA DEL MEDIO</t>
+        </is>
+      </c>
+      <c r="O272" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>Educación artística - artes plásticas</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>Briceño</t>
+        </is>
+      </c>
+      <c r="E273" t="inlineStr">
+        <is>
+          <t>08/07/2026 a las 10:44</t>
+        </is>
+      </c>
+      <c r="F273" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="G273" t="inlineStr">
+        <is>
+          <t>Briceño</t>
+        </is>
+      </c>
+      <c r="H273" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I273" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J273" t="inlineStr">
+        <is>
+          <t>I. E. ANTONIO ROLDAN BETANCUR</t>
+        </is>
+      </c>
+      <c r="K273" t="inlineStr">
+        <is>
+          <t>I. E. ANTONIO ROLDAN BETANCUR - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L273" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M273" t="inlineStr">
+        <is>
+          <t>CALLE HOSPITAL</t>
+        </is>
+      </c>
+      <c r="N273" t="inlineStr">
+        <is>
+          <t>ón: KR 7 10 42</t>
+        </is>
+      </c>
+      <c r="O273" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>Educación física, recreación y deporte</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>Valdivia</t>
+        </is>
+      </c>
+      <c r="E274" t="inlineStr">
+        <is>
+          <t>08/07/2026 a las 10:45</t>
+        </is>
+      </c>
+      <c r="F274" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="G274" t="inlineStr">
+        <is>
+          <t>Valdivia</t>
+        </is>
+      </c>
+      <c r="H274" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I274" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J274" t="inlineStr">
+        <is>
+          <t>I. E. VALDIVIA</t>
+        </is>
+      </c>
+      <c r="K274" t="inlineStr">
+        <is>
+          <t>I. E. VALDIVIA - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L274" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M274" t="inlineStr">
+        <is>
+          <t>BARRIO. LA FLORESTA</t>
+        </is>
+      </c>
+      <c r="N274" t="inlineStr">
+        <is>
+          <t>ón: CL LA FLORESTA 3 194</t>
+        </is>
+      </c>
+      <c r="O274" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>Tecnología e informática</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>Segovia</t>
+        </is>
+      </c>
+      <c r="E275" t="inlineStr">
+        <is>
+          <t>08/07/2026 a las 10:45</t>
+        </is>
+      </c>
+      <c r="F275" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G275" t="inlineStr">
+        <is>
+          <t>Segovia</t>
+        </is>
+      </c>
+      <c r="H275" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I275" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J275" t="inlineStr">
+        <is>
+          <t>I. E. LIBORIO BATALLER</t>
+        </is>
+      </c>
+      <c r="K275" t="inlineStr">
+        <is>
+          <t>COLEGIO LIBORIO BATALLER - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L275" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M275" t="inlineStr">
+        <is>
+          <t>BARRIO GUANANA</t>
+        </is>
+      </c>
+      <c r="N275" t="inlineStr">
+        <is>
+          <t>ón: KR 55 47 65</t>
+        </is>
+      </c>
+      <c r="O275" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>Puerto Triunfo</t>
+        </is>
+      </c>
+      <c r="E276" t="inlineStr">
+        <is>
+          <t>08/07/2026 a las 10:45</t>
+        </is>
+      </c>
+      <c r="F276" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="G276" t="inlineStr">
+        <is>
+          <t>Puerto Triunfo</t>
+        </is>
+      </c>
+      <c r="H276" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I276" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J276" t="inlineStr">
+        <is>
+          <t>I. E. R. HERMANO DANIEL</t>
+        </is>
+      </c>
+      <c r="K276" t="inlineStr">
+        <is>
+          <t>I. E. R. HERMANO DANIEL - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L276" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M276" t="inlineStr">
+        <is>
+          <t>CORREG.LAS MERCEDES</t>
+        </is>
+      </c>
+      <c r="N276" t="inlineStr">
+        <is>
+          <t>ón: CORREG.LAS MERCEDES</t>
+        </is>
+      </c>
+      <c r="O276" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>Educación física, recreación y deporte</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>Puerto Berrío</t>
+        </is>
+      </c>
+      <c r="E277" t="inlineStr">
+        <is>
+          <t>08/07/2026 a las 10:45</t>
+        </is>
+      </c>
+      <c r="F277" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="G277" t="inlineStr">
+        <is>
+          <t>Puerto Berrio</t>
+        </is>
+      </c>
+      <c r="H277" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I277" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J277" t="inlineStr">
+        <is>
+          <t>I. E. R. LA CARLOTA</t>
+        </is>
+      </c>
+      <c r="K277" t="inlineStr">
+        <is>
+          <t>I. E. R. LA CARLOTA - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L277" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M277" t="inlineStr">
+        <is>
+          <t>VDA. LA CARLOTA KM 18 VIA MEDELLIN</t>
+        </is>
+      </c>
+      <c r="N277" t="inlineStr">
+        <is>
+          <t>ón: VDA. LA CARLOTA KM 18 VIA MEDELLIN</t>
+        </is>
+      </c>
+      <c r="O277" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>Sabanalarga</t>
+        </is>
+      </c>
+      <c r="E278" t="inlineStr">
+        <is>
+          <t>08/07/2026 a las 10:46</t>
+        </is>
+      </c>
+      <c r="F278" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="G278" t="inlineStr">
+        <is>
+          <t>Sabanalarga</t>
+        </is>
+      </c>
+      <c r="H278" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I278" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J278" t="inlineStr">
+        <is>
+          <t>I. E. SAN JOSE</t>
+        </is>
+      </c>
+      <c r="K278" t="inlineStr">
+        <is>
+          <t>C. E. R. LLANO DE LOS ENCUENTROS</t>
+        </is>
+      </c>
+      <c r="L278" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M278" t="inlineStr">
+        <is>
+          <t>VDA. LLANO DE LOS ENCUENTROS</t>
+        </is>
+      </c>
+      <c r="N278" t="inlineStr">
+        <is>
+          <t>ón: VDA. LLANO DE LOS ENCUENTROS</t>
+        </is>
+      </c>
+      <c r="O278" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>Matemáticas</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>Mutatá</t>
+        </is>
+      </c>
+      <c r="E279" t="inlineStr">
+        <is>
+          <t>08/07/2026 a las 10:46</t>
+        </is>
+      </c>
+      <c r="F279" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G279" t="inlineStr">
+        <is>
+          <t>Mutatá</t>
+        </is>
+      </c>
+      <c r="H279" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I279" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J279" t="inlineStr">
+        <is>
+          <t>I. E. MUTATA</t>
+        </is>
+      </c>
+      <c r="K279" t="inlineStr">
+        <is>
+          <t>COLEGIO MUTATA - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L279" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M279" t="inlineStr">
+        <is>
+          <t>CABECERA MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="N279" t="inlineStr">
+        <is>
+          <t>ón: KR 11 8 67</t>
+        </is>
+      </c>
+      <c r="O279" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>Preescolar</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>Vigia Del Fuerte</t>
+        </is>
+      </c>
+      <c r="E280" t="inlineStr">
+        <is>
+          <t>08/07/2026 a las 10:46</t>
+        </is>
+      </c>
+      <c r="F280" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="G280" t="inlineStr">
+        <is>
+          <t>Vigia del Fuerte</t>
+        </is>
+      </c>
+      <c r="H280" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I280" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J280" t="inlineStr">
+        <is>
+          <t>I. E. R. ALIANZA PARA EL PROGRESO</t>
+        </is>
+      </c>
+      <c r="K280" t="inlineStr">
+        <is>
+          <t>C. E. R. ISLETA</t>
+        </is>
+      </c>
+      <c r="L280" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M280" t="inlineStr">
+        <is>
+          <t>VDA. ISLETA</t>
+        </is>
+      </c>
+      <c r="N280" t="inlineStr">
+        <is>
+          <t>ón: VDA ISLETA</t>
+        </is>
+      </c>
+      <c r="O280" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>Humanidades y lengua castellana</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>Remedios</t>
+        </is>
+      </c>
+      <c r="E281" t="inlineStr">
+        <is>
+          <t>08/07/2026 a las 10:46</t>
+        </is>
+      </c>
+      <c r="F281" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="G281" t="inlineStr">
+        <is>
+          <t>Remedios</t>
+        </is>
+      </c>
+      <c r="H281" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I281" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J281" t="inlineStr">
+        <is>
+          <t>I.E. IGNACIO YEPES YEPES</t>
+        </is>
+      </c>
+      <c r="K281" t="inlineStr">
+        <is>
+          <t>LICEO IGNACIO YEPES YEPES - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L281" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M281" t="inlineStr">
+        <is>
+          <t>ALTO DE LAS TAPIAS</t>
+        </is>
+      </c>
+      <c r="N281" t="inlineStr">
+        <is>
+          <t>ón: CQ 8 15 149</t>
+        </is>
+      </c>
+      <c r="O281" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>Matemáticas</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>Caucasia</t>
+        </is>
+      </c>
+      <c r="E282" t="inlineStr">
+        <is>
+          <t>08/07/2026 a las 10:47</t>
+        </is>
+      </c>
+      <c r="F282" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G282" t="inlineStr">
+        <is>
+          <t>Caucasia</t>
+        </is>
+      </c>
+      <c r="H282" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I282" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J282" t="inlineStr">
+        <is>
+          <t>I. E. R. SANTA ROSITA</t>
+        </is>
+      </c>
+      <c r="K282" t="inlineStr">
+        <is>
+          <t>I. E. R. SANTA ROSITA - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L282" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M282" t="inlineStr">
+        <is>
+          <t>VDA. SANTA ROSITA</t>
+        </is>
+      </c>
+      <c r="N282" t="inlineStr">
+        <is>
+          <t>ón: VDA. SANTA ROSITA</t>
+        </is>
+      </c>
+      <c r="O282" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>Ciencias naturales y educación ambiental</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>Puerto Berrío</t>
+        </is>
+      </c>
+      <c r="E283" t="inlineStr">
+        <is>
+          <t>08/07/2026 a las 10:47</t>
+        </is>
+      </c>
+      <c r="F283" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="G283" t="inlineStr">
+        <is>
+          <t>Puerto Berrio</t>
+        </is>
+      </c>
+      <c r="H283" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I283" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J283" t="inlineStr">
+        <is>
+          <t>I. E. ANTONIO NARINO</t>
+        </is>
+      </c>
+      <c r="K283" t="inlineStr">
+        <is>
+          <t>COLEGIO ANTONIO NARINO - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L283" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M283" t="inlineStr">
+        <is>
+          <t>Dirección: CL 50 KR 13</t>
+        </is>
+      </c>
+      <c r="N283" t="inlineStr">
+        <is>
+          <t>ón: CL 50 KR 13</t>
+        </is>
+      </c>
+      <c r="O283" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Priorizadas para jóvenes entre 18 y 28 años</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>Humanidades y lengua castellana</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>El Bagre</t>
+        </is>
+      </c>
+      <c r="E284" t="inlineStr">
+        <is>
+          <t>08/07/2026 a las 10:47</t>
+        </is>
+      </c>
+      <c r="F284" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="G284" t="inlineStr">
+        <is>
+          <t>El Bagre</t>
+        </is>
+      </c>
+      <c r="H284" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I284" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J284" t="inlineStr">
+        <is>
+          <t>I. E. BIJAO</t>
+        </is>
+      </c>
+      <c r="K284" t="inlineStr">
+        <is>
+          <t>I. E. BIJAO - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L284" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M284" t="inlineStr">
+        <is>
+          <t>BARRIO BIJAO</t>
+        </is>
+      </c>
+      <c r="N284" t="inlineStr">
+        <is>
+          <t>ón: CL 54 48 33</t>
+        </is>
+      </c>
+      <c r="O284" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>Idioma extranjero inglés</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>Tarazá</t>
+        </is>
+      </c>
+      <c r="E285" t="inlineStr">
+        <is>
+          <t>08/07/2026 a las 10:47</t>
+        </is>
+      </c>
+      <c r="F285" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G285" t="inlineStr">
+        <is>
+          <t>Tarazá</t>
+        </is>
+      </c>
+      <c r="H285" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I285" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J285" t="inlineStr">
+        <is>
+          <t>I. E. RAFAEL NUNEZ</t>
+        </is>
+      </c>
+      <c r="K285" t="inlineStr">
+        <is>
+          <t>LICEO RAFAEL NUNEZ - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L285" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M285" t="inlineStr">
+        <is>
+          <t>B. VILLA DEL LAGO</t>
+        </is>
+      </c>
+      <c r="N285" t="inlineStr">
+        <is>
+          <t>ón: CL 28 28 18</t>
+        </is>
+      </c>
+      <c r="O285" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>Humanidades y lengua castellana</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>Arboletes</t>
+        </is>
+      </c>
+      <c r="E286" t="inlineStr">
+        <is>
+          <t>08/07/2026 a las 10:48</t>
+        </is>
+      </c>
+      <c r="F286" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="G286" t="inlineStr">
+        <is>
+          <t>Arboletes</t>
+        </is>
+      </c>
+      <c r="H286" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I286" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J286" t="inlineStr">
+        <is>
+          <t>I. E. R. LA CANDELARIA</t>
+        </is>
+      </c>
+      <c r="K286" t="inlineStr">
+        <is>
+          <t>COLEGIO LA CANDELARIA - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L286" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M286" t="inlineStr">
+        <is>
+          <t>CORREG.LA CANDELARIA</t>
+        </is>
+      </c>
+      <c r="N286" t="inlineStr">
+        <is>
+          <t>ón: CORREG. LA CANDELARIA</t>
+        </is>
+      </c>
+      <c r="O286" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>Matemáticas</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>Arboletes</t>
+        </is>
+      </c>
+      <c r="E287" t="inlineStr">
+        <is>
+          <t>08/07/2026 a las 10:48</t>
+        </is>
+      </c>
+      <c r="F287" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="G287" t="inlineStr">
+        <is>
+          <t>Arboletes</t>
+        </is>
+      </c>
+      <c r="H287" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I287" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J287" t="inlineStr">
+        <is>
+          <t>I. E. JOSE MANUEL RESTREPO</t>
+        </is>
+      </c>
+      <c r="K287" t="inlineStr">
+        <is>
+          <t>COLEGIO JOSE MANUEL RESTREPO - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L287" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M287" t="inlineStr">
+        <is>
+          <t>BRR KENNEDY</t>
+        </is>
+      </c>
+      <c r="N287" t="inlineStr">
+        <is>
+          <t>ón: KR 33 27 51</t>
+        </is>
+      </c>
+      <c r="O287" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>Sonsón</t>
+        </is>
+      </c>
+      <c r="E288" t="inlineStr">
+        <is>
+          <t>08/07/2026 a las 10:48</t>
+        </is>
+      </c>
+      <c r="F288" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="G288" t="inlineStr">
+        <is>
+          <t>Sonsón</t>
+        </is>
+      </c>
+      <c r="H288" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I288" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J288" t="inlineStr">
+        <is>
+          <t>I. E. TECNICO AGROPECUARIO Y EN SALUD DE SONSN</t>
+        </is>
+      </c>
+      <c r="K288" t="inlineStr">
+        <is>
+          <t>C. E. R. LA CIENAGA</t>
+        </is>
+      </c>
+      <c r="L288" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M288" t="inlineStr">
+        <is>
+          <t>Dirección: VDA. LA CIENAGA</t>
+        </is>
+      </c>
+      <c r="N288" t="inlineStr">
+        <is>
+          <t>ón: VDA. LA CIENAGA</t>
+        </is>
+      </c>
+      <c r="O288" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="E289" t="inlineStr">
+        <is>
+          <t>08/07/2026 a las 13:22</t>
+        </is>
+      </c>
+      <c r="F289" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="G289" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="H289" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I289" t="inlineStr">
+        <is>
+          <t>ía de Educación: Medellín</t>
+        </is>
+      </c>
+      <c r="J289" t="inlineStr">
+        <is>
+          <t>INST EDUC MANUEL JOSE GOMEZ SERNA</t>
+        </is>
+      </c>
+      <c r="K289" t="inlineStr">
+        <is>
+          <t>SEC ESC ALEJO PIMIENTA</t>
+        </is>
+      </c>
+      <c r="L289" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M289" t="inlineStr">
+        <is>
+          <t>CASTILA</t>
+        </is>
+      </c>
+      <c r="N289" t="inlineStr">
+        <is>
+          <t>ón: CL 96 70 43</t>
+        </is>
+      </c>
+      <c r="O289" t="inlineStr">
         <is>
           <t>A</t>
         </is>

--- a/nuevas_plazas.xlsx
+++ b/nuevas_plazas.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O289"/>
+  <dimension ref="A1:O290"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19806,10 +19806,8 @@
           <t>08/07/2026 a las 10:42</t>
         </is>
       </c>
-      <c r="F259" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="F259" t="n">
+        <v>6</v>
       </c>
       <c r="G259" t="inlineStr">
         <is>
@@ -19883,10 +19881,8 @@
           <t>08/07/2026 a las 10:42</t>
         </is>
       </c>
-      <c r="F260" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
+      <c r="F260" t="n">
+        <v>11</v>
       </c>
       <c r="G260" t="inlineStr">
         <is>
@@ -19960,10 +19956,8 @@
           <t>08/07/2026 a las 10:42</t>
         </is>
       </c>
-      <c r="F261" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
+      <c r="F261" t="n">
+        <v>18</v>
       </c>
       <c r="G261" t="inlineStr">
         <is>
@@ -20037,10 +20031,8 @@
           <t>08/07/2026 a las 10:42</t>
         </is>
       </c>
-      <c r="F262" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
+      <c r="F262" t="n">
+        <v>16</v>
       </c>
       <c r="G262" t="inlineStr">
         <is>
@@ -20114,10 +20106,8 @@
           <t>08/07/2026 a las 10:42</t>
         </is>
       </c>
-      <c r="F263" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
+      <c r="F263" t="n">
+        <v>12</v>
       </c>
       <c r="G263" t="inlineStr">
         <is>
@@ -20191,10 +20181,8 @@
           <t>08/07/2026 a las 10:43</t>
         </is>
       </c>
-      <c r="F264" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
+      <c r="F264" t="n">
+        <v>11</v>
       </c>
       <c r="G264" t="inlineStr">
         <is>
@@ -20268,10 +20256,8 @@
           <t>08/07/2026 a las 10:43</t>
         </is>
       </c>
-      <c r="F265" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
+      <c r="F265" t="n">
+        <v>7</v>
       </c>
       <c r="G265" t="inlineStr">
         <is>
@@ -20345,10 +20331,8 @@
           <t>08/07/2026 a las 10:43</t>
         </is>
       </c>
-      <c r="F266" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="F266" t="n">
+        <v>3</v>
       </c>
       <c r="G266" t="inlineStr">
         <is>
@@ -20422,10 +20406,8 @@
           <t>08/07/2026 a las 10:43</t>
         </is>
       </c>
-      <c r="F267" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
+      <c r="F267" t="n">
+        <v>18</v>
       </c>
       <c r="G267" t="inlineStr">
         <is>
@@ -20499,10 +20481,8 @@
           <t>08/07/2026 a las 10:43</t>
         </is>
       </c>
-      <c r="F268" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
+      <c r="F268" t="n">
+        <v>18</v>
       </c>
       <c r="G268" t="inlineStr">
         <is>
@@ -20576,10 +20556,8 @@
           <t>08/07/2026 a las 10:43</t>
         </is>
       </c>
-      <c r="F269" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
+      <c r="F269" t="n">
+        <v>9</v>
       </c>
       <c r="G269" t="inlineStr">
         <is>
@@ -20653,10 +20631,8 @@
           <t>08/07/2026 a las 10:44</t>
         </is>
       </c>
-      <c r="F270" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
+      <c r="F270" t="n">
+        <v>19</v>
       </c>
       <c r="G270" t="inlineStr">
         <is>
@@ -20730,10 +20706,8 @@
           <t>08/07/2026 a las 10:44</t>
         </is>
       </c>
-      <c r="F271" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
+      <c r="F271" t="n">
+        <v>10</v>
       </c>
       <c r="G271" t="inlineStr">
         <is>
@@ -20807,10 +20781,8 @@
           <t>08/07/2026 a las 10:44</t>
         </is>
       </c>
-      <c r="F272" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="F272" t="n">
+        <v>8</v>
       </c>
       <c r="G272" t="inlineStr">
         <is>
@@ -20884,10 +20856,8 @@
           <t>08/07/2026 a las 10:44</t>
         </is>
       </c>
-      <c r="F273" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
+      <c r="F273" t="n">
+        <v>12</v>
       </c>
       <c r="G273" t="inlineStr">
         <is>
@@ -20961,10 +20931,8 @@
           <t>08/07/2026 a las 10:45</t>
         </is>
       </c>
-      <c r="F274" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
+      <c r="F274" t="n">
+        <v>11</v>
       </c>
       <c r="G274" t="inlineStr">
         <is>
@@ -21038,10 +21006,8 @@
           <t>08/07/2026 a las 10:45</t>
         </is>
       </c>
-      <c r="F275" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
+      <c r="F275" t="n">
+        <v>7</v>
       </c>
       <c r="G275" t="inlineStr">
         <is>
@@ -21115,10 +21081,8 @@
           <t>08/07/2026 a las 10:45</t>
         </is>
       </c>
-      <c r="F276" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
+      <c r="F276" t="n">
+        <v>19</v>
       </c>
       <c r="G276" t="inlineStr">
         <is>
@@ -21192,10 +21156,8 @@
           <t>08/07/2026 a las 10:45</t>
         </is>
       </c>
-      <c r="F277" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
+      <c r="F277" t="n">
+        <v>12</v>
       </c>
       <c r="G277" t="inlineStr">
         <is>
@@ -21269,10 +21231,8 @@
           <t>08/07/2026 a las 10:46</t>
         </is>
       </c>
-      <c r="F278" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
+      <c r="F278" t="n">
+        <v>19</v>
       </c>
       <c r="G278" t="inlineStr">
         <is>
@@ -21346,10 +21306,8 @@
           <t>08/07/2026 a las 10:46</t>
         </is>
       </c>
-      <c r="F279" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="F279" t="n">
+        <v>6</v>
       </c>
       <c r="G279" t="inlineStr">
         <is>
@@ -21423,10 +21381,8 @@
           <t>08/07/2026 a las 10:46</t>
         </is>
       </c>
-      <c r="F280" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
+      <c r="F280" t="n">
+        <v>16</v>
       </c>
       <c r="G280" t="inlineStr">
         <is>
@@ -21500,10 +21456,8 @@
           <t>08/07/2026 a las 10:46</t>
         </is>
       </c>
-      <c r="F281" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
+      <c r="F281" t="n">
+        <v>20</v>
       </c>
       <c r="G281" t="inlineStr">
         <is>
@@ -21577,10 +21531,8 @@
           <t>08/07/2026 a las 10:47</t>
         </is>
       </c>
-      <c r="F282" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
+      <c r="F282" t="n">
+        <v>10</v>
       </c>
       <c r="G282" t="inlineStr">
         <is>
@@ -21654,10 +21606,8 @@
           <t>08/07/2026 a las 10:47</t>
         </is>
       </c>
-      <c r="F283" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
+      <c r="F283" t="n">
+        <v>18</v>
       </c>
       <c r="G283" t="inlineStr">
         <is>
@@ -21731,10 +21681,8 @@
           <t>08/07/2026 a las 10:47</t>
         </is>
       </c>
-      <c r="F284" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
+      <c r="F284" t="n">
+        <v>11</v>
       </c>
       <c r="G284" t="inlineStr">
         <is>
@@ -21808,10 +21756,8 @@
           <t>08/07/2026 a las 10:47</t>
         </is>
       </c>
-      <c r="F285" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="F285" t="n">
+        <v>6</v>
       </c>
       <c r="G285" t="inlineStr">
         <is>
@@ -21885,10 +21831,8 @@
           <t>08/07/2026 a las 10:48</t>
         </is>
       </c>
-      <c r="F286" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
+      <c r="F286" t="n">
+        <v>18</v>
       </c>
       <c r="G286" t="inlineStr">
         <is>
@@ -21962,10 +21906,8 @@
           <t>08/07/2026 a las 10:48</t>
         </is>
       </c>
-      <c r="F287" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
+      <c r="F287" t="n">
+        <v>14</v>
       </c>
       <c r="G287" t="inlineStr">
         <is>
@@ -22039,10 +21981,8 @@
           <t>08/07/2026 a las 10:48</t>
         </is>
       </c>
-      <c r="F288" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
+      <c r="F288" t="n">
+        <v>31</v>
       </c>
       <c r="G288" t="inlineStr">
         <is>
@@ -22116,10 +22056,8 @@
           <t>08/07/2026 a las 13:22</t>
         </is>
       </c>
-      <c r="F289" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
+      <c r="F289" t="n">
+        <v>12</v>
       </c>
       <c r="G289" t="inlineStr">
         <is>
@@ -22162,6 +22100,83 @@
         </is>
       </c>
       <c r="O289" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>Educación artística - artes plásticas</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>Rionegro</t>
+        </is>
+      </c>
+      <c r="E290" t="inlineStr">
+        <is>
+          <t>10/07/2026 a las 10:27</t>
+        </is>
+      </c>
+      <c r="F290" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G290" t="inlineStr">
+        <is>
+          <t>Rionegro</t>
+        </is>
+      </c>
+      <c r="H290" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I290" t="inlineStr">
+        <is>
+          <t>ía de Educación: Rionegro</t>
+        </is>
+      </c>
+      <c r="J290" t="inlineStr">
+        <is>
+          <t>I. E. CONCEJO MUNICIPAL EL PORVENIR</t>
+        </is>
+      </c>
+      <c r="K290" t="inlineStr">
+        <is>
+          <t>COLEGIO CONCEJO MUNICIPAL EL PORVENIR - SEDE PRINC</t>
+        </is>
+      </c>
+      <c r="L290" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M290" t="inlineStr">
+        <is>
+          <t>COMUNA OCCIDENTAL</t>
+        </is>
+      </c>
+      <c r="N290" t="inlineStr">
+        <is>
+          <t>ón: CRA 69 48B-63</t>
+        </is>
+      </c>
+      <c r="O290" t="inlineStr">
         <is>
           <t>A</t>
         </is>

--- a/nuevas_plazas.xlsx
+++ b/nuevas_plazas.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O290"/>
+  <dimension ref="A1:O310"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22131,52 +22131,1590 @@
           <t>10/07/2026 a las 10:27</t>
         </is>
       </c>
-      <c r="F290" t="inlineStr">
+      <c r="F290" t="n">
+        <v>10</v>
+      </c>
+      <c r="G290" t="inlineStr">
+        <is>
+          <t>Rionegro</t>
+        </is>
+      </c>
+      <c r="H290" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I290" t="inlineStr">
+        <is>
+          <t>ía de Educación: Rionegro</t>
+        </is>
+      </c>
+      <c r="J290" t="inlineStr">
+        <is>
+          <t>I. E. CONCEJO MUNICIPAL EL PORVENIR</t>
+        </is>
+      </c>
+      <c r="K290" t="inlineStr">
+        <is>
+          <t>COLEGIO CONCEJO MUNICIPAL EL PORVENIR - SEDE PRINC</t>
+        </is>
+      </c>
+      <c r="L290" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M290" t="inlineStr">
+        <is>
+          <t>COMUNA OCCIDENTAL</t>
+        </is>
+      </c>
+      <c r="N290" t="inlineStr">
+        <is>
+          <t>ón: CRA 69 48B-63</t>
+        </is>
+      </c>
+      <c r="O290" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>Ciencias naturales química</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="E291" t="inlineStr">
+        <is>
+          <t>11/07/2026 a las 14:54</t>
+        </is>
+      </c>
+      <c r="F291" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="G291" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="H291" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I291" t="inlineStr">
+        <is>
+          <t>ía de Educación: Medellín</t>
+        </is>
+      </c>
+      <c r="J291" t="inlineStr">
+        <is>
+          <t>INST EDUC LA SALLE DE CAMPOAMOR</t>
+        </is>
+      </c>
+      <c r="K291" t="inlineStr">
+        <is>
+          <t>INST EDUC LA SALLE DE CAMPOAMOR - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L291" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M291" t="inlineStr">
+        <is>
+          <t>Dirección: CR 65B NO 4-49</t>
+        </is>
+      </c>
+      <c r="N291" t="inlineStr">
+        <is>
+          <t>ón: CR 65B NO 4-49</t>
+        </is>
+      </c>
+      <c r="O291" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Priorizadas para jóvenes entre 18 y 28 años</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>Ciencias naturales y educación ambiental</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="E292" t="inlineStr">
+        <is>
+          <t>11/07/2026 a las 14:54</t>
+        </is>
+      </c>
+      <c r="F292" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="G292" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="H292" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I292" t="inlineStr">
+        <is>
+          <t>ía de Educación: Medellín</t>
+        </is>
+      </c>
+      <c r="J292" t="inlineStr">
+        <is>
+          <t>INST EDUC GERARDO VALENCIA CANO</t>
+        </is>
+      </c>
+      <c r="K292" t="inlineStr">
+        <is>
+          <t>INST EDUC GERARDO VALENCIA CANO - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L292" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M292" t="inlineStr">
+        <is>
+          <t>SAN GERMAN</t>
+        </is>
+      </c>
+      <c r="N292" t="inlineStr">
+        <is>
+          <t>ón: CL 65 74 B 273</t>
+        </is>
+      </c>
+      <c r="O292" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>Ciencias naturales y educación ambiental</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="E293" t="inlineStr">
+        <is>
+          <t>11/07/2026 a las 14:54</t>
+        </is>
+      </c>
+      <c r="F293" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="G293" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="H293" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I293" t="inlineStr">
+        <is>
+          <t>ía de Educación: Medellín</t>
+        </is>
+      </c>
+      <c r="J293" t="inlineStr">
+        <is>
+          <t>INST EDUC SAN ANTONIO DE PRADO</t>
+        </is>
+      </c>
+      <c r="K293" t="inlineStr">
+        <is>
+          <t>SEC ESC MANUEL MARIA MALLARINO</t>
+        </is>
+      </c>
+      <c r="L293" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M293" t="inlineStr">
+        <is>
+          <t>Dirección: CL 40 SUR 75 B 101</t>
+        </is>
+      </c>
+      <c r="N293" t="inlineStr">
+        <is>
+          <t>ón: CL 40 SUR 75 B 101</t>
+        </is>
+      </c>
+      <c r="O293" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>Ciencias sociales</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="E294" t="inlineStr">
+        <is>
+          <t>11/07/2026 a las 14:54</t>
+        </is>
+      </c>
+      <c r="F294" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="G294" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="H294" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I294" t="inlineStr">
+        <is>
+          <t>ía de Educación: Medellín</t>
+        </is>
+      </c>
+      <c r="J294" t="inlineStr">
+        <is>
+          <t>INST EDUC CONCEJO DE MEDELLIN</t>
+        </is>
+      </c>
+      <c r="K294" t="inlineStr">
+        <is>
+          <t>INST EDUC CONCEJO DE MEDELLIN - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L294" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M294" t="inlineStr">
+        <is>
+          <t>Dirección: CR 82 NO 47A-65</t>
+        </is>
+      </c>
+      <c r="N294" t="inlineStr">
+        <is>
+          <t>ón: CR 82 NO 47A-65</t>
+        </is>
+      </c>
+      <c r="O294" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>Ciencias sociales</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="E295" t="inlineStr">
+        <is>
+          <t>11/07/2026 a las 14:54</t>
+        </is>
+      </c>
+      <c r="F295" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="G295" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="H295" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I295" t="inlineStr">
+        <is>
+          <t>ía de Educación: Medellín</t>
+        </is>
+      </c>
+      <c r="J295" t="inlineStr">
+        <is>
+          <t>INST EDUC JORGE ROBLEDO</t>
+        </is>
+      </c>
+      <c r="K295" t="inlineStr">
+        <is>
+          <t>INST EDUC JORGE ROBLEDO - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L295" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M295" t="inlineStr">
+        <is>
+          <t>Dirección: CL 65 87 74</t>
+        </is>
+      </c>
+      <c r="N295" t="inlineStr">
+        <is>
+          <t>ón: CL 65 87 74</t>
+        </is>
+      </c>
+      <c r="O295" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>Ciencias sociales</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="E296" t="inlineStr">
+        <is>
+          <t>11/07/2026 a las 14:54</t>
+        </is>
+      </c>
+      <c r="F296" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="G296" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="H296" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I296" t="inlineStr">
+        <is>
+          <t>ía de Educación: Medellín</t>
+        </is>
+      </c>
+      <c r="J296" t="inlineStr">
+        <is>
+          <t>INST EDUC BARRIO SANTA MARGARITA</t>
+        </is>
+      </c>
+      <c r="K296" t="inlineStr">
+        <is>
+          <t>INST EDUC BARRIO SANTA MARGARITA - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L296" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M296" t="inlineStr">
+        <is>
+          <t>Dirección: CLL 63 NO 108BB-160</t>
+        </is>
+      </c>
+      <c r="N296" t="inlineStr">
+        <is>
+          <t>ón: CLL 63 NO 108BB-160</t>
+        </is>
+      </c>
+      <c r="O296" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>Educación artística - artes plásticas</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="E297" t="inlineStr">
+        <is>
+          <t>11/07/2026 a las 14:54</t>
+        </is>
+      </c>
+      <c r="F297" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="G297" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="H297" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I297" t="inlineStr">
+        <is>
+          <t>ía de Educación: Medellín</t>
+        </is>
+      </c>
+      <c r="J297" t="inlineStr">
+        <is>
+          <t>INST EDUC MARCO FIDEL SUAREZ</t>
+        </is>
+      </c>
+      <c r="K297" t="inlineStr">
+        <is>
+          <t>INST EDUC MARCO FIDEL SUAREZ - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L297" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M297" t="inlineStr">
+        <is>
+          <t>SURAMERICANA</t>
+        </is>
+      </c>
+      <c r="N297" t="inlineStr">
+        <is>
+          <t>ón: KR 70 49 70</t>
+        </is>
+      </c>
+      <c r="O297" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>Educación religiosa</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="E298" t="inlineStr">
+        <is>
+          <t>11/07/2026 a las 14:54</t>
+        </is>
+      </c>
+      <c r="F298" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="G298" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="H298" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I298" t="inlineStr">
+        <is>
+          <t>ía de Educación: Medellín</t>
+        </is>
+      </c>
+      <c r="J298" t="inlineStr">
+        <is>
+          <t>INST EDUC ESCUELA NORMAL SUPERIOR DE MEDELLIN</t>
+        </is>
+      </c>
+      <c r="K298" t="inlineStr">
+        <is>
+          <t>INST EDUC ESCUELA NORMAL SUPERIOR DE MEDELLIN - SE</t>
+        </is>
+      </c>
+      <c r="L298" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M298" t="inlineStr">
+        <is>
+          <t>Dirección: KR 34 65 02</t>
+        </is>
+      </c>
+      <c r="N298" t="inlineStr">
+        <is>
+          <t>ón: KR 34 65 02</t>
+        </is>
+      </c>
+      <c r="O298" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>Humanidades y lengua castellana</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="E299" t="inlineStr">
+        <is>
+          <t>11/07/2026 a las 14:54</t>
+        </is>
+      </c>
+      <c r="F299" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="G299" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="H299" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I299" t="inlineStr">
+        <is>
+          <t>ía de Educación: Medellín</t>
+        </is>
+      </c>
+      <c r="J299" t="inlineStr">
+        <is>
+          <t>INST EDUC ASAMBLEA DEPARTAMENTAL</t>
+        </is>
+      </c>
+      <c r="K299" t="inlineStr">
+        <is>
+          <t>INST EDUC ASAMBLEA DEPARTAMENTAL - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L299" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M299" t="inlineStr">
+        <is>
+          <t>MIRAFLORES</t>
+        </is>
+      </c>
+      <c r="N299" t="inlineStr">
+        <is>
+          <t>ón: KR 27 47 45</t>
+        </is>
+      </c>
+      <c r="O299" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>Humanidades y lengua castellana</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="E300" t="inlineStr">
+        <is>
+          <t>11/07/2026 a las 14:54</t>
+        </is>
+      </c>
+      <c r="F300" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="G300" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="H300" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I300" t="inlineStr">
+        <is>
+          <t>ía de Educación: Medellín</t>
+        </is>
+      </c>
+      <c r="J300" t="inlineStr">
+        <is>
+          <t>INST EDUC GERARDO VALENCIA CANO</t>
+        </is>
+      </c>
+      <c r="K300" t="inlineStr">
+        <is>
+          <t>INST EDUC GERARDO VALENCIA CANO - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L300" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M300" t="inlineStr">
+        <is>
+          <t>SAN GERMAN</t>
+        </is>
+      </c>
+      <c r="N300" t="inlineStr">
+        <is>
+          <t>ón: CL 65 74 B 273</t>
+        </is>
+      </c>
+      <c r="O300" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>Humanidades y lengua castellana</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="E301" t="inlineStr">
+        <is>
+          <t>11/07/2026 a las 14:54</t>
+        </is>
+      </c>
+      <c r="F301" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="G301" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="H301" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I301" t="inlineStr">
+        <is>
+          <t>ía de Educación: Medellín</t>
+        </is>
+      </c>
+      <c r="J301" t="inlineStr">
+        <is>
+          <t>INST EDUC JOSE ACEVEDO Y GOMEZ</t>
+        </is>
+      </c>
+      <c r="K301" t="inlineStr">
+        <is>
+          <t>INST EDUC JOSE ACEVEDO Y GOMEZ - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L301" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M301" t="inlineStr">
+        <is>
+          <t>GUAYABAL</t>
+        </is>
+      </c>
+      <c r="N301" t="inlineStr">
+        <is>
+          <t>ón: CL 8 SUR 52 B 72</t>
+        </is>
+      </c>
+      <c r="O301" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>Idioma extranjero inglés</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="E302" t="inlineStr">
+        <is>
+          <t>11/07/2026 a las 14:55</t>
+        </is>
+      </c>
+      <c r="F302" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="G302" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="H302" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I302" t="inlineStr">
+        <is>
+          <t>ía de Educación: Medellín</t>
+        </is>
+      </c>
+      <c r="J302" t="inlineStr">
+        <is>
+          <t>INST EDUC SAN CRISTOBAL</t>
+        </is>
+      </c>
+      <c r="K302" t="inlineStr">
+        <is>
+          <t>INST EDUC SAN CRISTOBAL - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L302" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M302" t="inlineStr">
+        <is>
+          <t>SAN CRISTOBAL</t>
+        </is>
+      </c>
+      <c r="N302" t="inlineStr">
+        <is>
+          <t>ón: KR 131 65 07</t>
+        </is>
+      </c>
+      <c r="O302" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>Matemáticas</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="E303" t="inlineStr">
+        <is>
+          <t>11/07/2026 a las 14:55</t>
+        </is>
+      </c>
+      <c r="F303" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="G303" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="H303" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I303" t="inlineStr">
+        <is>
+          <t>ía de Educación: Medellín</t>
+        </is>
+      </c>
+      <c r="J303" t="inlineStr">
+        <is>
+          <t>INST EDUC LORENZA VILLEGAS DE SANTOS</t>
+        </is>
+      </c>
+      <c r="K303" t="inlineStr">
+        <is>
+          <t>INST EDUC LORENZA VILLEGAS DE SANTOS - SEDE PRINCI</t>
+        </is>
+      </c>
+      <c r="L303" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M303" t="inlineStr">
+        <is>
+          <t>Dirección: CR 51 NO 87-040</t>
+        </is>
+      </c>
+      <c r="N303" t="inlineStr">
+        <is>
+          <t>ón: CR 51 NO 87-040</t>
+        </is>
+      </c>
+      <c r="O303" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>Matemáticas</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="E304" t="inlineStr">
+        <is>
+          <t>11/07/2026 a las 14:55</t>
+        </is>
+      </c>
+      <c r="F304" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="G304" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="H304" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I304" t="inlineStr">
+        <is>
+          <t>ía de Educación: Medellín</t>
+        </is>
+      </c>
+      <c r="J304" t="inlineStr">
+        <is>
+          <t>INST EDUC SAN JOSE OBRERO</t>
+        </is>
+      </c>
+      <c r="K304" t="inlineStr">
+        <is>
+          <t>INST EDUC SAN JOSE OBRERO - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L304" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M304" t="inlineStr">
+        <is>
+          <t>VEREDA LA FLORIDA</t>
+        </is>
+      </c>
+      <c r="N304" t="inlineStr">
+        <is>
+          <t>ón: CR 85 48 A SUR 51</t>
+        </is>
+      </c>
+      <c r="O304" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>Matemáticas</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="E305" t="inlineStr">
+        <is>
+          <t>11/07/2026 a las 14:55</t>
+        </is>
+      </c>
+      <c r="F305" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="G290" t="inlineStr">
-        <is>
-          <t>Rionegro</t>
-        </is>
-      </c>
-      <c r="H290" t="inlineStr">
-        <is>
-          <t>Antioquia</t>
-        </is>
-      </c>
-      <c r="I290" t="inlineStr">
-        <is>
-          <t>ía de Educación: Rionegro</t>
-        </is>
-      </c>
-      <c r="J290" t="inlineStr">
-        <is>
-          <t>I. E. CONCEJO MUNICIPAL EL PORVENIR</t>
-        </is>
-      </c>
-      <c r="K290" t="inlineStr">
-        <is>
-          <t>COLEGIO CONCEJO MUNICIPAL EL PORVENIR - SEDE PRINC</t>
-        </is>
-      </c>
-      <c r="L290" t="inlineStr">
+      <c r="G305" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="H305" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I305" t="inlineStr">
+        <is>
+          <t>ía de Educación: Medellín</t>
+        </is>
+      </c>
+      <c r="J305" t="inlineStr">
+        <is>
+          <t>INST EDUC COMPARTIR</t>
+        </is>
+      </c>
+      <c r="K305" t="inlineStr">
+        <is>
+          <t>INST EDUC COMPARTIR - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L305" t="inlineStr">
         <is>
           <t>URBANA</t>
         </is>
       </c>
-      <c r="M290" t="inlineStr">
-        <is>
-          <t>COMUNA OCCIDENTAL</t>
-        </is>
-      </c>
-      <c r="N290" t="inlineStr">
-        <is>
-          <t>ón: CRA 69 48B-63</t>
-        </is>
-      </c>
-      <c r="O290" t="inlineStr">
+      <c r="M305" t="inlineStr">
+        <is>
+          <t>Dirección: KR 62 A 42 D 26 SUR</t>
+        </is>
+      </c>
+      <c r="N305" t="inlineStr">
+        <is>
+          <t>ón: KR 62 A 42 D 26 SUR</t>
+        </is>
+      </c>
+      <c r="O305" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Priorizadas para jóvenes entre 18 y 28 años</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>Tecnología e informática</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="E306" t="inlineStr">
+        <is>
+          <t>11/07/2026 a las 14:55</t>
+        </is>
+      </c>
+      <c r="F306" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G306" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="H306" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I306" t="inlineStr">
+        <is>
+          <t>ía de Educación: Medellín</t>
+        </is>
+      </c>
+      <c r="J306" t="inlineStr">
+        <is>
+          <t>INST EDUC ARZOBISPO TULIO BOTERO SALAZAR</t>
+        </is>
+      </c>
+      <c r="K306" t="inlineStr">
+        <is>
+          <t>INST EDUC ARZOBISPO TULIO BOTERO SALAZAR - SEDE PR</t>
+        </is>
+      </c>
+      <c r="L306" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M306" t="inlineStr">
+        <is>
+          <t>Dirección: CL 49 A 03 A 006</t>
+        </is>
+      </c>
+      <c r="N306" t="inlineStr">
+        <is>
+          <t>ón: CL 49 A 03 A 006</t>
+        </is>
+      </c>
+      <c r="O306" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>Tecnología e informática</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="E307" t="inlineStr">
+        <is>
+          <t>11/07/2026 a las 14:55</t>
+        </is>
+      </c>
+      <c r="F307" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G307" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="H307" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I307" t="inlineStr">
+        <is>
+          <t>ía de Educación: Medellín</t>
+        </is>
+      </c>
+      <c r="J307" t="inlineStr">
+        <is>
+          <t>INST EDUC MARCO FIDEL SUAREZ</t>
+        </is>
+      </c>
+      <c r="K307" t="inlineStr">
+        <is>
+          <t>INST EDUC MARCO FIDEL SUAREZ - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L307" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M307" t="inlineStr">
+        <is>
+          <t>SURAMERICANA</t>
+        </is>
+      </c>
+      <c r="N307" t="inlineStr">
+        <is>
+          <t>ón: KR 70 49 70</t>
+        </is>
+      </c>
+      <c r="O307" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>Educación artística – música</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="E308" t="inlineStr">
+        <is>
+          <t>11/07/2026 a las 14:55</t>
+        </is>
+      </c>
+      <c r="F308" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="G308" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="H308" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I308" t="inlineStr">
+        <is>
+          <t>ía de Educación: Medellín</t>
+        </is>
+      </c>
+      <c r="J308" t="inlineStr">
+        <is>
+          <t>INST EDUC CIUDADELA LAS AMERICAS</t>
+        </is>
+      </c>
+      <c r="K308" t="inlineStr">
+        <is>
+          <t>INST EDUC CIUDADELA LAS AMERICAS - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L308" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M308" t="inlineStr">
+        <is>
+          <t>Dirección: CLL 111 NO 79-77</t>
+        </is>
+      </c>
+      <c r="N308" t="inlineStr">
+        <is>
+          <t>ón: CLL 111 NO 79-77</t>
+        </is>
+      </c>
+      <c r="O308" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>Tecnología e informática</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="E309" t="inlineStr">
+        <is>
+          <t>11/07/2026 a las 14:55</t>
+        </is>
+      </c>
+      <c r="F309" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G309" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="H309" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I309" t="inlineStr">
+        <is>
+          <t>ía de Educación: Medellín</t>
+        </is>
+      </c>
+      <c r="J309" t="inlineStr">
+        <is>
+          <t>INST EDUC PRESBITERO JUAN J. ESCOBAR</t>
+        </is>
+      </c>
+      <c r="K309" t="inlineStr">
+        <is>
+          <t>INST EDUC PRESBITERO JUAN J. ESCOBAR - SEDE PRINCI</t>
+        </is>
+      </c>
+      <c r="L309" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M309" t="inlineStr">
+        <is>
+          <t>CORREG. SAN CRISTOBAL</t>
+        </is>
+      </c>
+      <c r="N309" t="inlineStr">
+        <is>
+          <t>ón: CL 62 128 120</t>
+        </is>
+      </c>
+      <c r="O309" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>Humanidades y lengua castellana</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="E310" t="inlineStr">
+        <is>
+          <t>11/07/2026 a las 14:55</t>
+        </is>
+      </c>
+      <c r="F310" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="G310" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="H310" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I310" t="inlineStr">
+        <is>
+          <t>ía de Educación: Medellín</t>
+        </is>
+      </c>
+      <c r="J310" t="inlineStr">
+        <is>
+          <t>INST EDUC ARZOBISPO TULIO BOTERO SALAZAR</t>
+        </is>
+      </c>
+      <c r="K310" t="inlineStr">
+        <is>
+          <t>INST EDUC ARZOBISPO TULIO BOTERO SALAZAR - SEDE PR</t>
+        </is>
+      </c>
+      <c r="L310" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M310" t="inlineStr">
+        <is>
+          <t>Dirección: CL 49 A 03 A 006</t>
+        </is>
+      </c>
+      <c r="N310" t="inlineStr">
+        <is>
+          <t>ón: CL 49 A 03 A 006</t>
+        </is>
+      </c>
+      <c r="O310" t="inlineStr">
         <is>
           <t>A</t>
         </is>

--- a/nuevas_plazas.xlsx
+++ b/nuevas_plazas.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O310"/>
+  <dimension ref="A1:O311"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22206,10 +22206,8 @@
           <t>11/07/2026 a las 14:54</t>
         </is>
       </c>
-      <c r="F291" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
+      <c r="F291" t="n">
+        <v>12</v>
       </c>
       <c r="G291" t="inlineStr">
         <is>
@@ -22283,10 +22281,8 @@
           <t>11/07/2026 a las 14:54</t>
         </is>
       </c>
-      <c r="F292" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
+      <c r="F292" t="n">
+        <v>22</v>
       </c>
       <c r="G292" t="inlineStr">
         <is>
@@ -22360,10 +22356,8 @@
           <t>11/07/2026 a las 14:54</t>
         </is>
       </c>
-      <c r="F293" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
+      <c r="F293" t="n">
+        <v>21</v>
       </c>
       <c r="G293" t="inlineStr">
         <is>
@@ -22437,10 +22431,8 @@
           <t>11/07/2026 a las 14:54</t>
         </is>
       </c>
-      <c r="F294" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
+      <c r="F294" t="n">
+        <v>18</v>
       </c>
       <c r="G294" t="inlineStr">
         <is>
@@ -22514,10 +22506,8 @@
           <t>11/07/2026 a las 14:54</t>
         </is>
       </c>
-      <c r="F295" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
+      <c r="F295" t="n">
+        <v>18</v>
       </c>
       <c r="G295" t="inlineStr">
         <is>
@@ -22591,10 +22581,8 @@
           <t>11/07/2026 a las 14:54</t>
         </is>
       </c>
-      <c r="F296" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
+      <c r="F296" t="n">
+        <v>16</v>
       </c>
       <c r="G296" t="inlineStr">
         <is>
@@ -22668,10 +22656,8 @@
           <t>11/07/2026 a las 14:54</t>
         </is>
       </c>
-      <c r="F297" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
+      <c r="F297" t="n">
+        <v>12</v>
       </c>
       <c r="G297" t="inlineStr">
         <is>
@@ -22745,10 +22731,8 @@
           <t>11/07/2026 a las 14:54</t>
         </is>
       </c>
-      <c r="F298" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
+      <c r="F298" t="n">
+        <v>11</v>
       </c>
       <c r="G298" t="inlineStr">
         <is>
@@ -22822,10 +22806,8 @@
           <t>11/07/2026 a las 14:54</t>
         </is>
       </c>
-      <c r="F299" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
+      <c r="F299" t="n">
+        <v>12</v>
       </c>
       <c r="G299" t="inlineStr">
         <is>
@@ -22899,10 +22881,8 @@
           <t>11/07/2026 a las 14:54</t>
         </is>
       </c>
-      <c r="F300" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
+      <c r="F300" t="n">
+        <v>14</v>
       </c>
       <c r="G300" t="inlineStr">
         <is>
@@ -22976,10 +22956,8 @@
           <t>11/07/2026 a las 14:54</t>
         </is>
       </c>
-      <c r="F301" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
+      <c r="F301" t="n">
+        <v>14</v>
       </c>
       <c r="G301" t="inlineStr">
         <is>
@@ -23053,10 +23031,8 @@
           <t>11/07/2026 a las 14:55</t>
         </is>
       </c>
-      <c r="F302" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
+      <c r="F302" t="n">
+        <v>15</v>
       </c>
       <c r="G302" t="inlineStr">
         <is>
@@ -23130,10 +23106,8 @@
           <t>11/07/2026 a las 14:55</t>
         </is>
       </c>
-      <c r="F303" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
+      <c r="F303" t="n">
+        <v>9</v>
       </c>
       <c r="G303" t="inlineStr">
         <is>
@@ -23207,10 +23181,8 @@
           <t>11/07/2026 a las 14:55</t>
         </is>
       </c>
-      <c r="F304" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
+      <c r="F304" t="n">
+        <v>9</v>
       </c>
       <c r="G304" t="inlineStr">
         <is>
@@ -23284,10 +23256,8 @@
           <t>11/07/2026 a las 14:55</t>
         </is>
       </c>
-      <c r="F305" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
+      <c r="F305" t="n">
+        <v>10</v>
       </c>
       <c r="G305" t="inlineStr">
         <is>
@@ -23361,10 +23331,8 @@
           <t>11/07/2026 a las 14:55</t>
         </is>
       </c>
-      <c r="F306" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="F306" t="n">
+        <v>6</v>
       </c>
       <c r="G306" t="inlineStr">
         <is>
@@ -23438,10 +23406,8 @@
           <t>11/07/2026 a las 14:55</t>
         </is>
       </c>
-      <c r="F307" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="F307" t="n">
+        <v>8</v>
       </c>
       <c r="G307" t="inlineStr">
         <is>
@@ -23515,10 +23481,8 @@
           <t>11/07/2026 a las 14:55</t>
         </is>
       </c>
-      <c r="F308" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
+      <c r="F308" t="n">
+        <v>9</v>
       </c>
       <c r="G308" t="inlineStr">
         <is>
@@ -23592,10 +23556,8 @@
           <t>11/07/2026 a las 14:55</t>
         </is>
       </c>
-      <c r="F309" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
+      <c r="F309" t="n">
+        <v>7</v>
       </c>
       <c r="G309" t="inlineStr">
         <is>
@@ -23669,10 +23631,8 @@
           <t>11/07/2026 a las 14:55</t>
         </is>
       </c>
-      <c r="F310" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
+      <c r="F310" t="n">
+        <v>13</v>
       </c>
       <c r="G310" t="inlineStr">
         <is>
@@ -23715,6 +23675,83 @@
         </is>
       </c>
       <c r="O310" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>Educación artística - artes plásticas</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>Rionegro</t>
+        </is>
+      </c>
+      <c r="E311" t="inlineStr">
+        <is>
+          <t>15/07/2026 a las 18:00</t>
+        </is>
+      </c>
+      <c r="F311" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="G311" t="inlineStr">
+        <is>
+          <t>Rionegro</t>
+        </is>
+      </c>
+      <c r="H311" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I311" t="inlineStr">
+        <is>
+          <t>ía de Educación: Rionegro</t>
+        </is>
+      </c>
+      <c r="J311" t="inlineStr">
+        <is>
+          <t>I. E. CONCEJO MUNICIPAL EL PORVENIR</t>
+        </is>
+      </c>
+      <c r="K311" t="inlineStr">
+        <is>
+          <t>COLEGIO CONCEJO MUNICIPAL EL PORVENIR - SEDE PRINC</t>
+        </is>
+      </c>
+      <c r="L311" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M311" t="inlineStr">
+        <is>
+          <t>COMUNA OCCIDENTAL</t>
+        </is>
+      </c>
+      <c r="N311" t="inlineStr">
+        <is>
+          <t>ón: CRA 69 48B-63</t>
+        </is>
+      </c>
+      <c r="O311" t="inlineStr">
         <is>
           <t>A</t>
         </is>

--- a/nuevas_plazas.xlsx
+++ b/nuevas_plazas.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O311"/>
+  <dimension ref="A1:O322"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23706,10 +23706,8 @@
           <t>15/07/2026 a las 18:00</t>
         </is>
       </c>
-      <c r="F311" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
+      <c r="F311" t="n">
+        <v>22</v>
       </c>
       <c r="G311" t="inlineStr">
         <is>
@@ -23752,6 +23750,853 @@
         </is>
       </c>
       <c r="O311" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Priorizadas para jóvenes entre 18 y 28 años</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="E312" t="inlineStr">
+        <is>
+          <t>18/07/2026 a las 09:51</t>
+        </is>
+      </c>
+      <c r="F312" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="G312" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="H312" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I312" t="inlineStr">
+        <is>
+          <t>ía de Educación: Medellín</t>
+        </is>
+      </c>
+      <c r="J312" t="inlineStr">
+        <is>
+          <t>INST EDUC JOSE MARIA BERNAL</t>
+        </is>
+      </c>
+      <c r="K312" t="inlineStr">
+        <is>
+          <t>INST EDUC JOSE MARIA BERNAL - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L312" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M312" t="inlineStr">
+        <is>
+          <t>Dirección: KR 70 A 13 A 19</t>
+        </is>
+      </c>
+      <c r="N312" t="inlineStr">
+        <is>
+          <t>ón: KR 70 A 13 A 19</t>
+        </is>
+      </c>
+      <c r="O312" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>Preescolar</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="E313" t="inlineStr">
+        <is>
+          <t>18/07/2026 a las 09:52</t>
+        </is>
+      </c>
+      <c r="F313" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="G313" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="H313" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I313" t="inlineStr">
+        <is>
+          <t>ía de Educación: Medellín</t>
+        </is>
+      </c>
+      <c r="J313" t="inlineStr">
+        <is>
+          <t>INST EDUC JESUS MARIA - EL ROSAL</t>
+        </is>
+      </c>
+      <c r="K313" t="inlineStr">
+        <is>
+          <t>INST EDUC JESUS MARIA - EL ROSAL - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L313" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M313" t="inlineStr">
+        <is>
+          <t>CASTILLA</t>
+        </is>
+      </c>
+      <c r="N313" t="inlineStr">
+        <is>
+          <t>ón: KR 72 95 20</t>
+        </is>
+      </c>
+      <c r="O313" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="E314" t="inlineStr">
+        <is>
+          <t>18/07/2026 a las 09:52</t>
+        </is>
+      </c>
+      <c r="F314" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="G314" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="H314" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I314" t="inlineStr">
+        <is>
+          <t>ía de Educación: Medellín</t>
+        </is>
+      </c>
+      <c r="J314" t="inlineStr">
+        <is>
+          <t>INST EDUC YERMO Y PARRES</t>
+        </is>
+      </c>
+      <c r="K314" t="inlineStr">
+        <is>
+          <t>SEC ESC CARLOS FRANCO</t>
+        </is>
+      </c>
+      <c r="L314" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M314" t="inlineStr">
+        <is>
+          <t>BELEN</t>
+        </is>
+      </c>
+      <c r="N314" t="inlineStr">
+        <is>
+          <t>ón: CL 23 78 48</t>
+        </is>
+      </c>
+      <c r="O314" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="E315" t="inlineStr">
+        <is>
+          <t>18/07/2026 a las 09:52</t>
+        </is>
+      </c>
+      <c r="F315" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G315" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="H315" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I315" t="inlineStr">
+        <is>
+          <t>ía de Educación: Medellín</t>
+        </is>
+      </c>
+      <c r="J315" t="inlineStr">
+        <is>
+          <t>INST EDUC GABRIEL GARCIA MARQUEZ</t>
+        </is>
+      </c>
+      <c r="K315" t="inlineStr">
+        <is>
+          <t>INST EDUC GABRIEL GARCIA MARQUEZ - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L315" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M315" t="inlineStr">
+        <is>
+          <t>Dirección: KR 8 A 57 A 93</t>
+        </is>
+      </c>
+      <c r="N315" t="inlineStr">
+        <is>
+          <t>ón: KR 8 A 57 A 93</t>
+        </is>
+      </c>
+      <c r="O315" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>Preescolar</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="E316" t="inlineStr">
+        <is>
+          <t>18/07/2026 a las 09:52</t>
+        </is>
+      </c>
+      <c r="F316" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G316" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="H316" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I316" t="inlineStr">
+        <is>
+          <t>ía de Educación: Medellín</t>
+        </is>
+      </c>
+      <c r="J316" t="inlineStr">
+        <is>
+          <t>INST EDUC PEDRO LUIS VILLA</t>
+        </is>
+      </c>
+      <c r="K316" t="inlineStr">
+        <is>
+          <t>SEC ESC MARCO FIDEL SUAREZ</t>
+        </is>
+      </c>
+      <c r="L316" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M316" t="inlineStr">
+        <is>
+          <t>Dirección: CL 70 A 43 74</t>
+        </is>
+      </c>
+      <c r="N316" t="inlineStr">
+        <is>
+          <t>ón: CL 70 A 43 74</t>
+        </is>
+      </c>
+      <c r="O316" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="E317" t="inlineStr">
+        <is>
+          <t>18/07/2026 a las 09:52</t>
+        </is>
+      </c>
+      <c r="F317" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="G317" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="H317" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I317" t="inlineStr">
+        <is>
+          <t>ía de Educación: Medellín</t>
+        </is>
+      </c>
+      <c r="J317" t="inlineStr">
+        <is>
+          <t>INST EDUC FRANCISCO ANTONIO ZEA</t>
+        </is>
+      </c>
+      <c r="K317" t="inlineStr">
+        <is>
+          <t>SEC ESC PEDRO DE CASTRO</t>
+        </is>
+      </c>
+      <c r="L317" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M317" t="inlineStr">
+        <is>
+          <t>Dirección: CLL 40 NO 86A-101</t>
+        </is>
+      </c>
+      <c r="N317" t="inlineStr">
+        <is>
+          <t>ón: CLL 40 NO 86A-101</t>
+        </is>
+      </c>
+      <c r="O317" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>Preescolar</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="E318" t="inlineStr">
+        <is>
+          <t>18/07/2026 a las 09:52</t>
+        </is>
+      </c>
+      <c r="F318" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G318" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="H318" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I318" t="inlineStr">
+        <is>
+          <t>ía de Educación: Medellín</t>
+        </is>
+      </c>
+      <c r="J318" t="inlineStr">
+        <is>
+          <t>INST EDUC FRANCISCO MIRANDA</t>
+        </is>
+      </c>
+      <c r="K318" t="inlineStr">
+        <is>
+          <t>SEC ESC JULIO ARBOLEDA</t>
+        </is>
+      </c>
+      <c r="L318" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M318" t="inlineStr">
+        <is>
+          <t>Dirección: CLL 78 NO 51-12</t>
+        </is>
+      </c>
+      <c r="N318" t="inlineStr">
+        <is>
+          <t>ón: CLL 78 NO 51-12</t>
+        </is>
+      </c>
+      <c r="O318" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="E319" t="inlineStr">
+        <is>
+          <t>18/07/2026 a las 09:52</t>
+        </is>
+      </c>
+      <c r="F319" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G319" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="H319" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I319" t="inlineStr">
+        <is>
+          <t>ía de Educación: Medellín</t>
+        </is>
+      </c>
+      <c r="J319" t="inlineStr">
+        <is>
+          <t>INST EDUC MARIA DE LOS ANGELES CANO MARQUEZ</t>
+        </is>
+      </c>
+      <c r="K319" t="inlineStr">
+        <is>
+          <t>INST EDUC MARIA DE LOS ANGELES CANO MARQUEZ - SEDE</t>
+        </is>
+      </c>
+      <c r="L319" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M319" t="inlineStr">
+        <is>
+          <t>Dirección: CL 103 33 D 75</t>
+        </is>
+      </c>
+      <c r="N319" t="inlineStr">
+        <is>
+          <t>ón: CL 103 33 D 75</t>
+        </is>
+      </c>
+      <c r="O319" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="E320" t="inlineStr">
+        <is>
+          <t>18/07/2026 a las 09:52</t>
+        </is>
+      </c>
+      <c r="F320" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G320" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="H320" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I320" t="inlineStr">
+        <is>
+          <t>ía de Educación: Medellín</t>
+        </is>
+      </c>
+      <c r="J320" t="inlineStr">
+        <is>
+          <t>INST EDUC FRANCISCO MIRANDA</t>
+        </is>
+      </c>
+      <c r="K320" t="inlineStr">
+        <is>
+          <t>SEC ESC JULIO ARBOLEDA</t>
+        </is>
+      </c>
+      <c r="L320" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M320" t="inlineStr">
+        <is>
+          <t>Dirección: CLL 78 NO 51-12</t>
+        </is>
+      </c>
+      <c r="N320" t="inlineStr">
+        <is>
+          <t>ón: CLL 78 NO 51-12</t>
+        </is>
+      </c>
+      <c r="O320" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="E321" t="inlineStr">
+        <is>
+          <t>18/07/2026 a las 09:52</t>
+        </is>
+      </c>
+      <c r="F321" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="G321" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="H321" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I321" t="inlineStr">
+        <is>
+          <t>ía de Educación: Medellín</t>
+        </is>
+      </c>
+      <c r="J321" t="inlineStr">
+        <is>
+          <t>INST EDUC ALFONSO LOPEZ PUMAREJO</t>
+        </is>
+      </c>
+      <c r="K321" t="inlineStr">
+        <is>
+          <t>SEC ESC JULIA AGUDELO</t>
+        </is>
+      </c>
+      <c r="L321" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M321" t="inlineStr">
+        <is>
+          <t>ENCISO</t>
+        </is>
+      </c>
+      <c r="N321" t="inlineStr">
+        <is>
+          <t>ón: CL 58 28 58</t>
+        </is>
+      </c>
+      <c r="O321" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>Preescolar</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="E322" t="inlineStr">
+        <is>
+          <t>18/07/2026 a las 09:52</t>
+        </is>
+      </c>
+      <c r="F322" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G322" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="H322" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I322" t="inlineStr">
+        <is>
+          <t>ía de Educación: Medellín</t>
+        </is>
+      </c>
+      <c r="J322" t="inlineStr">
+        <is>
+          <t>INST EDUC ARZOBISPO TULIO BOTERO SALAZAR</t>
+        </is>
+      </c>
+      <c r="K322" t="inlineStr">
+        <is>
+          <t>INST EDUC ARZOBISPO TULIO BOTERO SALAZAR - SEDE PR</t>
+        </is>
+      </c>
+      <c r="L322" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M322" t="inlineStr">
+        <is>
+          <t>Dirección: CL 49 A 03 A 006</t>
+        </is>
+      </c>
+      <c r="N322" t="inlineStr">
+        <is>
+          <t>ón: CL 49 A 03 A 006</t>
+        </is>
+      </c>
+      <c r="O322" t="inlineStr">
         <is>
           <t>A</t>
         </is>

--- a/nuevas_plazas.xlsx
+++ b/nuevas_plazas.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O322"/>
+  <dimension ref="A1:O323"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23781,10 +23781,8 @@
           <t>18/07/2026 a las 09:51</t>
         </is>
       </c>
-      <c r="F312" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
+      <c r="F312" t="n">
+        <v>9</v>
       </c>
       <c r="G312" t="inlineStr">
         <is>
@@ -23858,10 +23856,8 @@
           <t>18/07/2026 a las 09:52</t>
         </is>
       </c>
-      <c r="F313" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
+      <c r="F313" t="n">
+        <v>9</v>
       </c>
       <c r="G313" t="inlineStr">
         <is>
@@ -23935,10 +23931,8 @@
           <t>18/07/2026 a las 09:52</t>
         </is>
       </c>
-      <c r="F314" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
+      <c r="F314" t="n">
+        <v>9</v>
       </c>
       <c r="G314" t="inlineStr">
         <is>
@@ -24012,10 +24006,8 @@
           <t>18/07/2026 a las 09:52</t>
         </is>
       </c>
-      <c r="F315" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="F315" t="n">
+        <v>8</v>
       </c>
       <c r="G315" t="inlineStr">
         <is>
@@ -24089,10 +24081,8 @@
           <t>18/07/2026 a las 09:52</t>
         </is>
       </c>
-      <c r="F316" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
+      <c r="F316" t="n">
+        <v>7</v>
       </c>
       <c r="G316" t="inlineStr">
         <is>
@@ -24166,10 +24156,8 @@
           <t>18/07/2026 a las 09:52</t>
         </is>
       </c>
-      <c r="F317" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
+      <c r="F317" t="n">
+        <v>11</v>
       </c>
       <c r="G317" t="inlineStr">
         <is>
@@ -24243,10 +24231,8 @@
           <t>18/07/2026 a las 09:52</t>
         </is>
       </c>
-      <c r="F318" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="F318" t="n">
+        <v>8</v>
       </c>
       <c r="G318" t="inlineStr">
         <is>
@@ -24320,10 +24306,8 @@
           <t>18/07/2026 a las 09:52</t>
         </is>
       </c>
-      <c r="F319" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
+      <c r="F319" t="n">
+        <v>10</v>
       </c>
       <c r="G319" t="inlineStr">
         <is>
@@ -24397,10 +24381,8 @@
           <t>18/07/2026 a las 09:52</t>
         </is>
       </c>
-      <c r="F320" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
+      <c r="F320" t="n">
+        <v>10</v>
       </c>
       <c r="G320" t="inlineStr">
         <is>
@@ -24474,10 +24456,8 @@
           <t>18/07/2026 a las 09:52</t>
         </is>
       </c>
-      <c r="F321" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
+      <c r="F321" t="n">
+        <v>11</v>
       </c>
       <c r="G321" t="inlineStr">
         <is>
@@ -24551,10 +24531,8 @@
           <t>18/07/2026 a las 09:52</t>
         </is>
       </c>
-      <c r="F322" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
+      <c r="F322" t="n">
+        <v>10</v>
       </c>
       <c r="G322" t="inlineStr">
         <is>
@@ -24597,6 +24575,83 @@
         </is>
       </c>
       <c r="O322" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>Educación artística - artes plásticas</t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>Rionegro</t>
+        </is>
+      </c>
+      <c r="E323" t="inlineStr">
+        <is>
+          <t>18/07/2026 a las 13:17</t>
+        </is>
+      </c>
+      <c r="F323" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="G323" t="inlineStr">
+        <is>
+          <t>Rionegro</t>
+        </is>
+      </c>
+      <c r="H323" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I323" t="inlineStr">
+        <is>
+          <t>ía de Educación: Rionegro</t>
+        </is>
+      </c>
+      <c r="J323" t="inlineStr">
+        <is>
+          <t>I. E. CONCEJO MUNICIPAL EL PORVENIR</t>
+        </is>
+      </c>
+      <c r="K323" t="inlineStr">
+        <is>
+          <t>COLEGIO CONCEJO MUNICIPAL EL PORVENIR - SEDE PRINC</t>
+        </is>
+      </c>
+      <c r="L323" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M323" t="inlineStr">
+        <is>
+          <t>COMUNA OCCIDENTAL</t>
+        </is>
+      </c>
+      <c r="N323" t="inlineStr">
+        <is>
+          <t>ón: CRA 69 48B-63</t>
+        </is>
+      </c>
+      <c r="O323" t="inlineStr">
         <is>
           <t>A</t>
         </is>

--- a/nuevas_plazas.xlsx
+++ b/nuevas_plazas.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O323"/>
+  <dimension ref="A1:O336"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24606,10 +24606,8 @@
           <t>18/07/2026 a las 13:17</t>
         </is>
       </c>
-      <c r="F323" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
+      <c r="F323" t="n">
+        <v>25</v>
       </c>
       <c r="G323" t="inlineStr">
         <is>
@@ -24652,6 +24650,1007 @@
         </is>
       </c>
       <c r="O323" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>Educación artística - artes plásticas</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>San Pedro</t>
+        </is>
+      </c>
+      <c r="E324" t="inlineStr">
+        <is>
+          <t>22/07/2026 a las 10:50</t>
+        </is>
+      </c>
+      <c r="F324" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G324" t="inlineStr">
+        <is>
+          <t>San Pedro</t>
+        </is>
+      </c>
+      <c r="H324" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I324" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J324" t="inlineStr">
+        <is>
+          <t>I.E. PADRE ROBERTO ARROYAVE VELEZ</t>
+        </is>
+      </c>
+      <c r="K324" t="inlineStr">
+        <is>
+          <t>I.E. PADRE ROBERTO ARROYAVE VELEZ - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L324" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M324" t="inlineStr">
+        <is>
+          <t>BARRIO SAN JOSE</t>
+        </is>
+      </c>
+      <c r="N324" t="inlineStr">
+        <is>
+          <t>ón: CL 46 50 225</t>
+        </is>
+      </c>
+      <c r="O324" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>Ciencias naturales física</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>Angostura</t>
+        </is>
+      </c>
+      <c r="E325" t="inlineStr">
+        <is>
+          <t>22/07/2026 a las 10:50</t>
+        </is>
+      </c>
+      <c r="F325" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G325" t="inlineStr">
+        <is>
+          <t>Angostura</t>
+        </is>
+      </c>
+      <c r="H325" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I325" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J325" t="inlineStr">
+        <is>
+          <t>I. E. MARIANO DE JESUS EUSSE</t>
+        </is>
+      </c>
+      <c r="K325" t="inlineStr">
+        <is>
+          <t>LICEO MARIANO DE J EUSSE - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L325" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M325" t="inlineStr">
+        <is>
+          <t>CENTRO</t>
+        </is>
+      </c>
+      <c r="N325" t="inlineStr">
+        <is>
+          <t>ón: KR 9 8 84</t>
+        </is>
+      </c>
+      <c r="O325" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>Frontino</t>
+        </is>
+      </c>
+      <c r="E326" t="inlineStr">
+        <is>
+          <t>22/07/2026 a las 10:50</t>
+        </is>
+      </c>
+      <c r="F326" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="G326" t="inlineStr">
+        <is>
+          <t>Frontino</t>
+        </is>
+      </c>
+      <c r="H326" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I326" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J326" t="inlineStr">
+        <is>
+          <t>I. E. R. NOBOGACITA</t>
+        </is>
+      </c>
+      <c r="K326" t="inlineStr">
+        <is>
+          <t>C. E. R. VENADOS ARRIBA</t>
+        </is>
+      </c>
+      <c r="L326" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M326" t="inlineStr">
+        <is>
+          <t>VDA. VENADOS ARRIBA</t>
+        </is>
+      </c>
+      <c r="N326" t="inlineStr">
+        <is>
+          <t>ón: VDA. VENADOS ARRIBA</t>
+        </is>
+      </c>
+      <c r="O326" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>Frontino</t>
+        </is>
+      </c>
+      <c r="E327" t="inlineStr">
+        <is>
+          <t>22/07/2026 a las 10:50</t>
+        </is>
+      </c>
+      <c r="F327" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G327" t="inlineStr">
+        <is>
+          <t>Frontino</t>
+        </is>
+      </c>
+      <c r="H327" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I327" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J327" t="inlineStr">
+        <is>
+          <t>I. E. R. LA BLANQUITA DEL MURRI</t>
+        </is>
+      </c>
+      <c r="K327" t="inlineStr">
+        <is>
+          <t>C.E.R LA CERRAZON</t>
+        </is>
+      </c>
+      <c r="L327" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M327" t="inlineStr">
+        <is>
+          <t>Dirección: VEREDA LA CERRAZON</t>
+        </is>
+      </c>
+      <c r="N327" t="inlineStr">
+        <is>
+          <t>ón: VEREDA LA CERRAZON</t>
+        </is>
+      </c>
+      <c r="O327" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Priorizadas para jóvenes entre 18 y 28 años</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>Ciencias naturales y educación ambiental</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>Arboletes</t>
+        </is>
+      </c>
+      <c r="E328" t="inlineStr">
+        <is>
+          <t>22/07/2026 a las 10:50</t>
+        </is>
+      </c>
+      <c r="F328" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G328" t="inlineStr">
+        <is>
+          <t>Arboletes</t>
+        </is>
+      </c>
+      <c r="H328" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I328" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J328" t="inlineStr">
+        <is>
+          <t>I. E. MIGUEL VICENTE GARRIDO ORTIZ</t>
+        </is>
+      </c>
+      <c r="K328" t="inlineStr">
+        <is>
+          <t>I. E. MIGUEL VICENTE GARRIDO ORTIZ - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L328" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M328" t="inlineStr">
+        <is>
+          <t>B/ ACEVEDO</t>
+        </is>
+      </c>
+      <c r="N328" t="inlineStr">
+        <is>
+          <t>ón: IND AV. 12 DE OCTUBRE</t>
+        </is>
+      </c>
+      <c r="O328" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>Ciencias naturales física</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>Tarazá</t>
+        </is>
+      </c>
+      <c r="E329" t="inlineStr">
+        <is>
+          <t>22/07/2026 a las 10:50</t>
+        </is>
+      </c>
+      <c r="F329" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G329" t="inlineStr">
+        <is>
+          <t>Tarazá</t>
+        </is>
+      </c>
+      <c r="H329" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I329" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J329" t="inlineStr">
+        <is>
+          <t>I. E. RAFAEL NUNEZ</t>
+        </is>
+      </c>
+      <c r="K329" t="inlineStr">
+        <is>
+          <t>LICEO RAFAEL NUNEZ - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L329" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M329" t="inlineStr">
+        <is>
+          <t>B. VILLA DEL LAGO</t>
+        </is>
+      </c>
+      <c r="N329" t="inlineStr">
+        <is>
+          <t>ón: CL 28 28 18</t>
+        </is>
+      </c>
+      <c r="O329" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>Matemáticas</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>Urrao</t>
+        </is>
+      </c>
+      <c r="E330" t="inlineStr">
+        <is>
+          <t>22/07/2026 a las 10:50</t>
+        </is>
+      </c>
+      <c r="F330" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G330" t="inlineStr">
+        <is>
+          <t>Urrao</t>
+        </is>
+      </c>
+      <c r="H330" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I330" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J330" t="inlineStr">
+        <is>
+          <t>I. E. R. LA CALDASIA</t>
+        </is>
+      </c>
+      <c r="K330" t="inlineStr">
+        <is>
+          <t>C. E. R. ALBERTO SALAZAR FLOREZ</t>
+        </is>
+      </c>
+      <c r="L330" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M330" t="inlineStr">
+        <is>
+          <t>Dirección: VDA. LA MINA</t>
+        </is>
+      </c>
+      <c r="N330" t="inlineStr">
+        <is>
+          <t>ón: VDA. LA MINA</t>
+        </is>
+      </c>
+      <c r="O330" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>Ciencias naturales física</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>Santafe De Antioquia</t>
+        </is>
+      </c>
+      <c r="E331" t="inlineStr">
+        <is>
+          <t>22/07/2026 a las 10:50</t>
+        </is>
+      </c>
+      <c r="F331" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G331" t="inlineStr">
+        <is>
+          <t>Occidente</t>
+        </is>
+      </c>
+      <c r="H331" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I331" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J331" t="inlineStr">
+        <is>
+          <t>I. E. ARTURO VELASQUEZ ORTIZ</t>
+        </is>
+      </c>
+      <c r="K331" t="inlineStr">
+        <is>
+          <t>COLEGIO ARTURO VELASQUEZ ORTIZ - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L331" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M331" t="inlineStr">
+        <is>
+          <t>BARRIO. SANTA LUCIA</t>
+        </is>
+      </c>
+      <c r="N331" t="inlineStr">
+        <is>
+          <t>ón: CL 9 2 25</t>
+        </is>
+      </c>
+      <c r="O331" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Priorizadas para jóvenes entre 18 y 28 años</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>Preescolar</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>Vegachí</t>
+        </is>
+      </c>
+      <c r="E332" t="inlineStr">
+        <is>
+          <t>22/07/2026 a las 10:50</t>
+        </is>
+      </c>
+      <c r="F332" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="G332" t="inlineStr">
+        <is>
+          <t>Vegachí</t>
+        </is>
+      </c>
+      <c r="H332" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I332" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J332" t="inlineStr">
+        <is>
+          <t>I. E. EFE GOMEZ</t>
+        </is>
+      </c>
+      <c r="K332" t="inlineStr">
+        <is>
+          <t>E U EFE GOMEZ</t>
+        </is>
+      </c>
+      <c r="L332" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M332" t="inlineStr">
+        <is>
+          <t>Dirección: KR 46 50 38</t>
+        </is>
+      </c>
+      <c r="N332" t="inlineStr">
+        <is>
+          <t>ón: KR 46 50 38</t>
+        </is>
+      </c>
+      <c r="O332" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>Ciencias naturales física</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>Vegachí</t>
+        </is>
+      </c>
+      <c r="E333" t="inlineStr">
+        <is>
+          <t>22/07/2026 a las 10:50</t>
+        </is>
+      </c>
+      <c r="F333" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G333" t="inlineStr">
+        <is>
+          <t>Vegachí</t>
+        </is>
+      </c>
+      <c r="H333" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I333" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J333" t="inlineStr">
+        <is>
+          <t>I. E. EFE GOMEZ</t>
+        </is>
+      </c>
+      <c r="K333" t="inlineStr">
+        <is>
+          <t>LICEO EFE GOMEZ - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L333" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M333" t="inlineStr">
+        <is>
+          <t>CABECEERA MPAL</t>
+        </is>
+      </c>
+      <c r="N333" t="inlineStr">
+        <is>
+          <t>ón: KR 47 50 40</t>
+        </is>
+      </c>
+      <c r="O333" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>Educación religiosa</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>Segovia</t>
+        </is>
+      </c>
+      <c r="E334" t="inlineStr">
+        <is>
+          <t>22/07/2026 a las 10:50</t>
+        </is>
+      </c>
+      <c r="F334" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G334" t="inlineStr">
+        <is>
+          <t>Segovia</t>
+        </is>
+      </c>
+      <c r="H334" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I334" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J334" t="inlineStr">
+        <is>
+          <t>I. E. LIBORIO BATALLER</t>
+        </is>
+      </c>
+      <c r="K334" t="inlineStr">
+        <is>
+          <t>COLEGIO LIBORIO BATALLER - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L334" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M334" t="inlineStr">
+        <is>
+          <t>BARRIO GUANANA</t>
+        </is>
+      </c>
+      <c r="N334" t="inlineStr">
+        <is>
+          <t>ón: KR 55 47 65</t>
+        </is>
+      </c>
+      <c r="O334" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>Preescolar</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>Anorí</t>
+        </is>
+      </c>
+      <c r="E335" t="inlineStr">
+        <is>
+          <t>22/07/2026 a las 10:50</t>
+        </is>
+      </c>
+      <c r="F335" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G335" t="inlineStr">
+        <is>
+          <t>Anorí</t>
+        </is>
+      </c>
+      <c r="H335" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I335" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J335" t="inlineStr">
+        <is>
+          <t>I. E. ANORI</t>
+        </is>
+      </c>
+      <c r="K335" t="inlineStr">
+        <is>
+          <t>LICEO JESUS MARIA URREA - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L335" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M335" t="inlineStr">
+        <is>
+          <t>BARRIO. LOS ANGELES</t>
+        </is>
+      </c>
+      <c r="N335" t="inlineStr">
+        <is>
+          <t>ón: KR 35 26 380</t>
+        </is>
+      </c>
+      <c r="O335" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>Itaguí</t>
+        </is>
+      </c>
+      <c r="E336" t="inlineStr">
+        <is>
+          <t>22/07/2026 a las 10:57</t>
+        </is>
+      </c>
+      <c r="F336" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="G336" t="inlineStr">
+        <is>
+          <t>Itaguí</t>
+        </is>
+      </c>
+      <c r="H336" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I336" t="inlineStr">
+        <is>
+          <t>ía de Educación: Itaguí</t>
+        </is>
+      </c>
+      <c r="J336" t="inlineStr">
+        <is>
+          <t>INSTITUCION EDUCATIVA CONCEJO MUNICIPAL DE ITAGUI</t>
+        </is>
+      </c>
+      <c r="K336" t="inlineStr">
+        <is>
+          <t>INSTITUCION EDUCATIVA CONCEJO MUNICIPAL SEDE PRINC</t>
+        </is>
+      </c>
+      <c r="L336" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M336" t="inlineStr">
+        <is>
+          <t>Dirección: CRA 64 #25-01</t>
+        </is>
+      </c>
+      <c r="N336" t="inlineStr">
+        <is>
+          <t>ón: CRA 64 #25-01</t>
+        </is>
+      </c>
+      <c r="O336" t="inlineStr">
         <is>
           <t>A</t>
         </is>

--- a/nuevas_plazas.xlsx
+++ b/nuevas_plazas.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O336"/>
+  <dimension ref="A1:O338"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24681,10 +24681,8 @@
           <t>22/07/2026 a las 10:50</t>
         </is>
       </c>
-      <c r="F324" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="F324" t="n">
+        <v>5</v>
       </c>
       <c r="G324" t="inlineStr">
         <is>
@@ -24758,10 +24756,8 @@
           <t>22/07/2026 a las 10:50</t>
         </is>
       </c>
-      <c r="F325" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="F325" t="n">
+        <v>1</v>
       </c>
       <c r="G325" t="inlineStr">
         <is>
@@ -24835,10 +24831,8 @@
           <t>22/07/2026 a las 10:50</t>
         </is>
       </c>
-      <c r="F326" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
+      <c r="F326" t="n">
+        <v>11</v>
       </c>
       <c r="G326" t="inlineStr">
         <is>
@@ -24912,10 +24906,8 @@
           <t>22/07/2026 a las 10:50</t>
         </is>
       </c>
-      <c r="F327" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
+      <c r="F327" t="n">
+        <v>10</v>
       </c>
       <c r="G327" t="inlineStr">
         <is>
@@ -24989,10 +24981,8 @@
           <t>22/07/2026 a las 10:50</t>
         </is>
       </c>
-      <c r="F328" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="F328" t="n">
+        <v>6</v>
       </c>
       <c r="G328" t="inlineStr">
         <is>
@@ -25066,10 +25056,8 @@
           <t>22/07/2026 a las 10:50</t>
         </is>
       </c>
-      <c r="F329" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F329" t="n">
+        <v>0</v>
       </c>
       <c r="G329" t="inlineStr">
         <is>
@@ -25143,10 +25131,8 @@
           <t>22/07/2026 a las 10:50</t>
         </is>
       </c>
-      <c r="F330" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="F330" t="n">
+        <v>5</v>
       </c>
       <c r="G330" t="inlineStr">
         <is>
@@ -25220,10 +25206,8 @@
           <t>22/07/2026 a las 10:50</t>
         </is>
       </c>
-      <c r="F331" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="F331" t="n">
+        <v>1</v>
       </c>
       <c r="G331" t="inlineStr">
         <is>
@@ -25297,10 +25281,8 @@
           <t>22/07/2026 a las 10:50</t>
         </is>
       </c>
-      <c r="F332" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
+      <c r="F332" t="n">
+        <v>11</v>
       </c>
       <c r="G332" t="inlineStr">
         <is>
@@ -25374,10 +25356,8 @@
           <t>22/07/2026 a las 10:50</t>
         </is>
       </c>
-      <c r="F333" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F333" t="n">
+        <v>0</v>
       </c>
       <c r="G333" t="inlineStr">
         <is>
@@ -25451,10 +25431,8 @@
           <t>22/07/2026 a las 10:50</t>
         </is>
       </c>
-      <c r="F334" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="F334" t="n">
+        <v>6</v>
       </c>
       <c r="G334" t="inlineStr">
         <is>
@@ -25528,10 +25506,8 @@
           <t>22/07/2026 a las 10:50</t>
         </is>
       </c>
-      <c r="F335" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
+      <c r="F335" t="n">
+        <v>10</v>
       </c>
       <c r="G335" t="inlineStr">
         <is>
@@ -25605,10 +25581,8 @@
           <t>22/07/2026 a las 10:57</t>
         </is>
       </c>
-      <c r="F336" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
+      <c r="F336" t="n">
+        <v>21</v>
       </c>
       <c r="G336" t="inlineStr">
         <is>
@@ -25651,6 +25625,160 @@
         </is>
       </c>
       <c r="O336" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>Matemáticas</t>
+        </is>
+      </c>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>Turbo</t>
+        </is>
+      </c>
+      <c r="E337" t="inlineStr">
+        <is>
+          <t>22/07/2026 a las 13:07</t>
+        </is>
+      </c>
+      <c r="F337" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G337" t="inlineStr">
+        <is>
+          <t>Turbo</t>
+        </is>
+      </c>
+      <c r="H337" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I337" t="inlineStr">
+        <is>
+          <t>ía de Educación: Turbo</t>
+        </is>
+      </c>
+      <c r="J337" t="inlineStr">
+        <is>
+          <t>I.E. San Vicente del Congo</t>
+        </is>
+      </c>
+      <c r="K337" t="inlineStr">
+        <is>
+          <t>Sede El Congo</t>
+        </is>
+      </c>
+      <c r="L337" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M337" t="inlineStr">
+        <is>
+          <t>Dirección: VDA. EL CONGO.</t>
+        </is>
+      </c>
+      <c r="N337" t="inlineStr">
+        <is>
+          <t>ón: VDA. EL CONGO.</t>
+        </is>
+      </c>
+      <c r="O337" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>Preescolar</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>Turbo</t>
+        </is>
+      </c>
+      <c r="E338" t="inlineStr">
+        <is>
+          <t>22/07/2026 a las 13:07</t>
+        </is>
+      </c>
+      <c r="F338" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="G338" t="inlineStr">
+        <is>
+          <t>Turbo</t>
+        </is>
+      </c>
+      <c r="H338" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I338" t="inlineStr">
+        <is>
+          <t>ía de Educación: Turbo</t>
+        </is>
+      </c>
+      <c r="J338" t="inlineStr">
+        <is>
+          <t>I.E. Pueblo Bello</t>
+        </is>
+      </c>
+      <c r="K338" t="inlineStr">
+        <is>
+          <t>I.E. Pueblo Bello - Sede Principal</t>
+        </is>
+      </c>
+      <c r="L338" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M338" t="inlineStr">
+        <is>
+          <t>Dirección: CORREG. PUEBLO BELLO</t>
+        </is>
+      </c>
+      <c r="N338" t="inlineStr">
+        <is>
+          <t>ón: CORREG. PUEBLO BELLO</t>
+        </is>
+      </c>
+      <c r="O338" t="inlineStr">
         <is>
           <t>A</t>
         </is>

--- a/nuevas_plazas.xlsx
+++ b/nuevas_plazas.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O338"/>
+  <dimension ref="A1:O339"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25656,10 +25656,8 @@
           <t>22/07/2026 a las 13:07</t>
         </is>
       </c>
-      <c r="F337" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="F337" t="n">
+        <v>5</v>
       </c>
       <c r="G337" t="inlineStr">
         <is>
@@ -25733,10 +25731,8 @@
           <t>22/07/2026 a las 13:07</t>
         </is>
       </c>
-      <c r="F338" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
+      <c r="F338" t="n">
+        <v>12</v>
       </c>
       <c r="G338" t="inlineStr">
         <is>
@@ -25779,6 +25775,83 @@
         </is>
       </c>
       <c r="O338" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>Humanidades y lengua castellana</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>Itaguí</t>
+        </is>
+      </c>
+      <c r="E339" t="inlineStr">
+        <is>
+          <t>24/07/2026 a las 09:03</t>
+        </is>
+      </c>
+      <c r="F339" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="G339" t="inlineStr">
+        <is>
+          <t>Itaguí</t>
+        </is>
+      </c>
+      <c r="H339" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I339" t="inlineStr">
+        <is>
+          <t>ía de Educación: Itaguí</t>
+        </is>
+      </c>
+      <c r="J339" t="inlineStr">
+        <is>
+          <t>I.E. MARIA JOSEFA ESCOBAR</t>
+        </is>
+      </c>
+      <c r="K339" t="inlineStr">
+        <is>
+          <t>I.E. MARIA JOSEFA ESCOBAR SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L339" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M339" t="inlineStr">
+        <is>
+          <t>Dirección: VDA. EL PEDREGAL</t>
+        </is>
+      </c>
+      <c r="N339" t="inlineStr">
+        <is>
+          <t>ón: VDA. EL PEDREGAL</t>
+        </is>
+      </c>
+      <c r="O339" t="inlineStr">
         <is>
           <t>A</t>
         </is>

--- a/nuevas_plazas.xlsx
+++ b/nuevas_plazas.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O339"/>
+  <dimension ref="A1:O340"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25806,10 +25806,8 @@
           <t>24/07/2026 a las 09:03</t>
         </is>
       </c>
-      <c r="F339" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
+      <c r="F339" t="n">
+        <v>20</v>
       </c>
       <c r="G339" t="inlineStr">
         <is>
@@ -25852,6 +25850,83 @@
         </is>
       </c>
       <c r="O339" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>Ciencias naturales y educación ambiental</t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>Itaguí</t>
+        </is>
+      </c>
+      <c r="E340" t="inlineStr">
+        <is>
+          <t>24/07/2026 a las 09:03</t>
+        </is>
+      </c>
+      <c r="F340" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="G340" t="inlineStr">
+        <is>
+          <t>Itaguí</t>
+        </is>
+      </c>
+      <c r="H340" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I340" t="inlineStr">
+        <is>
+          <t>ía de Educación: Itaguí</t>
+        </is>
+      </c>
+      <c r="J340" t="inlineStr">
+        <is>
+          <t>I.E. MARIA JOSEFA ESCOBAR</t>
+        </is>
+      </c>
+      <c r="K340" t="inlineStr">
+        <is>
+          <t>I. E. MARIA JOSEFA ESCOBAR SEDE JUAN ECHEVERRY ABA</t>
+        </is>
+      </c>
+      <c r="L340" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M340" t="inlineStr">
+        <is>
+          <t>Dirección: CRA 54 #26-02</t>
+        </is>
+      </c>
+      <c r="N340" t="inlineStr">
+        <is>
+          <t>ón: CRA 54 #26-02</t>
+        </is>
+      </c>
+      <c r="O340" t="inlineStr">
         <is>
           <t>A</t>
         </is>

--- a/nuevas_plazas.xlsx
+++ b/nuevas_plazas.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O340"/>
+  <dimension ref="A1:O350"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25881,10 +25881,8 @@
           <t>24/07/2026 a las 09:03</t>
         </is>
       </c>
-      <c r="F340" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
+      <c r="F340" t="n">
+        <v>41</v>
       </c>
       <c r="G340" t="inlineStr">
         <is>
@@ -25927,6 +25925,776 @@
         </is>
       </c>
       <c r="O340" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>Turbo</t>
+        </is>
+      </c>
+      <c r="E341" t="inlineStr">
+        <is>
+          <t>30/07/2026 a las 15:38</t>
+        </is>
+      </c>
+      <c r="F341" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G341" t="inlineStr">
+        <is>
+          <t>Turbo</t>
+        </is>
+      </c>
+      <c r="H341" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I341" t="inlineStr">
+        <is>
+          <t>ía de Educación: Turbo</t>
+        </is>
+      </c>
+      <c r="J341" t="inlineStr">
+        <is>
+          <t>C.E. Kilometro Veinticinco</t>
+        </is>
+      </c>
+      <c r="K341" t="inlineStr">
+        <is>
+          <t>Sede La Primavera</t>
+        </is>
+      </c>
+      <c r="L341" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M341" t="inlineStr">
+        <is>
+          <t>Dirección: VDA. LA PRIMAVERA</t>
+        </is>
+      </c>
+      <c r="N341" t="inlineStr">
+        <is>
+          <t>ón: VDA. LA PRIMAVERA</t>
+        </is>
+      </c>
+      <c r="O341" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>Educación física, recreación y deporte</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="E342" t="inlineStr">
+        <is>
+          <t>30/07/2026 a las 15:39</t>
+        </is>
+      </c>
+      <c r="F342" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G342" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="H342" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I342" t="inlineStr">
+        <is>
+          <t>ía de Educación: Medellín</t>
+        </is>
+      </c>
+      <c r="J342" t="inlineStr">
+        <is>
+          <t>INST EDUC LOLA GONZALEZ</t>
+        </is>
+      </c>
+      <c r="K342" t="inlineStr">
+        <is>
+          <t>INST EDUC LOLA GONZALEZ - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L342" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M342" t="inlineStr">
+        <is>
+          <t>Dirección: CL 47 F 94 63</t>
+        </is>
+      </c>
+      <c r="N342" t="inlineStr">
+        <is>
+          <t>ón: CL 47 F 94 63</t>
+        </is>
+      </c>
+      <c r="O342" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Priorizadas para jóvenes entre 18 y 28 años</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>Educación física, recreación y deporte</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="E343" t="inlineStr">
+        <is>
+          <t>30/07/2026 a las 15:39</t>
+        </is>
+      </c>
+      <c r="F343" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G343" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="H343" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I343" t="inlineStr">
+        <is>
+          <t>ía de Educación: Medellín</t>
+        </is>
+      </c>
+      <c r="J343" t="inlineStr">
+        <is>
+          <t>INST EDUC ROSALIA SUAREZ</t>
+        </is>
+      </c>
+      <c r="K343" t="inlineStr">
+        <is>
+          <t>INST EDUC ROSALIA SUAREZ - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L343" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M343" t="inlineStr">
+        <is>
+          <t>Dirección: CR 77 NO 30A-53</t>
+        </is>
+      </c>
+      <c r="N343" t="inlineStr">
+        <is>
+          <t>ón: CR 77 NO 30A-53</t>
+        </is>
+      </c>
+      <c r="O343" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>Educación física, recreación y deporte</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="E344" t="inlineStr">
+        <is>
+          <t>30/07/2026 a las 15:39</t>
+        </is>
+      </c>
+      <c r="F344" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G344" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="H344" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I344" t="inlineStr">
+        <is>
+          <t>ía de Educación: Medellín</t>
+        </is>
+      </c>
+      <c r="J344" t="inlineStr">
+        <is>
+          <t>INST EDUC SAN ANTONIO DE PRADO</t>
+        </is>
+      </c>
+      <c r="K344" t="inlineStr">
+        <is>
+          <t>SEC ESC MANUEL MARIA MALLARINO</t>
+        </is>
+      </c>
+      <c r="L344" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M344" t="inlineStr">
+        <is>
+          <t>Dirección: CL 40 SUR 75 B 101</t>
+        </is>
+      </c>
+      <c r="N344" t="inlineStr">
+        <is>
+          <t>ón: CL 40 SUR 75 B 101</t>
+        </is>
+      </c>
+      <c r="O344" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>Matemáticas</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="E345" t="inlineStr">
+        <is>
+          <t>30/07/2026 a las 15:39</t>
+        </is>
+      </c>
+      <c r="F345" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G345" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="H345" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I345" t="inlineStr">
+        <is>
+          <t>ía de Educación: Medellín</t>
+        </is>
+      </c>
+      <c r="J345" t="inlineStr">
+        <is>
+          <t>INST EDUC JAVIERA LONDO</t>
+        </is>
+      </c>
+      <c r="K345" t="inlineStr">
+        <is>
+          <t>INST EDUC JAVIERA LONDO - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L345" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M345" t="inlineStr">
+        <is>
+          <t>Dirección: CLL 53 NO 40-65</t>
+        </is>
+      </c>
+      <c r="N345" t="inlineStr">
+        <is>
+          <t>ón: CLL 53 NO 40-65</t>
+        </is>
+      </c>
+      <c r="O345" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>Matemáticas</t>
+        </is>
+      </c>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="E346" t="inlineStr">
+        <is>
+          <t>30/07/2026 a las 15:39</t>
+        </is>
+      </c>
+      <c r="F346" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G346" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="H346" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I346" t="inlineStr">
+        <is>
+          <t>ía de Educación: Medellín</t>
+        </is>
+      </c>
+      <c r="J346" t="inlineStr">
+        <is>
+          <t>INST EDUC FE Y ALEGRIA EL LIMONAR</t>
+        </is>
+      </c>
+      <c r="K346" t="inlineStr">
+        <is>
+          <t>INST EDUC FE Y ALEGRIA EL LIMONAR - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L346" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M346" t="inlineStr">
+        <is>
+          <t>Dirección: CL 55 SUR 60 A 13</t>
+        </is>
+      </c>
+      <c r="N346" t="inlineStr">
+        <is>
+          <t>ón: CL 55 SUR 60 A 13</t>
+        </is>
+      </c>
+      <c r="O346" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>Ciencias naturales física</t>
+        </is>
+      </c>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="E347" t="inlineStr">
+        <is>
+          <t>30/07/2026 a las 15:39</t>
+        </is>
+      </c>
+      <c r="F347" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G347" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="H347" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I347" t="inlineStr">
+        <is>
+          <t>ía de Educación: Medellín</t>
+        </is>
+      </c>
+      <c r="J347" t="inlineStr">
+        <is>
+          <t>INST EDUC VILLA DEL SOCORRO</t>
+        </is>
+      </c>
+      <c r="K347" t="inlineStr">
+        <is>
+          <t>INST EDUC VILLA DEL SOCORRO - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L347" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M347" t="inlineStr">
+        <is>
+          <t>Dirección: CL 104 C 48 50</t>
+        </is>
+      </c>
+      <c r="N347" t="inlineStr">
+        <is>
+          <t>ón: CL 104 C 48 50</t>
+        </is>
+      </c>
+      <c r="O347" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>Idioma extranjero inglés</t>
+        </is>
+      </c>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="E348" t="inlineStr">
+        <is>
+          <t>30/07/2026 a las 15:39</t>
+        </is>
+      </c>
+      <c r="F348" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G348" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="H348" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I348" t="inlineStr">
+        <is>
+          <t>ía de Educación: Medellín</t>
+        </is>
+      </c>
+      <c r="J348" t="inlineStr">
+        <is>
+          <t>INST EDUC LA INDEPENDENCIA</t>
+        </is>
+      </c>
+      <c r="K348" t="inlineStr">
+        <is>
+          <t>INST EDUC LA INDEPENDENCIA - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L348" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M348" t="inlineStr">
+        <is>
+          <t>Dirección: CLL 39D NO 112-81</t>
+        </is>
+      </c>
+      <c r="N348" t="inlineStr">
+        <is>
+          <t>ón: CLL 39D NO 112-81</t>
+        </is>
+      </c>
+      <c r="O348" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>Educación artística - artes plásticas</t>
+        </is>
+      </c>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="E349" t="inlineStr">
+        <is>
+          <t>30/07/2026 a las 15:39</t>
+        </is>
+      </c>
+      <c r="F349" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G349" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="H349" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I349" t="inlineStr">
+        <is>
+          <t>ía de Educación: Medellín</t>
+        </is>
+      </c>
+      <c r="J349" t="inlineStr">
+        <is>
+          <t>INST EDUC JUAN XXIII</t>
+        </is>
+      </c>
+      <c r="K349" t="inlineStr">
+        <is>
+          <t>INST EDUC JUAN XXIII - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L349" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M349" t="inlineStr">
+        <is>
+          <t>LA PRADERA</t>
+        </is>
+      </c>
+      <c r="N349" t="inlineStr">
+        <is>
+          <t>ón: CL 49 96 A 11</t>
+        </is>
+      </c>
+      <c r="O349" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>Ciencias naturales química</t>
+        </is>
+      </c>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>Rionegro</t>
+        </is>
+      </c>
+      <c r="E350" t="inlineStr">
+        <is>
+          <t>30/07/2026 a las 15:48</t>
+        </is>
+      </c>
+      <c r="F350" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G350" t="inlineStr">
+        <is>
+          <t>Rionegro</t>
+        </is>
+      </c>
+      <c r="H350" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I350" t="inlineStr">
+        <is>
+          <t>ía de Educación: Rionegro</t>
+        </is>
+      </c>
+      <c r="J350" t="inlineStr">
+        <is>
+          <t>I. E. CONCEJO MUNICIPAL EL PORVENIR</t>
+        </is>
+      </c>
+      <c r="K350" t="inlineStr">
+        <is>
+          <t>COLEGIO CONCEJO MUNICIPAL EL PORVENIR - SEDE PRINC</t>
+        </is>
+      </c>
+      <c r="L350" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M350" t="inlineStr">
+        <is>
+          <t>COMUNA OCCIDENTAL</t>
+        </is>
+      </c>
+      <c r="N350" t="inlineStr">
+        <is>
+          <t>ón: CRA 69 48B-63</t>
+        </is>
+      </c>
+      <c r="O350" t="inlineStr">
         <is>
           <t>A</t>
         </is>

--- a/nuevas_plazas.xlsx
+++ b/nuevas_plazas.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O350"/>
+  <dimension ref="A1:O379"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25956,10 +25956,8 @@
           <t>30/07/2026 a las 15:38</t>
         </is>
       </c>
-      <c r="F341" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="F341" t="n">
+        <v>8</v>
       </c>
       <c r="G341" t="inlineStr">
         <is>
@@ -26033,10 +26031,8 @@
           <t>30/07/2026 a las 15:39</t>
         </is>
       </c>
-      <c r="F342" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="F342" t="n">
+        <v>1</v>
       </c>
       <c r="G342" t="inlineStr">
         <is>
@@ -26110,10 +26106,8 @@
           <t>30/07/2026 a las 15:39</t>
         </is>
       </c>
-      <c r="F343" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="F343" t="n">
+        <v>1</v>
       </c>
       <c r="G343" t="inlineStr">
         <is>
@@ -26187,10 +26181,8 @@
           <t>30/07/2026 a las 15:39</t>
         </is>
       </c>
-      <c r="F344" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="F344" t="n">
+        <v>1</v>
       </c>
       <c r="G344" t="inlineStr">
         <is>
@@ -26264,10 +26256,8 @@
           <t>30/07/2026 a las 15:39</t>
         </is>
       </c>
-      <c r="F345" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="F345" t="n">
+        <v>2</v>
       </c>
       <c r="G345" t="inlineStr">
         <is>
@@ -26341,10 +26331,8 @@
           <t>30/07/2026 a las 15:39</t>
         </is>
       </c>
-      <c r="F346" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="F346" t="n">
+        <v>1</v>
       </c>
       <c r="G346" t="inlineStr">
         <is>
@@ -26418,10 +26406,8 @@
           <t>30/07/2026 a las 15:39</t>
         </is>
       </c>
-      <c r="F347" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F347" t="n">
+        <v>0</v>
       </c>
       <c r="G347" t="inlineStr">
         <is>
@@ -26495,10 +26481,8 @@
           <t>30/07/2026 a las 15:39</t>
         </is>
       </c>
-      <c r="F348" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="F348" t="n">
+        <v>1</v>
       </c>
       <c r="G348" t="inlineStr">
         <is>
@@ -26572,10 +26556,8 @@
           <t>30/07/2026 a las 15:39</t>
         </is>
       </c>
-      <c r="F349" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="F349" t="n">
+        <v>1</v>
       </c>
       <c r="G349" t="inlineStr">
         <is>
@@ -26649,52 +26631,2283 @@
           <t>30/07/2026 a las 15:48</t>
         </is>
       </c>
-      <c r="F350" t="inlineStr">
+      <c r="F350" t="n">
+        <v>0</v>
+      </c>
+      <c r="G350" t="inlineStr">
+        <is>
+          <t>Rionegro</t>
+        </is>
+      </c>
+      <c r="H350" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I350" t="inlineStr">
+        <is>
+          <t>ía de Educación: Rionegro</t>
+        </is>
+      </c>
+      <c r="J350" t="inlineStr">
+        <is>
+          <t>I. E. CONCEJO MUNICIPAL EL PORVENIR</t>
+        </is>
+      </c>
+      <c r="K350" t="inlineStr">
+        <is>
+          <t>COLEGIO CONCEJO MUNICIPAL EL PORVENIR - SEDE PRINC</t>
+        </is>
+      </c>
+      <c r="L350" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M350" t="inlineStr">
+        <is>
+          <t>COMUNA OCCIDENTAL</t>
+        </is>
+      </c>
+      <c r="N350" t="inlineStr">
+        <is>
+          <t>ón: CRA 69 48B-63</t>
+        </is>
+      </c>
+      <c r="O350" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>Preescolar</t>
+        </is>
+      </c>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="E351" t="inlineStr">
+        <is>
+          <t>31/07/2026 a las 15:27</t>
+        </is>
+      </c>
+      <c r="F351" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="G351" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="H351" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I351" t="inlineStr">
+        <is>
+          <t>ía de Educación: Medellín</t>
+        </is>
+      </c>
+      <c r="J351" t="inlineStr">
+        <is>
+          <t>INST EDUC GABRIEL GARCIA MARQUEZ</t>
+        </is>
+      </c>
+      <c r="K351" t="inlineStr">
+        <is>
+          <t>INST EDUC GABRIEL GARCIA MARQUEZ - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L351" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M351" t="inlineStr">
+        <is>
+          <t>Dirección: KR 8 A 57 A 93</t>
+        </is>
+      </c>
+      <c r="N351" t="inlineStr">
+        <is>
+          <t>ón: KR 8 A 57 A 93</t>
+        </is>
+      </c>
+      <c r="O351" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>Tecnología e informática</t>
+        </is>
+      </c>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="E352" t="inlineStr">
+        <is>
+          <t>31/07/2026 a las 15:27</t>
+        </is>
+      </c>
+      <c r="F352" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="G352" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="H352" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I352" t="inlineStr">
+        <is>
+          <t>ía de Educación: Medellín</t>
+        </is>
+      </c>
+      <c r="J352" t="inlineStr">
+        <is>
+          <t>INST EDUC EL PLAYON</t>
+        </is>
+      </c>
+      <c r="K352" t="inlineStr">
+        <is>
+          <t>INST EDUC EL PLAYON - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L352" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M352" t="inlineStr">
+        <is>
+          <t>Dirección: CL 125 51 D 12</t>
+        </is>
+      </c>
+      <c r="N352" t="inlineStr">
+        <is>
+          <t>ón: CL 125 51 D 12</t>
+        </is>
+      </c>
+      <c r="O352" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="D353" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="E353" t="inlineStr">
+        <is>
+          <t>31/07/2026 a las 15:27</t>
+        </is>
+      </c>
+      <c r="F353" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="G353" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="H353" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I353" t="inlineStr">
+        <is>
+          <t>ía de Educación: Medellín</t>
+        </is>
+      </c>
+      <c r="J353" t="inlineStr">
+        <is>
+          <t>INST EDUC LUSITANIA-PAZ DE COLOMBIA</t>
+        </is>
+      </c>
+      <c r="K353" t="inlineStr">
+        <is>
+          <t>INST EDUC LUSITANIA-PAZ DE COLOMBIA - SEDE PRINCIP</t>
+        </is>
+      </c>
+      <c r="L353" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M353" t="inlineStr">
+        <is>
+          <t>Dirección: KR 109 A 63 B 320</t>
+        </is>
+      </c>
+      <c r="N353" t="inlineStr">
+        <is>
+          <t>ón: KR 109 A 63 B 320</t>
+        </is>
+      </c>
+      <c r="O353" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Priorizadas para jóvenes entre 18 y 28 años</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>Turbo</t>
+        </is>
+      </c>
+      <c r="E354" t="inlineStr">
+        <is>
+          <t>31/07/2026 a las 15:31</t>
+        </is>
+      </c>
+      <c r="F354" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G354" t="inlineStr">
+        <is>
+          <t>Turbo</t>
+        </is>
+      </c>
+      <c r="H354" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I354" t="inlineStr">
+        <is>
+          <t>ía de Educación: Turbo</t>
+        </is>
+      </c>
+      <c r="J354" t="inlineStr">
+        <is>
+          <t>I.E. Pueblo Bello</t>
+        </is>
+      </c>
+      <c r="K354" t="inlineStr">
+        <is>
+          <t>Sede Santa Barbara Arriba</t>
+        </is>
+      </c>
+      <c r="L354" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M354" t="inlineStr">
+        <is>
+          <t>Dirección: VDA. SANTA BARBARA</t>
+        </is>
+      </c>
+      <c r="N354" t="inlineStr">
+        <is>
+          <t>ón: VDA. SANTA BARBARA</t>
+        </is>
+      </c>
+      <c r="O354" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>Ciencias naturales física</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>Cocorná</t>
+        </is>
+      </c>
+      <c r="E355" t="inlineStr">
+        <is>
+          <t>31/07/2026 a las 15:54</t>
+        </is>
+      </c>
+      <c r="F355" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G350" t="inlineStr">
-        <is>
-          <t>Rionegro</t>
-        </is>
-      </c>
-      <c r="H350" t="inlineStr">
-        <is>
-          <t>Antioquia</t>
-        </is>
-      </c>
-      <c r="I350" t="inlineStr">
-        <is>
-          <t>ía de Educación: Rionegro</t>
-        </is>
-      </c>
-      <c r="J350" t="inlineStr">
-        <is>
-          <t>I. E. CONCEJO MUNICIPAL EL PORVENIR</t>
-        </is>
-      </c>
-      <c r="K350" t="inlineStr">
-        <is>
-          <t>COLEGIO CONCEJO MUNICIPAL EL PORVENIR - SEDE PRINC</t>
-        </is>
-      </c>
-      <c r="L350" t="inlineStr">
+      <c r="G355" t="inlineStr">
+        <is>
+          <t>Cocorná</t>
+        </is>
+      </c>
+      <c r="H355" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I355" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J355" t="inlineStr">
+        <is>
+          <t>I. E. COCORNA</t>
+        </is>
+      </c>
+      <c r="K355" t="inlineStr">
+        <is>
+          <t>LICEO COCORNA - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L355" t="inlineStr">
         <is>
           <t>URBANA</t>
         </is>
       </c>
-      <c r="M350" t="inlineStr">
-        <is>
-          <t>COMUNA OCCIDENTAL</t>
-        </is>
-      </c>
-      <c r="N350" t="inlineStr">
-        <is>
-          <t>ón: CRA 69 48B-63</t>
-        </is>
-      </c>
-      <c r="O350" t="inlineStr">
+      <c r="M355" t="inlineStr">
+        <is>
+          <t>B. COCORNÁ</t>
+        </is>
+      </c>
+      <c r="N355" t="inlineStr">
+        <is>
+          <t>ón: CL 23 23 27</t>
+        </is>
+      </c>
+      <c r="O355" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>Sonsón</t>
+        </is>
+      </c>
+      <c r="E356" t="inlineStr">
+        <is>
+          <t>31/07/2026 a las 15:54</t>
+        </is>
+      </c>
+      <c r="F356" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G356" t="inlineStr">
+        <is>
+          <t>Sonsón</t>
+        </is>
+      </c>
+      <c r="H356" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I356" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J356" t="inlineStr">
+        <is>
+          <t>I. E. R. LA DANTA</t>
+        </is>
+      </c>
+      <c r="K356" t="inlineStr">
+        <is>
+          <t>C. E. R. LA PAZ SAN FRANCISCO</t>
+        </is>
+      </c>
+      <c r="L356" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M356" t="inlineStr">
+        <is>
+          <t>Dirección: VDA LA PAZ</t>
+        </is>
+      </c>
+      <c r="N356" t="inlineStr">
+        <is>
+          <t>ón: VDA LA PAZ</t>
+        </is>
+      </c>
+      <c r="O356" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>Idioma extranjero inglés</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>Sonsón</t>
+        </is>
+      </c>
+      <c r="E357" t="inlineStr">
+        <is>
+          <t>31/07/2026 a las 15:54</t>
+        </is>
+      </c>
+      <c r="F357" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G357" t="inlineStr">
+        <is>
+          <t>Sonsón</t>
+        </is>
+      </c>
+      <c r="H357" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I357" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J357" t="inlineStr">
+        <is>
+          <t>I. E. R. LA DANTA</t>
+        </is>
+      </c>
+      <c r="K357" t="inlineStr">
+        <is>
+          <t>I. E. R. LA DANTA - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L357" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M357" t="inlineStr">
+        <is>
+          <t>Dirección: CORRG. LA DANTA</t>
+        </is>
+      </c>
+      <c r="N357" t="inlineStr">
+        <is>
+          <t>ón: CORRG. LA DANTA</t>
+        </is>
+      </c>
+      <c r="O357" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>Educación artística - artes plásticas</t>
+        </is>
+      </c>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>Argelia</t>
+        </is>
+      </c>
+      <c r="E358" t="inlineStr">
+        <is>
+          <t>31/07/2026 a las 15:54</t>
+        </is>
+      </c>
+      <c r="F358" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G358" t="inlineStr">
+        <is>
+          <t>Argelia</t>
+        </is>
+      </c>
+      <c r="H358" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I358" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J358" t="inlineStr">
+        <is>
+          <t>I. E. SANTA TERESA</t>
+        </is>
+      </c>
+      <c r="K358" t="inlineStr">
+        <is>
+          <t>I. E. SANTA TERESA - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L358" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M358" t="inlineStr">
+        <is>
+          <t>CALLE DEL CEMENTERIO</t>
+        </is>
+      </c>
+      <c r="N358" t="inlineStr">
+        <is>
+          <t>ón: CL 31 26 78</t>
+        </is>
+      </c>
+      <c r="O358" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>Filosofía</t>
+        </is>
+      </c>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t>El Bagre</t>
+        </is>
+      </c>
+      <c r="E359" t="inlineStr">
+        <is>
+          <t>31/07/2026 a las 15:54</t>
+        </is>
+      </c>
+      <c r="F359" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G359" t="inlineStr">
+        <is>
+          <t>El Bagre</t>
+        </is>
+      </c>
+      <c r="H359" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I359" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J359" t="inlineStr">
+        <is>
+          <t>I. E. BIJAO</t>
+        </is>
+      </c>
+      <c r="K359" t="inlineStr">
+        <is>
+          <t>I. E. BIJAO - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L359" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M359" t="inlineStr">
+        <is>
+          <t>BARRIO BIJAO</t>
+        </is>
+      </c>
+      <c r="N359" t="inlineStr">
+        <is>
+          <t>ón: CL 54 48 33</t>
+        </is>
+      </c>
+      <c r="O359" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t>Yondó</t>
+        </is>
+      </c>
+      <c r="E360" t="inlineStr">
+        <is>
+          <t>31/07/2026 a las 15:55</t>
+        </is>
+      </c>
+      <c r="F360" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G360" t="inlineStr">
+        <is>
+          <t>Yondó</t>
+        </is>
+      </c>
+      <c r="H360" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I360" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J360" t="inlineStr">
+        <is>
+          <t>I. E. R. SAN MIGUEL DEL TIGRE</t>
+        </is>
+      </c>
+      <c r="K360" t="inlineStr">
+        <is>
+          <t>I. E. R. SAN MIGUEL DEL TIGRE - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L360" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M360" t="inlineStr">
+        <is>
+          <t>CORREG.SAN MIGUEL DEL TIGRE</t>
+        </is>
+      </c>
+      <c r="N360" t="inlineStr">
+        <is>
+          <t>ón: CORREG.SAN MIGUEL DEL TIGRE</t>
+        </is>
+      </c>
+      <c r="O360" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="D361" t="inlineStr">
+        <is>
+          <t>Carepa</t>
+        </is>
+      </c>
+      <c r="E361" t="inlineStr">
+        <is>
+          <t>31/07/2026 a las 15:55</t>
+        </is>
+      </c>
+      <c r="F361" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G361" t="inlineStr">
+        <is>
+          <t>Carepa</t>
+        </is>
+      </c>
+      <c r="H361" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I361" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J361" t="inlineStr">
+        <is>
+          <t>C. E. R. 25 DE AGOSTO</t>
+        </is>
+      </c>
+      <c r="K361" t="inlineStr">
+        <is>
+          <t>C. E. R. 25 DE AGOSTO - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L361" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M361" t="inlineStr">
+        <is>
+          <t>VDA.25 DE AGOSTO</t>
+        </is>
+      </c>
+      <c r="N361" t="inlineStr">
+        <is>
+          <t>ón: VDA.25 DE AGOSTO</t>
+        </is>
+      </c>
+      <c r="O361" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>Educación física, recreación y deporte</t>
+        </is>
+      </c>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>Briceño</t>
+        </is>
+      </c>
+      <c r="E362" t="inlineStr">
+        <is>
+          <t>31/07/2026 a las 15:55</t>
+        </is>
+      </c>
+      <c r="F362" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G362" t="inlineStr">
+        <is>
+          <t>Briceño</t>
+        </is>
+      </c>
+      <c r="H362" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I362" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J362" t="inlineStr">
+        <is>
+          <t>I. E. ANTONIO ROLDAN BETANCUR</t>
+        </is>
+      </c>
+      <c r="K362" t="inlineStr">
+        <is>
+          <t>I. E. R. EL ROBLAL</t>
+        </is>
+      </c>
+      <c r="L362" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M362" t="inlineStr">
+        <is>
+          <t>VDA. EL ROBLAL</t>
+        </is>
+      </c>
+      <c r="N362" t="inlineStr">
+        <is>
+          <t>ón: VDA. EL ROBLAL</t>
+        </is>
+      </c>
+      <c r="O362" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>Ciencias sociales</t>
+        </is>
+      </c>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t>Remedios</t>
+        </is>
+      </c>
+      <c r="E363" t="inlineStr">
+        <is>
+          <t>31/07/2026 a las 15:55</t>
+        </is>
+      </c>
+      <c r="F363" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G363" t="inlineStr">
+        <is>
+          <t>Remedios</t>
+        </is>
+      </c>
+      <c r="H363" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I363" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J363" t="inlineStr">
+        <is>
+          <t>I. E. R. LA CRUZADA</t>
+        </is>
+      </c>
+      <c r="K363" t="inlineStr">
+        <is>
+          <t>C. E. R. CARRIZAL</t>
+        </is>
+      </c>
+      <c r="L363" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M363" t="inlineStr">
+        <is>
+          <t>VDA. CARRIZAL</t>
+        </is>
+      </c>
+      <c r="N363" t="inlineStr">
+        <is>
+          <t>ón: VDA CARRIZAL</t>
+        </is>
+      </c>
+      <c r="O363" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="D364" t="inlineStr">
+        <is>
+          <t>Toledo</t>
+        </is>
+      </c>
+      <c r="E364" t="inlineStr">
+        <is>
+          <t>31/07/2026 a las 15:55</t>
+        </is>
+      </c>
+      <c r="F364" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G364" t="inlineStr">
+        <is>
+          <t>Toledo</t>
+        </is>
+      </c>
+      <c r="H364" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I364" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J364" t="inlineStr">
+        <is>
+          <t>C. E. R. LA LINDA</t>
+        </is>
+      </c>
+      <c r="K364" t="inlineStr">
+        <is>
+          <t>C. E. R. HELECHALES</t>
+        </is>
+      </c>
+      <c r="L364" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M364" t="inlineStr">
+        <is>
+          <t>VDA. HELECHALES</t>
+        </is>
+      </c>
+      <c r="N364" t="inlineStr">
+        <is>
+          <t>ón: VDA. HELECHALES</t>
+        </is>
+      </c>
+      <c r="O364" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t>Educación artística - artes plásticas</t>
+        </is>
+      </c>
+      <c r="D365" t="inlineStr">
+        <is>
+          <t>Copacabana</t>
+        </is>
+      </c>
+      <c r="E365" t="inlineStr">
+        <is>
+          <t>31/07/2026 a las 15:56</t>
+        </is>
+      </c>
+      <c r="F365" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G365" t="inlineStr">
+        <is>
+          <t>Valle del Aburrá</t>
+        </is>
+      </c>
+      <c r="H365" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I365" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J365" t="inlineStr">
+        <is>
+          <t>I. E. GABRIELA MISTRAL</t>
+        </is>
+      </c>
+      <c r="K365" t="inlineStr">
+        <is>
+          <t>COLEGIO GABRIELA MISTRAL - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L365" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M365" t="inlineStr">
+        <is>
+          <t>SAN JUAN</t>
+        </is>
+      </c>
+      <c r="N365" t="inlineStr">
+        <is>
+          <t>ón: KR 28 43 199</t>
+        </is>
+      </c>
+      <c r="O365" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C366" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="D366" t="inlineStr">
+        <is>
+          <t>Cáceres</t>
+        </is>
+      </c>
+      <c r="E366" t="inlineStr">
+        <is>
+          <t>31/07/2026 a las 15:56</t>
+        </is>
+      </c>
+      <c r="F366" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G366" t="inlineStr">
+        <is>
+          <t>Cáceres</t>
+        </is>
+      </c>
+      <c r="H366" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I366" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J366" t="inlineStr">
+        <is>
+          <t>I. E. R. EL TIGRE</t>
+        </is>
+      </c>
+      <c r="K366" t="inlineStr">
+        <is>
+          <t>C.E.R PELADERO</t>
+        </is>
+      </c>
+      <c r="L366" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M366" t="inlineStr">
+        <is>
+          <t>Dirección: VDA PELADERO</t>
+        </is>
+      </c>
+      <c r="N366" t="inlineStr">
+        <is>
+          <t>ón: VDA PELADERO</t>
+        </is>
+      </c>
+      <c r="O366" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C367" t="inlineStr">
+        <is>
+          <t>Educación artística – danzas</t>
+        </is>
+      </c>
+      <c r="D367" t="inlineStr">
+        <is>
+          <t>San Luis</t>
+        </is>
+      </c>
+      <c r="E367" t="inlineStr">
+        <is>
+          <t>31/07/2026 a las 15:56</t>
+        </is>
+      </c>
+      <c r="F367" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G367" t="inlineStr">
+        <is>
+          <t>San Luis</t>
+        </is>
+      </c>
+      <c r="H367" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I367" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J367" t="inlineStr">
+        <is>
+          <t>I. E. SAN LUIS</t>
+        </is>
+      </c>
+      <c r="K367" t="inlineStr">
+        <is>
+          <t>LICEO SAN LUIS - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L367" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M367" t="inlineStr">
+        <is>
+          <t>Dirección: CL 21 14 01</t>
+        </is>
+      </c>
+      <c r="N367" t="inlineStr">
+        <is>
+          <t>ón: CL 21 14 01</t>
+        </is>
+      </c>
+      <c r="O367" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C368" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="D368" t="inlineStr">
+        <is>
+          <t>San Pedro De Urabá</t>
+        </is>
+      </c>
+      <c r="E368" t="inlineStr">
+        <is>
+          <t>31/07/2026 a las 15:56</t>
+        </is>
+      </c>
+      <c r="F368" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G368" t="inlineStr">
+        <is>
+          <t>San Pedro de Urabá</t>
+        </is>
+      </c>
+      <c r="H368" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I368" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J368" t="inlineStr">
+        <is>
+          <t>I. E. R. BUCHADO MEDIO</t>
+        </is>
+      </c>
+      <c r="K368" t="inlineStr">
+        <is>
+          <t>I. E. R. ALTO ROSARIO</t>
+        </is>
+      </c>
+      <c r="L368" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M368" t="inlineStr">
+        <is>
+          <t>Dirección: VDA. ALTOS DEL ROSARIO</t>
+        </is>
+      </c>
+      <c r="N368" t="inlineStr">
+        <is>
+          <t>ón: VDA. ALTOS DEL ROSARIO</t>
+        </is>
+      </c>
+      <c r="O368" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C369" t="inlineStr">
+        <is>
+          <t>Tecnología e informática</t>
+        </is>
+      </c>
+      <c r="D369" t="inlineStr">
+        <is>
+          <t>Fredonia</t>
+        </is>
+      </c>
+      <c r="E369" t="inlineStr">
+        <is>
+          <t>31/07/2026 a las 15:56</t>
+        </is>
+      </c>
+      <c r="F369" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G369" t="inlineStr">
+        <is>
+          <t>Suroeste</t>
+        </is>
+      </c>
+      <c r="H369" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I369" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J369" t="inlineStr">
+        <is>
+          <t>I. E. ESCUELA NORMAL SUPERIOR MARIANO OSPINA RODRIGUEZ</t>
+        </is>
+      </c>
+      <c r="K369" t="inlineStr">
+        <is>
+          <t>I. E. ESCUELA NORMAL SUPERIOR MARIANO OSPINA RODRIGUEZ - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L369" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M369" t="inlineStr">
+        <is>
+          <t>CABECERA MPAL.</t>
+        </is>
+      </c>
+      <c r="N369" t="inlineStr">
+        <is>
+          <t>ón: KR 51 48 31</t>
+        </is>
+      </c>
+      <c r="O369" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C370" t="inlineStr">
+        <is>
+          <t>Matemáticas</t>
+        </is>
+      </c>
+      <c r="D370" t="inlineStr">
+        <is>
+          <t>Necoclí</t>
+        </is>
+      </c>
+      <c r="E370" t="inlineStr">
+        <is>
+          <t>31/07/2026 a las 15:56</t>
+        </is>
+      </c>
+      <c r="F370" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G370" t="inlineStr">
+        <is>
+          <t>Necoclí</t>
+        </is>
+      </c>
+      <c r="H370" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I370" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J370" t="inlineStr">
+        <is>
+          <t>I. E. R. MELLITO</t>
+        </is>
+      </c>
+      <c r="K370" t="inlineStr">
+        <is>
+          <t>COLEGIO DE DESARROLLO RURAL - MELLITO- SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L370" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M370" t="inlineStr">
+        <is>
+          <t>CORREG. MELLITO</t>
+        </is>
+      </c>
+      <c r="N370" t="inlineStr">
+        <is>
+          <t>ón: CORREG. MELLITO</t>
+        </is>
+      </c>
+      <c r="O370" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C371" t="inlineStr">
+        <is>
+          <t>Ciencias naturales química</t>
+        </is>
+      </c>
+      <c r="D371" t="inlineStr">
+        <is>
+          <t>Necoclí</t>
+        </is>
+      </c>
+      <c r="E371" t="inlineStr">
+        <is>
+          <t>31/07/2026 a las 15:57</t>
+        </is>
+      </c>
+      <c r="F371" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G371" t="inlineStr">
+        <is>
+          <t>Necoclí</t>
+        </is>
+      </c>
+      <c r="H371" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I371" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J371" t="inlineStr">
+        <is>
+          <t>I. E. R. ZAPATA</t>
+        </is>
+      </c>
+      <c r="K371" t="inlineStr">
+        <is>
+          <t>COLEGIO ZAPATA - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L371" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M371" t="inlineStr">
+        <is>
+          <t>CORREG.DE ZAPATA</t>
+        </is>
+      </c>
+      <c r="N371" t="inlineStr">
+        <is>
+          <t>ón: CORREG. DE ZAPATA</t>
+        </is>
+      </c>
+      <c r="O371" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C372" t="inlineStr">
+        <is>
+          <t>Ciencias naturales física</t>
+        </is>
+      </c>
+      <c r="D372" t="inlineStr">
+        <is>
+          <t>Retiro</t>
+        </is>
+      </c>
+      <c r="E372" t="inlineStr">
+        <is>
+          <t>31/07/2026 a las 15:57</t>
+        </is>
+      </c>
+      <c r="F372" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G372" t="inlineStr">
+        <is>
+          <t>Oriente</t>
+        </is>
+      </c>
+      <c r="H372" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I372" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J372" t="inlineStr">
+        <is>
+          <t>I. E. IGNACIO BOTERO VALLEJO</t>
+        </is>
+      </c>
+      <c r="K372" t="inlineStr">
+        <is>
+          <t>I. E. IGNACIO BOTERO VALLEJO - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L372" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M372" t="inlineStr">
+        <is>
+          <t>VDA. EL RETIRO</t>
+        </is>
+      </c>
+      <c r="N372" t="inlineStr">
+        <is>
+          <t>ón: KR 20 SUCRE 23 36</t>
+        </is>
+      </c>
+      <c r="O372" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C373" t="inlineStr">
+        <is>
+          <t>Educación física, recreación y deporte</t>
+        </is>
+      </c>
+      <c r="D373" t="inlineStr">
+        <is>
+          <t>Concordia</t>
+        </is>
+      </c>
+      <c r="E373" t="inlineStr">
+        <is>
+          <t>31/07/2026 a las 15:57</t>
+        </is>
+      </c>
+      <c r="F373" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G373" t="inlineStr">
+        <is>
+          <t>Suroeste</t>
+        </is>
+      </c>
+      <c r="H373" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I373" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J373" t="inlineStr">
+        <is>
+          <t>I. E. DE JESUS</t>
+        </is>
+      </c>
+      <c r="K373" t="inlineStr">
+        <is>
+          <t>I. E. DE JESUS - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L373" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M373" t="inlineStr">
+        <is>
+          <t>KR 22 19 65</t>
+        </is>
+      </c>
+      <c r="N373" t="inlineStr">
+        <is>
+          <t>ón: KR 22 19 65</t>
+        </is>
+      </c>
+      <c r="O373" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C374" t="inlineStr">
+        <is>
+          <t>Educación artística - artes plásticas</t>
+        </is>
+      </c>
+      <c r="D374" t="inlineStr">
+        <is>
+          <t>Santafe De Antioquia</t>
+        </is>
+      </c>
+      <c r="E374" t="inlineStr">
+        <is>
+          <t>31/07/2026 a las 15:57</t>
+        </is>
+      </c>
+      <c r="F374" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G374" t="inlineStr">
+        <is>
+          <t>Occidente</t>
+        </is>
+      </c>
+      <c r="H374" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I374" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J374" t="inlineStr">
+        <is>
+          <t>I. E. SAN LUIS GONZAGA</t>
+        </is>
+      </c>
+      <c r="K374" t="inlineStr">
+        <is>
+          <t>LICEO SAN LUIS GONZAGA - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L374" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M374" t="inlineStr">
+        <is>
+          <t>Dirección: KR 7 13 A 64</t>
+        </is>
+      </c>
+      <c r="N374" t="inlineStr">
+        <is>
+          <t>ón: KR 7 13 A 64</t>
+        </is>
+      </c>
+      <c r="O374" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C375" t="inlineStr">
+        <is>
+          <t>Ciencias sociales</t>
+        </is>
+      </c>
+      <c r="D375" t="inlineStr">
+        <is>
+          <t>Santa Rosa De Osos</t>
+        </is>
+      </c>
+      <c r="E375" t="inlineStr">
+        <is>
+          <t>31/07/2026 a las 15:58</t>
+        </is>
+      </c>
+      <c r="F375" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G375" t="inlineStr">
+        <is>
+          <t>Santa Rosa de Osos</t>
+        </is>
+      </c>
+      <c r="H375" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I375" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J375" t="inlineStr">
+        <is>
+          <t>I. E. R. HOYORRICO</t>
+        </is>
+      </c>
+      <c r="K375" t="inlineStr">
+        <is>
+          <t>I. E. R. HOYORRICO - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L375" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M375" t="inlineStr">
+        <is>
+          <t>CORREG. HOYO RICO</t>
+        </is>
+      </c>
+      <c r="N375" t="inlineStr">
+        <is>
+          <t>ón: CORREG. HOYO RICO</t>
+        </is>
+      </c>
+      <c r="O375" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C376" t="inlineStr">
+        <is>
+          <t>Matemáticas</t>
+        </is>
+      </c>
+      <c r="D376" t="inlineStr">
+        <is>
+          <t>Sabanalarga</t>
+        </is>
+      </c>
+      <c r="E376" t="inlineStr">
+        <is>
+          <t>31/07/2026 a las 15:58</t>
+        </is>
+      </c>
+      <c r="F376" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G376" t="inlineStr">
+        <is>
+          <t>Sabanalarga</t>
+        </is>
+      </c>
+      <c r="H376" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I376" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J376" t="inlineStr">
+        <is>
+          <t>I. E. SAN JOSE</t>
+        </is>
+      </c>
+      <c r="K376" t="inlineStr">
+        <is>
+          <t>C.E.R LA SANTAMARIA</t>
+        </is>
+      </c>
+      <c r="L376" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M376" t="inlineStr">
+        <is>
+          <t>VDA. LA STA MARIA</t>
+        </is>
+      </c>
+      <c r="N376" t="inlineStr">
+        <is>
+          <t>ón: VDA LA STA MARIA</t>
+        </is>
+      </c>
+      <c r="O376" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Priorizadas para jóvenes entre 18 y 28 años</t>
+        </is>
+      </c>
+      <c r="C377" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>Sabanalarga</t>
+        </is>
+      </c>
+      <c r="E377" t="inlineStr">
+        <is>
+          <t>31/07/2026 a las 15:59</t>
+        </is>
+      </c>
+      <c r="F377" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G377" t="inlineStr">
+        <is>
+          <t>Sabanalarga</t>
+        </is>
+      </c>
+      <c r="H377" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I377" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J377" t="inlineStr">
+        <is>
+          <t>I. E. R. EL JUNCO</t>
+        </is>
+      </c>
+      <c r="K377" t="inlineStr">
+        <is>
+          <t>C. E. R. EL PLACER</t>
+        </is>
+      </c>
+      <c r="L377" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M377" t="inlineStr">
+        <is>
+          <t>VDA. EL PLACER</t>
+        </is>
+      </c>
+      <c r="N377" t="inlineStr">
+        <is>
+          <t>ón: VDA EL PLACER</t>
+        </is>
+      </c>
+      <c r="O377" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C378" t="inlineStr">
+        <is>
+          <t>Preescolar</t>
+        </is>
+      </c>
+      <c r="D378" t="inlineStr">
+        <is>
+          <t>Carepa</t>
+        </is>
+      </c>
+      <c r="E378" t="inlineStr">
+        <is>
+          <t>31/07/2026 a las 15:59</t>
+        </is>
+      </c>
+      <c r="F378" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G378" t="inlineStr">
+        <is>
+          <t>Carepa</t>
+        </is>
+      </c>
+      <c r="H378" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I378" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J378" t="inlineStr">
+        <is>
+          <t>I. E. COLOMBIA</t>
+        </is>
+      </c>
+      <c r="K378" t="inlineStr">
+        <is>
+          <t>COLEGIO COLOMBIA - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L378" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M378" t="inlineStr">
+        <is>
+          <t>B. GAITAN</t>
+        </is>
+      </c>
+      <c r="N378" t="inlineStr">
+        <is>
+          <t>ón: CL. 83 CRA67</t>
+        </is>
+      </c>
+      <c r="O378" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Priorizadas para jóvenes entre 18 y 28 años</t>
+        </is>
+      </c>
+      <c r="C379" t="inlineStr">
+        <is>
+          <t>Preescolar</t>
+        </is>
+      </c>
+      <c r="D379" t="inlineStr">
+        <is>
+          <t>Necoclí</t>
+        </is>
+      </c>
+      <c r="E379" t="inlineStr">
+        <is>
+          <t>31/07/2026 a las 16:00</t>
+        </is>
+      </c>
+      <c r="F379" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G379" t="inlineStr">
+        <is>
+          <t>Necoclí</t>
+        </is>
+      </c>
+      <c r="H379" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I379" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J379" t="inlineStr">
+        <is>
+          <t>I. E. ANTONIO ROLDAN BETANCUR</t>
+        </is>
+      </c>
+      <c r="K379" t="inlineStr">
+        <is>
+          <t>E U MARIA AUXILIADORA</t>
+        </is>
+      </c>
+      <c r="L379" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M379" t="inlineStr">
+        <is>
+          <t>BR BLASDELEZO</t>
+        </is>
+      </c>
+      <c r="N379" t="inlineStr">
+        <is>
+          <t>ón: KR 46 51 55</t>
+        </is>
+      </c>
+      <c r="O379" t="inlineStr">
         <is>
           <t>A</t>
         </is>

--- a/nuevas_plazas.xlsx
+++ b/nuevas_plazas.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O379"/>
+  <dimension ref="A1:O380"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26706,10 +26706,8 @@
           <t>31/07/2026 a las 15:27</t>
         </is>
       </c>
-      <c r="F351" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
+      <c r="F351" t="n">
+        <v>14</v>
       </c>
       <c r="G351" t="inlineStr">
         <is>
@@ -26783,10 +26781,8 @@
           <t>31/07/2026 a las 15:27</t>
         </is>
       </c>
-      <c r="F352" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
+      <c r="F352" t="n">
+        <v>11</v>
       </c>
       <c r="G352" t="inlineStr">
         <is>
@@ -26860,10 +26856,8 @@
           <t>31/07/2026 a las 15:27</t>
         </is>
       </c>
-      <c r="F353" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
+      <c r="F353" t="n">
+        <v>26</v>
       </c>
       <c r="G353" t="inlineStr">
         <is>
@@ -26937,10 +26931,8 @@
           <t>31/07/2026 a las 15:31</t>
         </is>
       </c>
-      <c r="F354" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="F354" t="n">
+        <v>5</v>
       </c>
       <c r="G354" t="inlineStr">
         <is>
@@ -27014,10 +27006,8 @@
           <t>31/07/2026 a las 15:54</t>
         </is>
       </c>
-      <c r="F355" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F355" t="n">
+        <v>0</v>
       </c>
       <c r="G355" t="inlineStr">
         <is>
@@ -27091,10 +27081,8 @@
           <t>31/07/2026 a las 15:54</t>
         </is>
       </c>
-      <c r="F356" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="F356" t="n">
+        <v>5</v>
       </c>
       <c r="G356" t="inlineStr">
         <is>
@@ -27168,10 +27156,8 @@
           <t>31/07/2026 a las 15:54</t>
         </is>
       </c>
-      <c r="F357" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="F357" t="n">
+        <v>1</v>
       </c>
       <c r="G357" t="inlineStr">
         <is>
@@ -27245,10 +27231,8 @@
           <t>31/07/2026 a las 15:54</t>
         </is>
       </c>
-      <c r="F358" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="F358" t="n">
+        <v>1</v>
       </c>
       <c r="G358" t="inlineStr">
         <is>
@@ -27322,10 +27306,8 @@
           <t>31/07/2026 a las 15:54</t>
         </is>
       </c>
-      <c r="F359" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="F359" t="n">
+        <v>2</v>
       </c>
       <c r="G359" t="inlineStr">
         <is>
@@ -27399,10 +27381,8 @@
           <t>31/07/2026 a las 15:55</t>
         </is>
       </c>
-      <c r="F360" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="F360" t="n">
+        <v>3</v>
       </c>
       <c r="G360" t="inlineStr">
         <is>
@@ -27476,10 +27456,8 @@
           <t>31/07/2026 a las 15:55</t>
         </is>
       </c>
-      <c r="F361" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="F361" t="n">
+        <v>6</v>
       </c>
       <c r="G361" t="inlineStr">
         <is>
@@ -27553,10 +27531,8 @@
           <t>31/07/2026 a las 15:55</t>
         </is>
       </c>
-      <c r="F362" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="F362" t="n">
+        <v>5</v>
       </c>
       <c r="G362" t="inlineStr">
         <is>
@@ -27630,10 +27606,8 @@
           <t>31/07/2026 a las 15:55</t>
         </is>
       </c>
-      <c r="F363" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="F363" t="n">
+        <v>5</v>
       </c>
       <c r="G363" t="inlineStr">
         <is>
@@ -27707,10 +27681,8 @@
           <t>31/07/2026 a las 15:55</t>
         </is>
       </c>
-      <c r="F364" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="F364" t="n">
+        <v>6</v>
       </c>
       <c r="G364" t="inlineStr">
         <is>
@@ -27784,10 +27756,8 @@
           <t>31/07/2026 a las 15:56</t>
         </is>
       </c>
-      <c r="F365" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="F365" t="n">
+        <v>2</v>
       </c>
       <c r="G365" t="inlineStr">
         <is>
@@ -27861,10 +27831,8 @@
           <t>31/07/2026 a las 15:56</t>
         </is>
       </c>
-      <c r="F366" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="F366" t="n">
+        <v>3</v>
       </c>
       <c r="G366" t="inlineStr">
         <is>
@@ -27938,10 +27906,8 @@
           <t>31/07/2026 a las 15:56</t>
         </is>
       </c>
-      <c r="F367" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="F367" t="n">
+        <v>1</v>
       </c>
       <c r="G367" t="inlineStr">
         <is>
@@ -28015,10 +27981,8 @@
           <t>31/07/2026 a las 15:56</t>
         </is>
       </c>
-      <c r="F368" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="F368" t="n">
+        <v>2</v>
       </c>
       <c r="G368" t="inlineStr">
         <is>
@@ -28092,10 +28056,8 @@
           <t>31/07/2026 a las 15:56</t>
         </is>
       </c>
-      <c r="F369" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="F369" t="n">
+        <v>4</v>
       </c>
       <c r="G369" t="inlineStr">
         <is>
@@ -28169,10 +28131,8 @@
           <t>31/07/2026 a las 15:56</t>
         </is>
       </c>
-      <c r="F370" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="F370" t="n">
+        <v>2</v>
       </c>
       <c r="G370" t="inlineStr">
         <is>
@@ -28246,10 +28206,8 @@
           <t>31/07/2026 a las 15:57</t>
         </is>
       </c>
-      <c r="F371" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="F371" t="n">
+        <v>1</v>
       </c>
       <c r="G371" t="inlineStr">
         <is>
@@ -28323,10 +28281,8 @@
           <t>31/07/2026 a las 15:57</t>
         </is>
       </c>
-      <c r="F372" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F372" t="n">
+        <v>0</v>
       </c>
       <c r="G372" t="inlineStr">
         <is>
@@ -28400,10 +28356,8 @@
           <t>31/07/2026 a las 15:57</t>
         </is>
       </c>
-      <c r="F373" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="F373" t="n">
+        <v>5</v>
       </c>
       <c r="G373" t="inlineStr">
         <is>
@@ -28477,10 +28431,8 @@
           <t>31/07/2026 a las 15:57</t>
         </is>
       </c>
-      <c r="F374" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F374" t="n">
+        <v>0</v>
       </c>
       <c r="G374" t="inlineStr">
         <is>
@@ -28554,10 +28506,8 @@
           <t>31/07/2026 a las 15:58</t>
         </is>
       </c>
-      <c r="F375" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="F375" t="n">
+        <v>5</v>
       </c>
       <c r="G375" t="inlineStr">
         <is>
@@ -28631,10 +28581,8 @@
           <t>31/07/2026 a las 15:58</t>
         </is>
       </c>
-      <c r="F376" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="F376" t="n">
+        <v>1</v>
       </c>
       <c r="G376" t="inlineStr">
         <is>
@@ -28708,10 +28656,8 @@
           <t>31/07/2026 a las 15:59</t>
         </is>
       </c>
-      <c r="F377" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="F377" t="n">
+        <v>4</v>
       </c>
       <c r="G377" t="inlineStr">
         <is>
@@ -28785,10 +28731,8 @@
           <t>31/07/2026 a las 15:59</t>
         </is>
       </c>
-      <c r="F378" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="F378" t="n">
+        <v>4</v>
       </c>
       <c r="G378" t="inlineStr">
         <is>
@@ -28862,10 +28806,8 @@
           <t>31/07/2026 a las 16:00</t>
         </is>
       </c>
-      <c r="F379" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="F379" t="n">
+        <v>2</v>
       </c>
       <c r="G379" t="inlineStr">
         <is>
@@ -28908,6 +28850,83 @@
         </is>
       </c>
       <c r="O379" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C380" t="inlineStr">
+        <is>
+          <t>Ciencias naturales química</t>
+        </is>
+      </c>
+      <c r="D380" t="inlineStr">
+        <is>
+          <t>Rionegro</t>
+        </is>
+      </c>
+      <c r="E380" t="inlineStr">
+        <is>
+          <t>13/08/2026 a las 14:46</t>
+        </is>
+      </c>
+      <c r="F380" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G380" t="inlineStr">
+        <is>
+          <t>Rionegro</t>
+        </is>
+      </c>
+      <c r="H380" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I380" t="inlineStr">
+        <is>
+          <t>ía de Educación: Rionegro</t>
+        </is>
+      </c>
+      <c r="J380" t="inlineStr">
+        <is>
+          <t>I. E. CONCEJO MUNICIPAL EL PORVENIR</t>
+        </is>
+      </c>
+      <c r="K380" t="inlineStr">
+        <is>
+          <t>COLEGIO CONCEJO MUNICIPAL EL PORVENIR - SEDE PRINC</t>
+        </is>
+      </c>
+      <c r="L380" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M380" t="inlineStr">
+        <is>
+          <t>COMUNA OCCIDENTAL</t>
+        </is>
+      </c>
+      <c r="N380" t="inlineStr">
+        <is>
+          <t>ón: CRA 69 48B-63</t>
+        </is>
+      </c>
+      <c r="O380" t="inlineStr">
         <is>
           <t>A</t>
         </is>

--- a/nuevas_plazas.xlsx
+++ b/nuevas_plazas.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O380"/>
+  <dimension ref="A1:O384"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28881,10 +28881,8 @@
           <t>13/08/2026 a las 14:46</t>
         </is>
       </c>
-      <c r="F380" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="F380" t="n">
+        <v>8</v>
       </c>
       <c r="G380" t="inlineStr">
         <is>
@@ -28927,6 +28925,314 @@
         </is>
       </c>
       <c r="O380" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C381" t="inlineStr">
+        <is>
+          <t>Ciencias sociales</t>
+        </is>
+      </c>
+      <c r="D381" t="inlineStr">
+        <is>
+          <t>Turbo</t>
+        </is>
+      </c>
+      <c r="E381" t="inlineStr">
+        <is>
+          <t>14/08/2026 a las 11:09</t>
+        </is>
+      </c>
+      <c r="F381" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G381" t="inlineStr">
+        <is>
+          <t>Turbo</t>
+        </is>
+      </c>
+      <c r="H381" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I381" t="inlineStr">
+        <is>
+          <t>ía de Educación: Turbo</t>
+        </is>
+      </c>
+      <c r="J381" t="inlineStr">
+        <is>
+          <t>C.E. La Pita</t>
+        </is>
+      </c>
+      <c r="K381" t="inlineStr">
+        <is>
+          <t>C.E La Pita - Sede Principal</t>
+        </is>
+      </c>
+      <c r="L381" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M381" t="inlineStr">
+        <is>
+          <t>Dirección: VEREDA LA PITA</t>
+        </is>
+      </c>
+      <c r="N381" t="inlineStr">
+        <is>
+          <t>ón: VEREDA LA PITA</t>
+        </is>
+      </c>
+      <c r="O381" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C382" t="inlineStr">
+        <is>
+          <t>Educación física, recreación y deporte</t>
+        </is>
+      </c>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>Turbo</t>
+        </is>
+      </c>
+      <c r="E382" t="inlineStr">
+        <is>
+          <t>14/08/2026 a las 11:09</t>
+        </is>
+      </c>
+      <c r="F382" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="G382" t="inlineStr">
+        <is>
+          <t>Turbo</t>
+        </is>
+      </c>
+      <c r="H382" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I382" t="inlineStr">
+        <is>
+          <t>ía de Educación: Turbo</t>
+        </is>
+      </c>
+      <c r="J382" t="inlineStr">
+        <is>
+          <t>I.E. Pueblo Bello</t>
+        </is>
+      </c>
+      <c r="K382" t="inlineStr">
+        <is>
+          <t>I.E. Pueblo Bello - Sede Principal</t>
+        </is>
+      </c>
+      <c r="L382" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M382" t="inlineStr">
+        <is>
+          <t>Dirección: CORREG. PUEBLO BELLO</t>
+        </is>
+      </c>
+      <c r="N382" t="inlineStr">
+        <is>
+          <t>ón: CORREG. PUEBLO BELLO</t>
+        </is>
+      </c>
+      <c r="O382" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C383" t="inlineStr">
+        <is>
+          <t>Ciencias naturales química</t>
+        </is>
+      </c>
+      <c r="D383" t="inlineStr">
+        <is>
+          <t>Turbo</t>
+        </is>
+      </c>
+      <c r="E383" t="inlineStr">
+        <is>
+          <t>14/08/2026 a las 11:09</t>
+        </is>
+      </c>
+      <c r="F383" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G383" t="inlineStr">
+        <is>
+          <t>Turbo</t>
+        </is>
+      </c>
+      <c r="H383" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I383" t="inlineStr">
+        <is>
+          <t>ía de Educación: Turbo</t>
+        </is>
+      </c>
+      <c r="J383" t="inlineStr">
+        <is>
+          <t>I.E. Pueblo Bello</t>
+        </is>
+      </c>
+      <c r="K383" t="inlineStr">
+        <is>
+          <t>I.E. Pueblo Bello - Sede Principal</t>
+        </is>
+      </c>
+      <c r="L383" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M383" t="inlineStr">
+        <is>
+          <t>Dirección: CORREG. PUEBLO BELLO</t>
+        </is>
+      </c>
+      <c r="N383" t="inlineStr">
+        <is>
+          <t>ón: CORREG. PUEBLO BELLO</t>
+        </is>
+      </c>
+      <c r="O383" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C384" t="inlineStr">
+        <is>
+          <t>Humanidades y lengua castellana</t>
+        </is>
+      </c>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>Turbo</t>
+        </is>
+      </c>
+      <c r="E384" t="inlineStr">
+        <is>
+          <t>14/08/2026 a las 11:32</t>
+        </is>
+      </c>
+      <c r="F384" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G384" t="inlineStr">
+        <is>
+          <t>Turbo</t>
+        </is>
+      </c>
+      <c r="H384" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I384" t="inlineStr">
+        <is>
+          <t>ía de Educación: Turbo</t>
+        </is>
+      </c>
+      <c r="J384" t="inlineStr">
+        <is>
+          <t>I.E. Nuevo Antioquia</t>
+        </is>
+      </c>
+      <c r="K384" t="inlineStr">
+        <is>
+          <t>Sede El Venao</t>
+        </is>
+      </c>
+      <c r="L384" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M384" t="inlineStr">
+        <is>
+          <t>VEREDA EL VENAO</t>
+        </is>
+      </c>
+      <c r="N384" t="inlineStr">
+        <is>
+          <t>ón: VEREDA EL VENAO</t>
+        </is>
+      </c>
+      <c r="O384" t="inlineStr">
         <is>
           <t>A</t>
         </is>

--- a/nuevas_plazas.xlsx
+++ b/nuevas_plazas.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O384"/>
+  <dimension ref="A1:O385"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28956,10 +28956,8 @@
           <t>14/08/2026 a las 11:09</t>
         </is>
       </c>
-      <c r="F381" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="F381" t="n">
+        <v>5</v>
       </c>
       <c r="G381" t="inlineStr">
         <is>
@@ -29033,10 +29031,8 @@
           <t>14/08/2026 a las 11:09</t>
         </is>
       </c>
-      <c r="F382" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
+      <c r="F382" t="n">
+        <v>15</v>
       </c>
       <c r="G382" t="inlineStr">
         <is>
@@ -29110,10 +29106,8 @@
           <t>14/08/2026 a las 11:09</t>
         </is>
       </c>
-      <c r="F383" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="F383" t="n">
+        <v>3</v>
       </c>
       <c r="G383" t="inlineStr">
         <is>
@@ -29187,10 +29181,8 @@
           <t>14/08/2026 a las 11:32</t>
         </is>
       </c>
-      <c r="F384" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="F384" t="n">
+        <v>5</v>
       </c>
       <c r="G384" t="inlineStr">
         <is>
@@ -29233,6 +29225,83 @@
         </is>
       </c>
       <c r="O384" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>Cargo Docente Orientador</t>
+        </is>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C385" t="inlineStr">
+        <is>
+          <t>Sin asignación directa</t>
+        </is>
+      </c>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>Envigado</t>
+        </is>
+      </c>
+      <c r="E385" t="inlineStr">
+        <is>
+          <t>14/08/2026 a las 14:29</t>
+        </is>
+      </c>
+      <c r="F385" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G385" t="inlineStr">
+        <is>
+          <t>Envigado</t>
+        </is>
+      </c>
+      <c r="H385" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I385" t="inlineStr">
+        <is>
+          <t>ía de Educación: Envigado</t>
+        </is>
+      </c>
+      <c r="J385" t="inlineStr">
+        <is>
+          <t>INSTITUCION EDUCATIVA MARTIN EDUARDO RIOS LLANOS</t>
+        </is>
+      </c>
+      <c r="K385" t="inlineStr">
+        <is>
+          <t>CENTRO EDUCATIVO RURAL MARTIN EDUARDO RIOS LLANOS</t>
+        </is>
+      </c>
+      <c r="L385" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M385" t="inlineStr">
+        <is>
+          <t>Dirección: VEREDA PANTANILLO</t>
+        </is>
+      </c>
+      <c r="N385" t="inlineStr">
+        <is>
+          <t>ón: VEREDA PANTANILLO</t>
+        </is>
+      </c>
+      <c r="O385" t="inlineStr">
         <is>
           <t>A</t>
         </is>

--- a/nuevas_plazas.xlsx
+++ b/nuevas_plazas.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O385"/>
+  <dimension ref="A1:O390"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29256,10 +29256,8 @@
           <t>14/08/2026 a las 14:29</t>
         </is>
       </c>
-      <c r="F385" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F385" t="n">
+        <v>0</v>
       </c>
       <c r="G385" t="inlineStr">
         <is>
@@ -29302,6 +29300,391 @@
         </is>
       </c>
       <c r="O385" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>Cargo Docente Orientador</t>
+        </is>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C386" t="inlineStr">
+        <is>
+          <t>Sin asignación directa</t>
+        </is>
+      </c>
+      <c r="D386" t="inlineStr">
+        <is>
+          <t>Envigado</t>
+        </is>
+      </c>
+      <c r="E386" t="inlineStr">
+        <is>
+          <t>14/08/2026 a las 14:29</t>
+        </is>
+      </c>
+      <c r="F386" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G386" t="inlineStr">
+        <is>
+          <t>Envigado</t>
+        </is>
+      </c>
+      <c r="H386" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I386" t="inlineStr">
+        <is>
+          <t>ía de Educación: Envigado</t>
+        </is>
+      </c>
+      <c r="J386" t="inlineStr">
+        <is>
+          <t>I. E. JOSE MIGUEL DE LA CALLE</t>
+        </is>
+      </c>
+      <c r="K386" t="inlineStr">
+        <is>
+          <t>SEDE UNICA JOSE MIGUEL DE LA CALLE</t>
+        </is>
+      </c>
+      <c r="L386" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M386" t="inlineStr">
+        <is>
+          <t>Dirección: TR. 34 B S 31 E 66</t>
+        </is>
+      </c>
+      <c r="N386" t="inlineStr">
+        <is>
+          <t>ón: TR. 34 B S 31 E 66</t>
+        </is>
+      </c>
+      <c r="O386" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>Cargo Docente Orientador</t>
+        </is>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C387" t="inlineStr">
+        <is>
+          <t>Sin asignación directa</t>
+        </is>
+      </c>
+      <c r="D387" t="inlineStr">
+        <is>
+          <t>Envigado</t>
+        </is>
+      </c>
+      <c r="E387" t="inlineStr">
+        <is>
+          <t>14/08/2026 a las 14:29</t>
+        </is>
+      </c>
+      <c r="F387" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G387" t="inlineStr">
+        <is>
+          <t>Envigado</t>
+        </is>
+      </c>
+      <c r="H387" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I387" t="inlineStr">
+        <is>
+          <t>ía de Educación: Envigado</t>
+        </is>
+      </c>
+      <c r="J387" t="inlineStr">
+        <is>
+          <t>I. E. COMERCIAL DE ENVIGADO</t>
+        </is>
+      </c>
+      <c r="K387" t="inlineStr">
+        <is>
+          <t>SEDE COMERCIAL DE ENVIGADO</t>
+        </is>
+      </c>
+      <c r="L387" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M387" t="inlineStr">
+        <is>
+          <t>Dirección: CL 41 S 24 C 71</t>
+        </is>
+      </c>
+      <c r="N387" t="inlineStr">
+        <is>
+          <t>ón: CL 41 S 24 C 71</t>
+        </is>
+      </c>
+      <c r="O387" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>Cargo Docente Orientador</t>
+        </is>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C388" t="inlineStr">
+        <is>
+          <t>Sin asignación directa</t>
+        </is>
+      </c>
+      <c r="D388" t="inlineStr">
+        <is>
+          <t>Envigado</t>
+        </is>
+      </c>
+      <c r="E388" t="inlineStr">
+        <is>
+          <t>14/08/2026 a las 14:30</t>
+        </is>
+      </c>
+      <c r="F388" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G388" t="inlineStr">
+        <is>
+          <t>Envigado</t>
+        </is>
+      </c>
+      <c r="H388" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I388" t="inlineStr">
+        <is>
+          <t>ía de Educación: Envigado</t>
+        </is>
+      </c>
+      <c r="J388" t="inlineStr">
+        <is>
+          <t>I. E. LAS PALMAS</t>
+        </is>
+      </c>
+      <c r="K388" t="inlineStr">
+        <is>
+          <t>SEDE LAS PALMAS</t>
+        </is>
+      </c>
+      <c r="L388" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M388" t="inlineStr">
+        <is>
+          <t>Dirección: VIA LAS PALMAS KM 16</t>
+        </is>
+      </c>
+      <c r="N388" t="inlineStr">
+        <is>
+          <t>ón: VIA LAS PALMAS KM 16</t>
+        </is>
+      </c>
+      <c r="O388" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>Cargo Docente Orientador</t>
+        </is>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C389" t="inlineStr">
+        <is>
+          <t>Sin asignación directa</t>
+        </is>
+      </c>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t>Envigado</t>
+        </is>
+      </c>
+      <c r="E389" t="inlineStr">
+        <is>
+          <t>14/08/2026 a las 14:30</t>
+        </is>
+      </c>
+      <c r="F389" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G389" t="inlineStr">
+        <is>
+          <t>Envigado</t>
+        </is>
+      </c>
+      <c r="H389" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I389" t="inlineStr">
+        <is>
+          <t>ía de Educación: Envigado</t>
+        </is>
+      </c>
+      <c r="J389" t="inlineStr">
+        <is>
+          <t>I. E. MANUEL URIBE ANGEL</t>
+        </is>
+      </c>
+      <c r="K389" t="inlineStr">
+        <is>
+          <t>SEDE MANUEL URIBE ANGEL</t>
+        </is>
+      </c>
+      <c r="L389" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M389" t="inlineStr">
+        <is>
+          <t>Dirección: CRA 44 NO.38 SUR 15</t>
+        </is>
+      </c>
+      <c r="N389" t="inlineStr">
+        <is>
+          <t>ón: CRA 44 NO.38 SUR 15</t>
+        </is>
+      </c>
+      <c r="O389" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>Cargo Docente Orientador</t>
+        </is>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C390" t="inlineStr">
+        <is>
+          <t>Sin asignación directa</t>
+        </is>
+      </c>
+      <c r="D390" t="inlineStr">
+        <is>
+          <t>Envigado</t>
+        </is>
+      </c>
+      <c r="E390" t="inlineStr">
+        <is>
+          <t>14/08/2026 a las 14:30</t>
+        </is>
+      </c>
+      <c r="F390" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G390" t="inlineStr">
+        <is>
+          <t>Envigado</t>
+        </is>
+      </c>
+      <c r="H390" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I390" t="inlineStr">
+        <is>
+          <t>ía de Educación: Envigado</t>
+        </is>
+      </c>
+      <c r="J390" t="inlineStr">
+        <is>
+          <t>I. E. LA PAZ</t>
+        </is>
+      </c>
+      <c r="K390" t="inlineStr">
+        <is>
+          <t>INSTITUCION EDUCATIVA LA PAZ</t>
+        </is>
+      </c>
+      <c r="L390" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M390" t="inlineStr">
+        <is>
+          <t>Dirección: CLL 46 S 42-16</t>
+        </is>
+      </c>
+      <c r="N390" t="inlineStr">
+        <is>
+          <t>ón: CLL 46 S 42-16</t>
+        </is>
+      </c>
+      <c r="O390" t="inlineStr">
         <is>
           <t>A</t>
         </is>

--- a/nuevas_plazas.xlsx
+++ b/nuevas_plazas.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O390"/>
+  <dimension ref="A1:O391"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29331,10 +29331,8 @@
           <t>14/08/2026 a las 14:29</t>
         </is>
       </c>
-      <c r="F386" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="F386" t="n">
+        <v>1</v>
       </c>
       <c r="G386" t="inlineStr">
         <is>
@@ -29408,10 +29406,8 @@
           <t>14/08/2026 a las 14:29</t>
         </is>
       </c>
-      <c r="F387" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="F387" t="n">
+        <v>2</v>
       </c>
       <c r="G387" t="inlineStr">
         <is>
@@ -29485,10 +29481,8 @@
           <t>14/08/2026 a las 14:30</t>
         </is>
       </c>
-      <c r="F388" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="F388" t="n">
+        <v>2</v>
       </c>
       <c r="G388" t="inlineStr">
         <is>
@@ -29562,10 +29556,8 @@
           <t>14/08/2026 a las 14:30</t>
         </is>
       </c>
-      <c r="F389" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="F389" t="n">
+        <v>2</v>
       </c>
       <c r="G389" t="inlineStr">
         <is>
@@ -29639,10 +29631,8 @@
           <t>14/08/2026 a las 14:30</t>
         </is>
       </c>
-      <c r="F390" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="F390" t="n">
+        <v>1</v>
       </c>
       <c r="G390" t="inlineStr">
         <is>
@@ -29685,6 +29675,83 @@
         </is>
       </c>
       <c r="O390" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C391" t="inlineStr">
+        <is>
+          <t>Educación artística - artes plásticas</t>
+        </is>
+      </c>
+      <c r="D391" t="inlineStr">
+        <is>
+          <t>Rionegro</t>
+        </is>
+      </c>
+      <c r="E391" t="inlineStr">
+        <is>
+          <t>15/08/2026 a las 14:00</t>
+        </is>
+      </c>
+      <c r="F391" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="G391" t="inlineStr">
+        <is>
+          <t>Rionegro</t>
+        </is>
+      </c>
+      <c r="H391" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I391" t="inlineStr">
+        <is>
+          <t>ía de Educación: Rionegro</t>
+        </is>
+      </c>
+      <c r="J391" t="inlineStr">
+        <is>
+          <t>I. E. LA MOSQUITA</t>
+        </is>
+      </c>
+      <c r="K391" t="inlineStr">
+        <is>
+          <t>I. E. LA MOSQUITA - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L391" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M391" t="inlineStr">
+        <is>
+          <t>VDA. LA MOSQUITA</t>
+        </is>
+      </c>
+      <c r="N391" t="inlineStr">
+        <is>
+          <t>ón: VDA. LA MOSQUITA</t>
+        </is>
+      </c>
+      <c r="O391" t="inlineStr">
         <is>
           <t>A</t>
         </is>

--- a/nuevas_plazas.xlsx
+++ b/nuevas_plazas.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O391"/>
+  <dimension ref="A1:O393"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29706,10 +29706,8 @@
           <t>15/08/2026 a las 14:00</t>
         </is>
       </c>
-      <c r="F391" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
+      <c r="F391" t="n">
+        <v>11</v>
       </c>
       <c r="G391" t="inlineStr">
         <is>
@@ -29752,6 +29750,160 @@
         </is>
       </c>
       <c r="O391" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C392" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="D392" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="E392" t="inlineStr">
+        <is>
+          <t>15/08/2026 a las 15:49</t>
+        </is>
+      </c>
+      <c r="F392" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G392" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="H392" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I392" t="inlineStr">
+        <is>
+          <t>ía de Educación: Medellín</t>
+        </is>
+      </c>
+      <c r="J392" t="inlineStr">
+        <is>
+          <t>INST EDUC LA INDEPENDENCIA</t>
+        </is>
+      </c>
+      <c r="K392" t="inlineStr">
+        <is>
+          <t>SEC ESC REFUGIO DEL NIN</t>
+        </is>
+      </c>
+      <c r="L392" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M392" t="inlineStr">
+        <is>
+          <t>LAS INDEPENDENCIAS</t>
+        </is>
+      </c>
+      <c r="N392" t="inlineStr">
+        <is>
+          <t>ón: KR 114 36 C 61</t>
+        </is>
+      </c>
+      <c r="O392" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C393" t="inlineStr">
+        <is>
+          <t>Humanidades y lengua castellana</t>
+        </is>
+      </c>
+      <c r="D393" t="inlineStr">
+        <is>
+          <t>Itaguí</t>
+        </is>
+      </c>
+      <c r="E393" t="inlineStr">
+        <is>
+          <t>15/08/2026 a las 15:52</t>
+        </is>
+      </c>
+      <c r="F393" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G393" t="inlineStr">
+        <is>
+          <t>Itaguí</t>
+        </is>
+      </c>
+      <c r="H393" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I393" t="inlineStr">
+        <is>
+          <t>ía de Educación: Itaguí</t>
+        </is>
+      </c>
+      <c r="J393" t="inlineStr">
+        <is>
+          <t>I.E. LOS GOMEZ</t>
+        </is>
+      </c>
+      <c r="K393" t="inlineStr">
+        <is>
+          <t>I.E. LOS GOMEZ SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L393" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M393" t="inlineStr">
+        <is>
+          <t>Dirección: VDA. LOS GÓMEZ</t>
+        </is>
+      </c>
+      <c r="N393" t="inlineStr">
+        <is>
+          <t>ón: VDA. LOS GÓMEZ</t>
+        </is>
+      </c>
+      <c r="O393" t="inlineStr">
         <is>
           <t>A</t>
         </is>

--- a/nuevas_plazas.xlsx
+++ b/nuevas_plazas.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O393"/>
+  <dimension ref="A1:O394"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29781,10 +29781,8 @@
           <t>15/08/2026 a las 15:49</t>
         </is>
       </c>
-      <c r="F392" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="F392" t="n">
+        <v>1</v>
       </c>
       <c r="G392" t="inlineStr">
         <is>
@@ -29858,10 +29856,8 @@
           <t>15/08/2026 a las 15:52</t>
         </is>
       </c>
-      <c r="F393" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F393" t="n">
+        <v>0</v>
       </c>
       <c r="G393" t="inlineStr">
         <is>
@@ -29904,6 +29900,83 @@
         </is>
       </c>
       <c r="O393" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C394" t="inlineStr">
+        <is>
+          <t>Preescolar</t>
+        </is>
+      </c>
+      <c r="D394" t="inlineStr">
+        <is>
+          <t>Turbo</t>
+        </is>
+      </c>
+      <c r="E394" t="inlineStr">
+        <is>
+          <t>19/08/2026 a las 12:13</t>
+        </is>
+      </c>
+      <c r="F394" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="G394" t="inlineStr">
+        <is>
+          <t>Turbo</t>
+        </is>
+      </c>
+      <c r="H394" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I394" t="inlineStr">
+        <is>
+          <t>ía de Educación: Turbo</t>
+        </is>
+      </c>
+      <c r="J394" t="inlineStr">
+        <is>
+          <t>I.E. Pueblo Bello</t>
+        </is>
+      </c>
+      <c r="K394" t="inlineStr">
+        <is>
+          <t>I.E. Pueblo Bello - Sede Principal</t>
+        </is>
+      </c>
+      <c r="L394" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M394" t="inlineStr">
+        <is>
+          <t>Dirección: CORREG. PUEBLO BELLO</t>
+        </is>
+      </c>
+      <c r="N394" t="inlineStr">
+        <is>
+          <t>ón: CORREG. PUEBLO BELLO</t>
+        </is>
+      </c>
+      <c r="O394" t="inlineStr">
         <is>
           <t>A</t>
         </is>

--- a/nuevas_plazas.xlsx
+++ b/nuevas_plazas.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O394"/>
+  <dimension ref="A1:O395"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29931,10 +29931,8 @@
           <t>19/08/2026 a las 12:13</t>
         </is>
       </c>
-      <c r="F394" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
+      <c r="F394" t="n">
+        <v>9</v>
       </c>
       <c r="G394" t="inlineStr">
         <is>
@@ -29977,6 +29975,83 @@
         </is>
       </c>
       <c r="O394" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="C395" t="inlineStr">
+        <is>
+          <t>Ciencias sociales</t>
+        </is>
+      </c>
+      <c r="D395" t="inlineStr">
+        <is>
+          <t>Itaguí</t>
+        </is>
+      </c>
+      <c r="E395" t="inlineStr">
+        <is>
+          <t>03/09/2026 a las 09:55</t>
+        </is>
+      </c>
+      <c r="F395" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="G395" t="inlineStr">
+        <is>
+          <t>Itaguí</t>
+        </is>
+      </c>
+      <c r="H395" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I395" t="inlineStr">
+        <is>
+          <t>ía de Educación: Itaguí</t>
+        </is>
+      </c>
+      <c r="J395" t="inlineStr">
+        <is>
+          <t>I.E. SIMON BOLIVAR</t>
+        </is>
+      </c>
+      <c r="K395" t="inlineStr">
+        <is>
+          <t>I.E. SIMON BOLIVAR SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="L395" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="M395" t="inlineStr">
+        <is>
+          <t>Dirección: CL 65 46 A 95</t>
+        </is>
+      </c>
+      <c r="N395" t="inlineStr">
+        <is>
+          <t>ón: CL 65 46 A 95</t>
+        </is>
+      </c>
+      <c r="O395" t="inlineStr">
         <is>
           <t>A</t>
         </is>

--- a/nuevas_plazas.xlsx
+++ b/nuevas_plazas.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O395"/>
+  <dimension ref="A1:O396"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30006,10 +30006,8 @@
           <t>03/09/2026 a las 09:55</t>
         </is>
       </c>
-      <c r="F395" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
+      <c r="F395" t="n">
+        <v>50</v>
       </c>
       <c r="G395" t="inlineStr">
         <is>
@@ -30052,6 +30050,83 @@
         </is>
       </c>
       <c r="O395" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>Cargo Docente de aula</t>
+        </is>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>ón: Vacantes Priorizadas para jóvenes entre 18 y 28 años</t>
+        </is>
+      </c>
+      <c r="C396" t="inlineStr">
+        <is>
+          <t>Educación física, recreación y deporte</t>
+        </is>
+      </c>
+      <c r="D396" t="inlineStr">
+        <is>
+          <t>Olaya</t>
+        </is>
+      </c>
+      <c r="E396" t="inlineStr">
+        <is>
+          <t>05/09/2026 a las 09:58</t>
+        </is>
+      </c>
+      <c r="F396" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="G396" t="inlineStr">
+        <is>
+          <t>Occidente</t>
+        </is>
+      </c>
+      <c r="H396" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="I396" t="inlineStr">
+        <is>
+          <t>ía de Educación: Antioquia</t>
+        </is>
+      </c>
+      <c r="J396" t="inlineStr">
+        <is>
+          <t>I. E. OLAYA</t>
+        </is>
+      </c>
+      <c r="K396" t="inlineStr">
+        <is>
+          <t>I. E. LLANADAS</t>
+        </is>
+      </c>
+      <c r="L396" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="M396" t="inlineStr">
+        <is>
+          <t>CORREG. LLANADAS</t>
+        </is>
+      </c>
+      <c r="N396" t="inlineStr">
+        <is>
+          <t>ón: CRA. 11 10-14</t>
+        </is>
+      </c>
+      <c r="O396" t="inlineStr">
         <is>
           <t>A</t>
         </is>
